--- a/untitled folder/HSC_Physics_1st_Paper_Chapter_05_Work_Energy_and_Power.xlsx
+++ b/untitled folder/HSC_Physics_1st_Paper_Chapter_05_Work_Energy_and_Power.xlsx
@@ -1052,7 +1052,7 @@
       <c r="G2" t="inlineStr">
         <is>
           <t>##PRESET:spring(100)[size:medium]##
-একটি কণার ওপর দ্বিমাত্রিক বল $ec{F} = (2y\hat{i} + x^2\hat{j})	ext{ N}$ ক্রিয়াশীল। কণাটিকে মূলবিন্দু $(0,0)$ থেকে $(1,1)	ext{ m}$ বিন্দুতে (ক) সরলরেখা $y = x$ বরাবর এবং (খ) পরাবৃত্তাকার পথ $y = x^2$ বরাবর স্থানান্তরিত করতে কৃতকাজ কত?</t>
+একটি কণার ওপর দ্বিমাত্রিক বল $ec{F} = (2y\hat{i} + x^2\hat{j})\text{ N}$ ক্রিয়াশীল। কণাটিকে মূলবিন্দু $(0,0)$ থেকে $(1,1)\text{ m}$ বিন্দুতে (ক) সরলরেখা $y = x$ বরাবর এবং (খ) পরাবৃত্তাকার পথ $y = x^2$ বরাবর স্থানান্তরিত করতে কৃতকাজ কত?</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1062,9 +1062,9 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>কৃতকাজের লাইন ইন্টিগ্রাল $W = \int ec{F}\cdot dec{r} = \int (2y dx + x^2 dy)$। (ক) পথ $y = x \implies dy = dx$: $W_1 = \int_0^1 (2x dx + x^2 dx) = \left[ x^2 + rac{x^3}{3} -ight]_0^1 = 1 + rac{1}{3} = rac{4}{3}	ext{ J}$। (খ) পথ $y = x^2 \implies dy = 2x dx$: $W_2 = \int_0^1 (2(x^2) dx + x^2(2x dx)) = \int_0^1 (2x^2 + 2x^3)dx = \left[ rac{2x^3}{3} + rac{2x^4}{4} -ight]_0^1 = rac{2}{3} + rac{1}{2} = rac{7}{6}	ext{ J}$। যেহেতু $W_1 
+          <t>কৃতকাজের লাইন ইন্টিগ্রাল $W = \int ec{F}\cdot dec{r} = \int (2y dx + x^2 dy)$। (ক) পথ $y = x \implies dy = dx$: $W_1 = \int_0^1 (2x dx + x^2 dx) = \left[ x^2 + \frac{x^3}{3} +ight]_0^1 = 1 + \frac{1}{3} = \frac{4}{3}\text{ J}$। (খ) পথ $y = x^2 \implies dy = 2x dx$: $W_2 = \int_0^1 (2(x^2) dx + x^2(2x dx)) = \int_0^1 (2x^2 + 2x^3)dx = \left[ \frac{2x^3}{3} + \frac{2x^4}{4} +ight]_0^1 = \frac{2}{3} + \frac{1}{2} = \frac{7}{6}\text{ J}$। যেহেতু $W_1 
 eq W_2$, বলটি পথ-নির্ভর বা অসংরক্ষণশীল।</t>
         </is>
       </c>
@@ -1108,19 +1108,14 @@
           <t>একটি ত্রিমাত্রিক বল ক্ষেত্র $ec{F} = (2xy + z^3)\hat{i} + x^2\hat{j} + 3xz^2\hat{k}$ দ্বারা সংজ্ঞায়িত। প্রমাণ কর যে বলটি একটি সংরক্ষণশীল বল এবং $(0,0,0)$ থেকে $(1,2,1)$ বিন্দুতে কৃতকাজ নির্ণয় কর।</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>কার্ল নির্ণয় করি: $ec{
-abla}	imesec{F} = \hat{i}\left(rac{\partial}{\partial y}(3xz^2) - rac{\partial}{\partial z}(x^2)-ight) - \hat{j}\left(rac{\partial}{\partial x}(3xz^2) - rac{\partial}{\partial z}(2xy+z^3)-ight) + \hat{k}\left(rac{\partial}{\partial y}(x^2) - rac{\partial}{\partial x}(2xy+z^3)+abla}\timesec{F} = \hat{i}\left(\frac{\partial}{\partial y}(3xz^2) - \frac{\partial}{\partial z}(x^2)+ight) - \hat{j}\left(\frac{\partial}{\partial x}(3xz^2) - \frac{\partial}{\partial z}(2xy+z^3)+ight) + \hat{k}\left(\frac{\partial}{\partial y}(x^2) - \frac{\partial}{\partial x}(2xy+z^3) ight) = \hat{i}(0 - 0) - \hat{j}(3z^2 - 3z^2) + \hat{k}(2x - 2x) = ec{0}$। যেহেতু কার্ল শূন্য, বলটি সংরক্ষণশীল। স্কেলার বিভব অপেক্ষক $ec{F} = -ec{
-abla}U \implies U(x,y,z) = -x^2 y - xz^3$। কৃতকাজ $W = -\Delta U = U(0,0,0) - U(1,2,1) = 0 - (-1^2(2) - 1(1)^3) = 2 + 1 = 3	ext{ J}$।</t>
+abla}U \implies U(x,y,z) = -x^2 y - xz^3$। কৃতকাজ $W = -\Delta U = U(0,0,0) - U(1,2,1) = 0 - (-1^2(2) - 1(1)^3) = 2 + 1 = 3\text{ J}$।</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1163,16 +1158,11 @@
           <t>একটি কেন্দ্রীয় বল $ec{F} = -k r^n \hat{r}$ ($k &gt; 0$ ধ্রুবক)। একটি কণা এই বলের অধীনে যে কোনো আবদ্ধ লুপ (Closed Loop) সম্পন্ন করে আদি অবস্থানে ফিরে আসলে মোট কৃতকাজ কত হবে?</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>যেকোনো কেন্দ্রীয় বল $ec{F} = f(r)\hat{r}$ একটি সংরক্ষণশীল বল ক্ষেত্র। এর কার্ল সর্বদা শূন্য: $ec{
-abla}	imes(f(r)\hat{r}) = ec{0}$। ফলে বলের লাইন ইন্টিগ্রাল কেবলমাত্র প্রারম্ভিক ও চূড়ান্ত অবস্থানের দূরত্বের ওপর নির্ভর করে। স্টোকসের উপপাদ্য অনুসারে যেকোনো আবদ্ধ পথ $C$-এর জন্য কৃতকাজ $W = \oint_C ec{F}\cdot dec{r} = \iint_S (ec{
-abla}	imesec{F})\cdot dec{A} = 0$। অতএব কণাটি যে কোনো পথে আদি বিন্দুতে ফিরলে নেট কৃতকাজ সর্বদা শূন্য।</t>
+abla}\times(f(r)\hat{r}) = ec{0}$। ফলে বলের লাইন ইন্টিগ্রাল কেবলমাত্র প্রারম্ভিক ও চূড়ান্ত অবস্থানের দূরত্বের ওপর নির্ভর করে। স্টোকসের উপপাদ্য অনুসারে যেকোনো আবদ্ধ পথ $C$-এর জন্য কৃতকাজ $W = \oint_C ec{F}\cdot dec{r} = \iint_S (ec{
+abla}\timesec{F})\cdot dec{A} = 0$। অতএব কণাটি যে কোনো পথে আদি বিন্দুতে ফিরলে নেট কৃতকাজ সর্বদা শূন্য।</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1212,21 +1202,16 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>একটি অনড় ডিস্ক অনুভূমিক তলে স্থির অক্ষের সাপেক্ষে ঘুরছে। ডিস্কের ওপর একটি পরিবর্তনশীল টর্ক $	au(	heta) = 	au_0 \cos(2	heta)$ ক্রিয়াশীল। $	heta = 0$ থেকে $	heta = \pi/4$ রেডিয়ান ঘূর্ণনে টর্ক দ্বারা কৃত মোট কাজ কত?</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>একটি অনড় ডিস্ক অনুভূমিক তলে স্থির অক্ষের সাপেক্ষে ঘুরছে। ডিস্কের ওপর একটি পরিবর্তনশীল টর্ক $\tau(\theta) = \tau_0 \cos(2\theta)$ ক্রিয়াশীল। $\theta = 0$ থেকে $\theta = \pi/4$ রেডিয়ান ঘূর্ণনে টর্ক দ্বারা কৃত মোট কাজ কত?</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ঘূর্ণন গতির ক্ষেত্রে টর্কের কৃতকাজ হলো কোণীয় সরণের সাপেক্ষে সমাকলন: $W = \int_0^{	heta_f} 	au(	heta)d	heta$। সমাকলন করি: $W = \int_0^{\pi/4} 	au_0 \cos(2	heta)d	heta = 	au_0 \left[ rac{\sin(2	heta)}{2} -ight]_0^{\pi/4} = rac{	au_0}{2}\left[\sin\left(2\cdotrac{\pi}{4}+          <t>ঘূর্ণন গতির ক্ষেত্রে টর্কের কৃতকাজ হলো কোণীয় সরণের সাপেক্ষে সমাকলন: $W = \int_0^{\theta_f} \tau(\theta)d\theta$। সমাকলন করি: $W = \int_0^{\pi/4} \tau_0 \cos(2\theta)d\theta = \tau_0 \left[ \frac{\sin(2\theta)}{2} +ight]_0^{\pi/4} = \frac{\tau_0}{2}\left[\sin\left(2\cdotrac{\pi}{4} ight) - \sin 0-ight] = rac{	au_0}{2}\sin\left(rac{\pi}{2}-ight) = rac{	au_0}{2}$।</t>
+ight] = \frac{\tau_0}{2}\sin\left(\frac{\pi}{2}+ight) = \frac{\tau_0}{2}$।</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1269,14 +1254,9 @@
           <t>একটি আহিত কণা $q$ একটি স্থানিক পরিবর্তনশীল কিন্তু সময়-নিরপেক্ষ শক্তিশালী চৌম্বক ক্ষেত্রে $ec{B}(ec{r})$ বেগ $ec{v}$ নিয়ে প্রবেশ করে একটি জটিল ত্রিমাত্রিক হেলিকাল ও অপ্রতিসম গতিপথ অতিক্রম করে। চৌম্বক বল দ্বারা কণার ওপর কৃত মোট কাজ কত এবং কেন?</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>চৌম্বক ক্ষেত্রে আহিত কণার ওপর ক্রিয়াশীল লরেন্টজ বল হলো $ec{F}_B = q(ec{v}	imesec{B})$। এই বলের দিক সর্বদা কণার তাৎক্ষণিক বেগ $ec{v}$ এবং চৌম্বক ক্ষেত্র $ec{B}$ উভয়ের সাথে লম্ব। কণার ক্ষুদ্র সরণ $dec{r} = ec{v}dt$। অতএব বল কর্তৃক তাৎক্ষণিক কৃতকাজ $dW = ec{F}_B\cdot dec{r} = [q(ec{v}	imesec{B})]\cdot (ec{v}dt) = q[(ec{v}	imesec{B})\cdotec{v}]dt$। ভেক্টর ত্রৈধ গুণনের ধর্ম অনুসারে দুটি একই ভেক্টরের ক্রস গুণনের সাথে ডট গুণন সর্বদা শূন্য: $(ec{v}	imesec{B})\cdotec{v} = 0$। সুতরাং তাৎক্ষণিক ক্ষমতা $P = ec{F}_B\cdotec{v} = 0$ এবং সমগ্র গতিপথ জুড়ে মোট কৃতকাজ $W = 0$। চৌম্বক বল কখনো কণার গতিশক্তি বৃদ্ধি বা হ্রাস করতে পারে না।</t>
+          <t>চৌম্বক ক্ষেত্রে আহিত কণার ওপর ক্রিয়াশীল লরেন্টজ বল হলো $ec{F}_B = q(ec{v}\timesec{B})$। এই বলের দিক সর্বদা কণার তাৎক্ষণিক বেগ $ec{v}$ এবং চৌম্বক ক্ষেত্র $ec{B}$ উভয়ের সাথে লম্ব। কণার ক্ষুদ্র সরণ $dec{r} = ec{v}dt$। অতএব বল কর্তৃক তাৎক্ষণিক কৃতকাজ $dW = ec{F}_B\cdot dec{r} = [q(ec{v}\timesec{B})]\cdot (ec{v}dt) = q[(ec{v}\timesec{B})\cdotec{v}]dt$। ভেক্টর ত্রৈধ গুণনের ধর্ম অনুসারে দুটি একই ভেক্টরের ক্রস গুণনের সাথে ডট গুণন সর্বদা শূন্য: $(ec{v}\timesec{B})\cdotec{v} = 0$। সুতরাং তাৎক্ষণিক ক্ষমতা $P = ec{F}_B\cdotec{v} = 0$ এবং সমগ্র গতিপথ জুড়ে মোট কৃতকাজ $W = 0$। চৌম্বক বল কখনো কণার গতিশক্তি বৃদ্ধি বা হ্রাস করতে পারে না।</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1316,18 +1296,13 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>$m$ ভরের একটি বস্তুকে $u$ বেগে অনুভূমিকের সাথে $	heta$ কোণে নিক্ষেপ করা হলো। নিক্ষেপ বিন্দু থেকে সর্বোচ্চ বিন্দুতে পৌঁছানো পর্যন্ত এবং পুনরায় মাটিতে অবতরণ পর্যন্ত অভিকর্ষজ বল দ্বারা কৃতকাজ কত?</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>$m$ ভরের একটি বস্তুকে $u$ বেগে অনুভূমিকের সাথে $\theta$ কোণে নিক্ষেপ করা হলো। নিক্ষেপ বিন্দু থেকে সর্বোচ্চ বিন্দুতে পৌঁছানো পর্যন্ত এবং পুনরায় মাটিতে অবতরণ পর্যন্ত অভিকর্ষজ বল দ্বারা কৃতকাজ কত?</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>অভিকর্ষজ বল $ec{F} = -mg\hat{j}$ একটি সংরক্ষণশীল বল। এর কৃতকাজ কেবল উল্লম্ব সরণ $\Delta y$-এর ওপর নির্ভর করে: $W = -mg \Delta y$। (১) নিক্ষেপ বিন্দু থেকে সর্বোচ্চ বিন্দুতে উল্লম্ব সরণ $\Delta y = H_{\max} = rac{u^2\sin^2	heta}{2g}$। অতএব অভিকর্ষ বলের কৃতকাজ $W_1 = -mg H_{\max} = -mg\left(rac{u^2\sin^2	heta}{2g}-ight) = -rac{1}{2}m u^2\sin^2	heta$। (২) পুনরায় মাটিতে অবতরণ করলে প্রারম্ভিক ও চূড়ান্ত অবস্থানের উল্লম্ব উচ্চতার পার্থক্য $\Delta y = 0$। ফলে সম্পূর্ণ উড্ডয়নকালে অভিকর্ষজ বল দ্বারা মোট কৃতকাজ $W_{	ext{total}} = 0$।</t>
+          <t>অভিকর্ষজ বল $ec{F} = -mg\hat{j}$ একটি সংরক্ষণশীল বল। এর কৃতকাজ কেবল উল্লম্ব সরণ $\Delta y$-এর ওপর নির্ভর করে: $W = -mg \Delta y$। (১) নিক্ষেপ বিন্দু থেকে সর্বোচ্চ বিন্দুতে উল্লম্ব সরণ $\Delta y = H_{\max} = \frac{u^2\sin^2\theta}{2g}$। অতএব অভিকর্ষ বলের কৃতকাজ $W_1 = -mg H_{\max} = -mg\left(\frac{u^2\sin^2\theta}{2g}+ight) = -\frac{1}{2}m u^2\sin^2\theta$। (২) পুনরায় মাটিতে অবতরণ করলে প্রারম্ভিক ও চূড়ান্ত অবস্থানের উল্লম্ব উচ্চতার পার্থক্য $\Delta y = 0$। ফলে সম্পূর্ণ উড্ডয়নকালে অভিকর্ষজ বল দ্বারা মোট কৃতকাজ $W_{\text{total}} = 0$।</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1370,16 +1345,11 @@
           <t>একটি স্থির বিন্দু আধান $Q$ থেকে অসীম দূরত্বে থাকা অপর একটি আধান $q$-কে $r$ দূরত্বে আনতে স্থির তড়িৎ বল কর্তৃক কৃতকাজ এবং বাহ্যিক এজেন্ট কর্তৃক কৃতকাজ কত?</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>স্থির তড়িৎ বিকর্ষণ বল $F_e = rac{1}{4\pi\epsilon_0}rac{Qq}{x^2}$ (বাইরের দিকে)। অসীম থেকে $r$ দূরত্বে আনতে স্থির তড়িৎ বল দ্বারা কৃতকাজ: $W_e = \int_\infty^r ec{F}_e\cdot dec{r} = \int_\infty^r \left(rac{Qq}{4\pi\epsilon_0 x^2}\hat{r}-ight)\cdot(dx\hat{r}) = \left[ -rac{Qq}{4\pi\epsilon_0 x} -ight]_\infty^r = -rac{Qq}{4\pi\epsilon_0 r}$। গতিশক্তি পরিবর্তন ছাড়া আনতে হলে বাহ্যিক বল $F_{	ext{ext}} = -F_e$ প্রয়োগ করতে হয়। ফলে বাহ্যিক এজেন্ট কর্তৃক কৃতকাজ $W_{	ext{ext}} = -W_e = +rac{Qq}{4\pi\epsilon_0 r}$।</t>
+          <t>স্থির তড়িৎ বিকর্ষণ বল $F_e = \frac{1}{4\pi\epsilon_0}\frac{Qq}{x^2}$ (বাইরের দিকে)। অসীম থেকে $r$ দূরত্বে আনতে স্থির তড়িৎ বল দ্বারা কৃতকাজ: $W_e = \int_\infty^r ec{F}_e\cdot dec{r} = \int_\infty^r \left(\frac{Qq}{4\pi\epsilon_0 x^2}\hat{r}+ight)\cdot(dx\hat{r}) = \left[ -\frac{Qq}{4\pi\epsilon_0 x} +ight]_\infty^r = -\frac{Qq}{4\pi\epsilon_0 r}$। গতিশক্তি পরিবর্তন ছাড়া আনতে হলে বাহ্যিক বল $F_{\text{ext}} = -F_e$ প্রয়োগ করতে হয়। ফলে বাহ্যিক এজেন্ট কর্তৃক কৃতকাজ $W_{\text{ext}} = -W_e = +\frac{Qq}{4\pi\epsilon_0 r}$।</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1422,11 +1392,6 @@
           <t>একটি মেঝের ওপর $m$ ভরের একটি ব্লককে ব্যাসার্ধ $R$-এর একটি বৃত্তাকার পথ বরাবর সমদ্রুতিতে সম্পূর্ণ এক পাক ঘুরিয়ে আদি বিন্দুতে আনা হলো। তলের ঘর্ষণ গুণাঙ্ক $\mu$ হলে ঘর্ষণ বল দ্বারা কৃতকাজ কত?</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>গতীয় ঘর্ষণ বল সর্বদা তাৎক্ষণিক সরণের ঠিক বিপরীত দিকে ক্রিয়া করে: $ec{f}_k = -\mu mg \hat{t}$। ক্ষুদ্র সরণ $dec{r} = ds \hat{t}$। সুতরাং $ec{f}_k \cdot dec{r} = -\mu mg ds$। সম্পূর্ণ বৃত্তাকার পথে মোট পথদৈর্ঘ্য $s = 2\pi R$। অতএব ঘর্ষণ বল দ্বারা মোট কৃতকাজ $W = \int ec{f}_k \cdot dec{r} = -\mu mg \int_0^{2\pi R} ds = -2\pi \mu mg R$। লক্ষণীয় যে সরণ শূন্য হওয়া সত্ত্বেও ঘর্ষণ একটি অসংরক্ষণশীল বল হওয়ায় এর কৃতকাজ শূন্য হয় না এবং এটি তাপ শক্তিতে রূপান্তরিত হয়।</t>
@@ -1472,14 +1437,9 @@
           <t>একটি কণার ওপর প্রযুক্ত বল $ec{F} = z\hat{i} + x\hat{j} + y\hat{k}$। কণাটি একটি হেলিক্স পথ $ec{r}(t) = \cos t\hat{i} + \sin t\hat{j} + t\hat{k}$ বরাবর $t=0$ থেকে $t=2\pi$ পর্যন্ত গতিশীল হলে কৃতকাজ কত?</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>পথের সমীকরণ: $x = \cos t, y = \sin t, z = t$। ব্যবকলন: $dx = -\sin t dt, dy = \cos t dt, dz = dt$। বলের রূপ: $ec{F} = t\hat{i} + \cos t\hat{j} + \sin t\hat{k}$। কাজ $W = \int (F_x dx + F_y dy + F_z dz) = \int_0^{2\pi} (-t\sin t + \cos^2 t + \sin t)dt$। খণ্ড খণ্ড সমাকলন: (১) $\int_0^{2\pi} -t\sin t dt = [t\cos t]_0^{2\pi} - \int_0^{2\pi} \cos t dt = 2\pi(1) - 0 = 2\pi$। (২) $\int_0^{2\pi}\cos^2 t dt = \pi$। (৩) $\int_0^{2\pi}\sin t dt = 0$। অতএব মোট কৃতকাজ $W = 2\pi + \pi + 0 = 3\pi	ext{ J}$।</t>
+          <t>পথের সমীকরণ: $x = \cos t, y = \sin t, z = t$। ব্যবকলন: $dx = -\sin t dt, dy = \cos t dt, dz = dt$। বলের রূপ: $ec{F} = t\hat{i} + \cos t\hat{j} + \sin t\hat{k}$। কাজ $W = \int (F_x dx + F_y dy + F_z dz) = \int_0^{2\pi} (-t\sin t + \cos^2 t + \sin t)dt$। খণ্ড খণ্ড সমাকলন: (১) $\int_0^{2\pi} -t\sin t dt = [t\cos t]_0^{2\pi} - \int_0^{2\pi} \cos t dt = 2\pi(1) - 0 = 2\pi$। (২) $\int_0^{2\pi}\cos^2 t dt = \pi$। (৩) $\int_0^{2\pi}\sin t dt = 0$। অতএব মোট কৃতকাজ $W = 2\pi + \pi + 0 = 3\pi\text{ J}$।</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1522,11 +1482,6 @@
           <t>$m$ ভরের একটি ব্লককে অনুভূমিক মসৃণ তলে রাখা হয়েছে। মেঝে থেকে $h$ উচ্চতায় অবস্থিত একটি মসৃণ পুলির মধ্য দিয়ে একটি সুতা দিয়ে ব্লককে বাঁধা। অপর প্রান্ত দিয়ে সুতাটিকে অনুভূমিক সমদ্রুতিতে টেনে ব্লকের অনুভূমিক দূরত্ব $x_1$ থেকে কমিয়ে $x_2$ করা হলে টান বল কর্তৃক কৃতকাজ কত?</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>যেহেতু মেঝে মসৃণ এবং সুতা অপ্রসার্য, শক্তির সংরক্ষণশীলতা অনুসারে টান বল কর্তৃক কৃতকাজ ব্লকের গতিশক্তি বা সংস্থার পরিবর্তনের সমান। ধীরে ধীরে সমবেগে টানলে বিভব শক্তির পরিবর্তন বিবেচনা করি। পুলি থেকে ব্লকের সুতার দৈর্ঘ্য $L(x) = \sqrt{x^2 + h^2}$। সুতা যতটুকু টানা হয় তা হলো দৈর্ঘ্যের পরিবর্তন: $\Delta L = L(x_1) - L(x_2) = \sqrt{x_1^2 + h^2} - \sqrt{x_2^2 + h^2}$। সুতার টান $T$ ধ্রুব হলে কৃতকাজ $W = T \Delta L = T\left(\sqrt{x_1^2 + h^2} - \sqrt{x_2^2 + h^2}@@ -1570,26 +1525,21 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>দুটি নিরপেক্ষ অণুর মধ্যকার লেনার্ড-জোনস বিভব শক্তি $U(r) = 4\epsilon \left[ \left(rac{\sigma}{r}-ight)^{12} - \left(rac{\sigma}{r}+          <t>দুটি নিরপেক্ষ অণুর মধ্যকার লেনার্ড-জোনস বিভব শক্তি $U(r) = 4\epsilon \left[ \left(\frac{\sigma}{r}+ight)^{12} - \left(\frac{\sigma}{r} ight)^6  ight]$ দ্বারা প্রকাশিত। সাম্যাবস্থায় অণুদ্বয়ের মধ্যবর্তী দূরত্ব $r_0$ এবং ওই বিন্দুতে বন্ধন শক্তি (Well Depth) কত?</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>সাম্যাবস্থার শর্ত $rac{dU}{dr} = 0$। ব্যবকলন করি: $rac{dU}{dr} = 4\epsilon \left[ -12rac{\sigma^{12}}{r^{13}} + 6rac{\sigma^6}{r^7} -ight] = 0 \implies 12rac{\sigma^{12}}{r^{13}} = 6rac{\sigma^6}{r^7} \implies 2\sigma^6 = r^6 \implies r_0 = 2^{1/6}\sigma pprox 1.122\sigma$। এই দূরত্বে বিভব শক্তির মান: $U(r_0) = 4\epsilon \left[ \left(rac{1}{2^{1/6}}-ight)^{12} - \left(rac{1}{2^{1/6}}+          <t>সাম্যাবস্থার শর্ত $\frac{dU}{dr} = 0$। ব্যবকলন করি: $\frac{dU}{dr} = 4\epsilon \left[ -12\frac{\sigma^{12}}{r^{13}} + 6\frac{\sigma^6}{r^7} +ight] = 0 \implies 12\frac{\sigma^{12}}{r^{13}} = 6\frac{\sigma^6}{r^7} \implies 2\sigma^6 = r^6 \implies r_0 = 2^{1/6}\sigma pprox 1.122\sigma$। এই দূরত্বে বিভব শক্তির মান: $U(r_0) = 4\epsilon \left[ \left(\frac{1}{2^{1/6}}+ight)^{12} - \left(\frac{1}{2^{1/6}} ight)^6 -ight] = 4\epsilon \left[ rac{1}{4} - rac{1}{2} -ight] = 4\epsilon\left(-rac{1}{4}-ight) = -\epsilon$। অর্থাৎ বিভব কূপের গভীরতা বা বন্ধন শক্তি $\epsilon$। দ্বিতীয় অন্তরক $rac{d^2 U}{dr^2} &gt; 0$ হওয়ায় এটি একটি অত্যন্ত স্থিতিশীল সাম্যাবস্থা।</t>
+ight] = 4\epsilon \left[ \frac{1}{4} - \frac{1}{2} +ight] = 4\epsilon\left(-\frac{1}{4}+ight) = -\epsilon$। অর্থাৎ বিভব কূপের গভীরতা বা বন্ধন শক্তি $\epsilon$। দ্বিতীয় অন্তরক $\frac{d^2 U}{dr^2} &gt; 0$ হওয়ায় এটি একটি অত্যন্ত স্থিতিশীল সাম্যাবস্থা।</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1629,19 +1579,14 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>একটি কণার বিভব শক্তি অপেক্ষক $U(x) = rac{a}{x^2} - rac{b}{x}$ ($a, b &gt; 0$)। $m$ ভরের কণাটির স্থিতিশীল সাম্যাবস্থানের অবস্থান $x_0$ এবং ওই অবস্থানের সাপেক্ষে ক্ষুদ্র দোলনের কৌণিক কম্পাঙ্ক $\omega$ নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>একটি কণার বিভব শক্তি অপেক্ষক $U(x) = \frac{a}{x^2} - \frac{b}{x}$ ($a, b &gt; 0$)। $m$ ভরের কণাটির স্থিতিশীল সাম্যাবস্থানের অবস্থান $x_0$ এবং ওই অবস্থানের সাপেক্ষে ক্ষুদ্র দোলনের কৌণিক কম্পাঙ্ক $\omega$ নির্ণয় কর।</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>সাম্যাবস্থা: $rac{dU}{dx} = -rac{2a}{x^3} + rac{b}{x^2} = 0 \implies rac{b}{x^2} = rac{2a}{x^3} \implies x_0 = rac{2a}{b}$। দ্বিতীয় অন্তরক: $rac{d^2 U}{dx^2} = rac{6a}{x^4} - rac{2b}{x^3}$। $x_0 = rac{2a}{b}$ বিন্দুতে মান: $\left.rac{d^2 U}{dx^2}-ight|_{x_0} = rac{6a}{(2a/b)^4} - rac{2b}{(2a/b)^3} = rac{6a b^4}{16 a^4} - rac{2b b^3}{8 a^3} = rac{3 b^4}{8 a^3} - rac{2 b^4}{8 a^3} = rac{b^4}{8 a^3} &gt; 0$ (স্থিতিশীল)। কার্যকর বল ধ্রুবক $k_{	ext{eff}} = \left.rac{d^2 U}{dx^2}-ight|_{x_0} = rac{b^4}{8 a^3}$। অতএব ক্ষুদ্র দোলনের কৌণিক কম্পাঙ্ক $\omega = \sqrt{rac{k_{	ext{eff}}}{m}} = \sqrt{rac{b^4}{8 m a^3}} = rac{b^2}{2\sqrt{2 m a^3}}$।</t>
+          <t>সাম্যাবস্থা: $\frac{dU}{dx} = -\frac{2a}{x^3} + \frac{b}{x^2} = 0 \implies \frac{b}{x^2} = \frac{2a}{x^3} \implies x_0 = \frac{2a}{b}$। দ্বিতীয় অন্তরক: $\frac{d^2 U}{dx^2} = \frac{6a}{x^4} - \frac{2b}{x^3}$। $x_0 = \frac{2a}{b}$ বিন্দুতে মান: $\left.\frac{d^2 U}{dx^2}+ight|_{x_0} = \frac{6a}{(2a/b)^4} - \frac{2b}{(2a/b)^3} = \frac{6a b^4}{16 a^4} - \frac{2b b^3}{8 a^3} = \frac{3 b^4}{8 a^3} - \frac{2 b^4}{8 a^3} = \frac{b^4}{8 a^3} &gt; 0$ (স্থিতিশীল)। কার্যকর বল ধ্রুবক $k_{\text{eff}} = \left.\frac{d^2 U}{dx^2}+ight|_{x_0} = \frac{b^4}{8 a^3}$। অতএব ক্ষুদ্র দোলনের কৌণিক কম্পাঙ্ক $\omega = \sqrt{\frac{k_{\text{eff}}}{m}} = \sqrt{\frac{b^4}{8 m a^3}} = \frac{b^2}{2\sqrt{2 m a^3}}$।</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1681,18 +1626,13 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>একটি কণার বিভব শক্তি $U(x) = - rac{1}{2}lpha x^2 + rac{1}{4}eta x^4$ ($lpha, eta &gt; 0$)। কণাটির সকল সাম্যাবস্থা নির্ণয় কর এবং কোনগুলো স্থিতিশীল ও কোনটি অস্থিতিশীল তা শনাক্ত কর।</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>একটি কণার বিভব শক্তি $U(x) = - \frac{1}{2}\alpha x^2 + \frac{1}{4}\beta x^4$ ($\alpha, \beta &gt; 0$)। কণাটির সকল সাম্যাবস্থা নির্ণয় কর এবং কোনগুলো স্থিতিশীল ও কোনটি অস্থিতিশীল তা শনাক্ত কর।</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>সাম্যাবস্থার সমীকরণ $rac{dU}{dx} = -lpha x + eta x^3 = x(-lpha + eta x^2) = 0$। এর সমাধান তিনটি বিন্দু: $x_1 = 0$, $x_2 = +\sqrt{rac{lpha}{eta}}$, $x_3 = -\sqrt{rac{lpha}{eta}}$। দ্বিতীয় অন্তরক $rac{d^2 U}{dx^2} = -lpha + 3eta x^2$। (১) $x = 0$-তে $rac{d^2 U}{dx^2} = -lpha &lt; 0$, অর্থাৎ $x = 0$ একটি অস্থিতিশীল সাম্যাবস্থা (Unstable peak)। (২) $x = \pm\sqrt{rac{lpha}{eta}}$-তে $rac{d^2 U}{dx^2} = -lpha + 3eta\left(rac{lpha}{eta}-ight) = 2lpha &gt; 0$, অর্থাৎ এই দুটি বিন্দুতে বিভব শক্তি স্থানীয় সর্বনিম্ন এবং এরা দুটি প্রতিসম স্থিতিশীল সাম্যাবস্থা (Stable double-wells)।</t>
+          <t>সাম্যাবস্থার সমীকরণ $\frac{dU}{dx} = -\alpha x + \beta x^3 = x(-\alpha + \beta x^2) = 0$। এর সমাধান তিনটি বিন্দু: $x_1 = 0$, $x_2 = +\sqrt{\frac{\alpha}{eta}}$, $x_3 = -\sqrt{\frac{\alpha}{eta}}$। দ্বিতীয় অন্তরক $\frac{d^2 U}{dx^2} = -\alpha + 3\beta x^2$। (১) $x = 0$-তে $\frac{d^2 U}{dx^2} = -\alpha &lt; 0$, অর্থাৎ $x = 0$ একটি অস্থিতিশীল সাম্যাবস্থা (Unstable peak)। (২) $x = \pm\sqrt{\frac{\alpha}{eta}}$-তে $\frac{d^2 U}{dx^2} = -\alpha + 3eta\left(\frac{\alpha}{eta}+ight) = 2\alpha &gt; 0$, অর্থাৎ এই দুটি বিন্দুতে বিভব শক্তি স্থানীয় সর্বনিম্ন এবং এরা দুটি প্রতিসম স্থিতিশীল সাম্যাবস্থা (Stable double-wells)।</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1732,22 +1672,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>মোট শক্তি $E$ নিয়ে গতিশীল একটি কণার বিভব শক্তি $U(x) = U_0 	an^2\left(rac{\pi x}{2a}+          <t>মোট শক্তি $E$ নিয়ে গতিশীল একটি কণার বিভব শক্তি $U(x) = U_0 \tan^2\left(\frac{\pi x}{2a} ight)$ (যেখানে $-a &lt; x &lt; a$)। কণাটির গতির অনুমোদিত অঞ্চল (Classically Allowed Region) এবং টার্নিং পয়েন্টসমূহের স্থানাঙ্ক নির্ণয় কর।</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>গতিশক্তি $K(x) = E - U(x) \ge 0 \implies U(x) \le E$। টার্নিং পয়েন্ট (যেখানে বেগ $v=0$) ঘটে যখন $U(x) = E$: $U_0 	an^2\left(rac{\pi x}{2a}-ight) = E \implies 	an\left(rac{\pi x}{2a}-ight) = \pm\sqrt{rac{E}{U_0}} \implies x = \pm rac{2a}{\pi}	an^{-1}\left(\sqrt{rac{E}{U_0}}-ight)$। অনুমোদিত অঞ্চল হলো $-rac{2a}{\pi}	an^{-1}\left(\sqrt{rac{E}{U_0}}-ight) \le x \le rac{2a}{\pi}	an^{-1}\left(\sqrt{rac{E}{U_0}}+          <t>গতিশক্তি $K(x) = E - U(x) \ge 0 \implies U(x) \le E$। টার্নিং পয়েন্ট (যেখানে বেগ $v=0$) ঘটে যখন $U(x) = E$: $U_0 \tan^2\left(\frac{\pi x}{2a}+ight) = E \implies \tan\left(\frac{\pi x}{2a}+ight) = \pm\sqrt{\frac{E}{U_0}} \implies x = \pm \frac{2a}{\pi}\tan^{-1}\left(\sqrt{\frac{E}{U_0}}+ight)$। অনুমোদিত অঞ্চল হলো $-\frac{2a}{\pi}\tan^{-1}\left(\sqrt{\frac{E}{U_0}}+ight) \le x \le \frac{2a}{\pi}\tan^{-1}\left(\sqrt{\frac{E}{U_0}} ight)$। এই সীমার মধ্যে কণাটি অসীম সময় ধরে স্পন্দিত হতে থাকবে।</t>
         </is>
       </c>
@@ -1788,18 +1723,13 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>কেন্দ্রীয় মহাকর্ষীয় বল ক্ষেত্রে $m$ ভরের কণার কৌণিক ভরবেগ $L$ হলে তার এক-মাত্রিক রেডিয়াল গতির জন্য কার্যকর বিভব শক্তি $U_{	ext{eff}}(r) = rac{L^2}{2m r^2} - rac{GMm}{r}$। বৃত্তাকার কক্ষপথের ব্যাসার্ধ $r_c$ এবং ওই কক্ষপথের স্থিতিশীলতা বিশ্লেষণ কর।</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>কেন্দ্রীয় মহাকর্ষীয় বল ক্ষেত্রে $m$ ভরের কণার কৌণিক ভরবেগ $L$ হলে তার এক-মাত্রিক রেডিয়াল গতির জন্য কার্যকর বিভব শক্তি $U_{\text{eff}}(r) = \frac{L^2}{2m r^2} - \frac{GMm}{r}$। বৃত্তাকার কক্ষপথের ব্যাসার্ধ $r_c$ এবং ওই কক্ষপথের স্থিতিশীলতা বিশ্লেষণ কর।</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>কার্যকর সাম্যাবস্থার জন্য $rac{dU_{	ext{eff}}}{dr} = 0 \implies -rac{L^2}{m r^3} + rac{GMm}{r^2} = 0 \implies rac{GMm}{r^2} = rac{L^2}{m r^3} \implies r_c = rac{L^2}{GM m^2}$। এটি বৃত্তাকার কক্ষপথের ব্যাসার্ধ নির্দেশ করে। দ্বিতীয় অন্তরক: $rac{d^2 U_{	ext{eff}}}{dr^2} = rac{3L^2}{m r^4} - rac{2GMm}{r^3}$। $r_c$-এর মান বসিয়ে পাই: $\left.rac{d^2 U_{	ext{eff}}}{dr^2}-ight|_{r_c} = rac{3L^2}{m r_c^4} - rac{2(L^2/mr_c^3)}{r_c} = rac{L^2}{m r_c^4} &gt; 0$। যেহেতু দ্বিতীয় অন্তরক ধনাত্মক, সেহেতু মহাকর্ষীয় ক্ষেত্রে বৃত্তাকার কক্ষপথ সর্বদা ক্ষুদ্র বিচ্যুতির বিপরীতে স্থিতিশীল।</t>
+          <t>কার্যকর সাম্যাবস্থার জন্য $\frac{dU_{\text{eff}}}{dr} = 0 \implies -\frac{L^2}{m r^3} + \frac{GMm}{r^2} = 0 \implies \frac{GMm}{r^2} = \frac{L^2}{m r^3} \implies r_c = \frac{L^2}{GM m^2}$। এটি বৃত্তাকার কক্ষপথের ব্যাসার্ধ নির্দেশ করে। দ্বিতীয় অন্তরক: $\frac{d^2 U_{\text{eff}}}{dr^2} = \frac{3L^2}{m r^4} - \frac{2GMm}{r^3}$। $r_c$-এর মান বসিয়ে পাই: $\left.\frac{d^2 U_{\text{eff}}}{dr^2}+ight|_{r_c} = \frac{3L^2}{m r_c^4} - \frac{2(L^2/mr_c^3)}{r_c} = \frac{L^2}{m r_c^4} &gt; 0$। যেহেতু দ্বিতীয় অন্তরক ধনাত্মক, সেহেতু মহাকর্ষীয় ক্ষেত্রে বৃত্তাকার কক্ষপথ সর্বদা ক্ষুদ্র বিচ্যুতির বিপরীতে স্থিতিশীল।</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1842,14 +1772,9 @@
           <t>একটি দ্বি-পরমাণুক অণুর মোর্স বিভব শক্তি $U(r) = D_e [1 - e^{-a(r - r_e)}]^2$ দ্বারা নির্দেশিত। $r = r_e$ বিন্দুতে বিভব শক্তির মান, ক্ষুদ্র প্রসারণে স্প্রিং ধ্রুবক $k$ এবং বিযোজন শক্তি (Dissociation Energy) নির্ণয় কর।</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>$r = r_e$ বিন্দুতে $1 - e^0 = 0$, ফলে $U(r_e) = 0$। যখন $r 	o \infty$, তখন $e^{-a(r-r_e)} 	o 0$, ফলে $U(\infty) = D_e$। অতএব অণুর বন্ধন ভাঙতে প্রয়োজনীয় বিযোজন শক্তি $D_e$। ক্ষুদ্র প্রসারণে $x = r - r_e \ll 1/a$ হলে $e^{-ax} pprox 1 - ax$। ফলে $1 - e^{-ax} pprox ax$। সুতরাং বিভব শক্তি $U(x) pprox D_e (ax)^2 = D_e a^2 x^2 = rac{1}{2}(2 D_e a^2)x^2$। এটি সরল ছন্দিত স্পন্দনের স্থিতি শক্তি $rac{1}{2}kx^2$-এর সমতুল্য, যেখানে কার্যকর স্প্রিং ধ্রুবক $k = 2 D_e a^2$।</t>
+          <t>$r = r_e$ বিন্দুতে $1 - e^0 = 0$, ফলে $U(r_e) = 0$। যখন $r \to \infty$, তখন $e^{-a(r-r_e)} \to 0$, ফলে $U(\infty) = D_e$। অতএব অণুর বন্ধন ভাঙতে প্রয়োজনীয় বিযোজন শক্তি $D_e$। ক্ষুদ্র প্রসারণে $x = r - r_e \ll 1/a$ হলে $e^{-ax} pprox 1 - ax$। ফলে $1 - e^{-ax} pprox ax$। সুতরাং বিভব শক্তি $U(x) pprox D_e (ax)^2 = D_e a^2 x^2 = \frac{1}{2}(2 D_e a^2)x^2$। এটি সরল ছন্দিত স্পন্দনের স্থিতি শক্তি $\frac{1}{2}kx^2$-এর সমতুল্য, যেখানে কার্যকর স্প্রিং ধ্রুবক $k = 2 D_e a^2$।</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1889,19 +1814,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>একটি একমাত্রিক সংরক্ষণশীল বল ক্ষেত্রের বিভব শক্তি $U(x) = x^4 - 8x^2 + 16$ (যেখানে $U$ জুলে এবং $x$ মিটারে)। $m = 2	ext{ kg}$ ভরের একটি কণার ত্বরণ কোন কোন বিন্দুতে শূন্য হবে এবং কোন বিন্দুতে কণার ওপর বল সর্বাধিক হবে ($-2 \le x \le 2$ ব্যবধিতে)?</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>একটি একমাত্রিক সংরক্ষণশীল বল ক্ষেত্রের বিভব শক্তি $U(x) = x^4 - 8x^2 + 16$ (যেখানে $U$ জুলে এবং $x$ মিটারে)। $m = 2\text{ kg}$ ভরের একটি কণার ত্বরণ কোন কোন বিন্দুতে শূন্য হবে এবং কোন বিন্দুতে কণার ওপর বল সর্বাধিক হবে ($-2 \le x \le 2$ ব্যবধিতে)?</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>বল $F(x) = -rac{dU}{dx} = -(4x^3 - 16x) = 16x - 4x^3$। ত্বরণ শূন্য হওয়ার শর্ত $F(x) = 0 \implies 4x(4 - x^2) = 0 \implies x = 0, \pm 2	ext{ m}$। বলের সর্বোচ্চ মানের জন্য $rac{dF}{dx} = 16 - 12x^2 = 0 \implies x^2 = rac{16}{12} = rac{4}{3} \implies x = \pm rac{2}{\sqrt{3}}	ext{ m}$। ওই বিন্দুতে সর্বোচ্চ বল $F_{\max} = 16\left(rac{2}{\sqrt{3}}-ight) - 4\left(rac{2}{\sqrt{3}}-ight)^3 = rac{32}{\sqrt{3}} - rac{32}{3\sqrt{3}} = rac{64}{3\sqrt{3}}	ext{ N} pprox 12.32	ext{ N}$।</t>
+          <t>বল $F(x) = -\frac{dU}{dx} = -(4x^3 - 16x) = 16x - 4x^3$। ত্বরণ শূন্য হওয়ার শর্ত $F(x) = 0 \implies 4x(4 - x^2) = 0 \implies x = 0, \pm 2\text{ m}$। বলের সর্বোচ্চ মানের জন্য $\frac{dF}{dx} = 16 - 12x^2 = 0 \implies x^2 = \frac{16}{12} = \frac{4}{3} \implies x = \pm \frac{2}{\sqrt{3}}\text{ m}$। ওই বিন্দুতে সর্বোচ্চ বল $F_{\max} = 16\left(\frac{2}{\sqrt{3}}+ight) - 4\left(\frac{2}{\sqrt{3}}+ight)^3 = \frac{32}{\sqrt{3}} - \frac{32}{3\sqrt{3}} = \frac{64}{3\sqrt{3}}\text{ N} pprox 12.32\text{ N}$।</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1991,28 +1911,23 @@
         <is>
           <t>একটি তরলের ঘনত্ব গভীরতার সাথে রৈখিকভাবে বৃদ্ধি পায়: $ ho(y) = -ho_0 (1 + lpha y)$ ($lpha &gt; 0$)। $V$ আয়তন এবং $m$ ভরের একটি ক্ষুদ্র কঠিন কণা তরলে ডুবানো হলো। কণার বিভব শক্তি অপেক্ষক $U(y)$ গঠন কর এবং কণার স্থিতিশীল ভাসমান গভীরতা নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>None</t>
+ho_0 (1 + \alpha y)$ ($\alpha &gt; 0$)। $V$ আয়তন এবং $m$ ভরের একটি ক্ষুদ্র কঠিন কণা তরলে ডুবানো হলো। কণার বিভব শক্তি অপেক্ষক $U(y)$ গঠন কর এবং কণার স্থিতিশীল ভাসমান গভীরতা নির্ণয় কর।</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>গভীরতা $y$ নিচের দিকে ধনাত্মক ধরলে কণার ওপর নিম্নমুখী ওজন $mg$ এবং ঊর্ধ্বমুখী প্লবতা বল $F_b(y) =  ho(y) V g = -ho_0 V g(1 + lpha y)$। নেট নিম্নমুখী বল $F_{	ext{net}}(y) = mg - +ho_0 V g(1 + \alpha y)$। নেট নিম্নমুখী বল $F_{\text{net}}(y) = mg -  ho_0 V g - -ho_0 V g lpha y$। বিভব শক্তি $U(y) = -\int F_{	ext{net}} dy = -(mg - -ho_0 V g)y + rac{1}{2}-ho_0 V g lpha y^2$। সাম্যাবস্থার শর্ত $F_{	ext{net}} = 0 \implies -ho_0 V g(1 + lpha y_0) = mg \implies 1 + lpha y_0 = rac{m}{-ho_0 V} \implies y_0 = rac{1}{lpha}\left(rac{m}{+ho_0 V g \alpha y$। বিভব শক্তি $U(y) = -\int F_{\text{net}} dy = -(mg - +ho_0 V g)y + \frac{1}{2}+ho_0 V g \alpha y^2$। সাম্যাবস্থার শর্ত $F_{\text{net}} = 0 \implies +ho_0 V g(1 + \alpha y_0) = mg \implies 1 + \alpha y_0 = \frac{m}{+ho_0 V} \implies y_0 = \frac{1}{\alpha}\left(\frac{m}{ ho_0 V} - 1-ight)$। দ্বিতীয় অন্তরক $rac{d^2 U}{dy^2} = -ho_0 V g lpha &gt; 0$, ফলে গভীরতা $y_0$ একটি স্থিতিশীল সাম্যাবস্থা।</t>
+ight)$। দ্বিতীয় অন্তরক $\frac{d^2 U}{dy^2} = +ho_0 V g \alpha &gt; 0$, ফলে গভীরতা $y_0$ একটি স্থিতিশীল সাম্যাবস্থা।</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2063,7 +1978,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>খাঁদের ভেতরে কোনো বল নেই ($F = 0$), ফলে কণাটি ধ্রুব দ্রুতি $v = \sqrt{rac{2E}{m}}$ নিয়ে চলাচল করে। দুই দেয়ালের মধ্যে একবার পূর্ণ চক্র (সামনে ও পেছনে যাওয়া) সম্পন্ন করতে অতিক্রান্ত দূরত্ব $2L$। সুতরাং পর্যায়কাল $T = rac{2L}{v} = 2L\sqrt{rac{m}{2E}} = L\sqrt{rac{2m}{E}}$। প্রতিটি দেওয়ালে স্থিতিস্থাপক ধাক্কায় ভরবেগের পরিবর্তন $\Delta p = 2mv = 2m\sqrt{rac{2E}{m}} = 2\sqrt{2mE}$। প্রতিটি দেওয়ালে প্রতি সেকেন্ডে সংঘটিত ধাক্কার সংখ্যা $rac{1}{T} = rac{1}{2L}\sqrt{rac{2E}{m}}$। অতএব দেয়ালের ওপর গড় বল $ar{F} = rac{\Delta p}{T} = rac{2\sqrt{2mE}}{L\sqrt{2m/E}} = rac{2E}{L}$।</t>
+          <t>খাঁদের ভেতরে কোনো বল নেই ($F = 0$), ফলে কণাটি ধ্রুব দ্রুতি $v = \sqrt{\frac{2E}{m}}$ নিয়ে চলাচল করে। দুই দেয়ালের মধ্যে একবার পূর্ণ চক্র (সামনে ও পেছনে যাওয়া) সম্পন্ন করতে অতিক্রান্ত দূরত্ব $2L$। সুতরাং পর্যায়কাল $T = \frac{2L}{v} = 2L\sqrt{\frac{m}{2E}} = L\sqrt{\frac{2m}{E}}$। প্রতিটি দেওয়ালে স্থিতিস্থাপক ধাক্কায় ভরবেগের পরিবর্তন $\Delta p = 2mv = 2m\sqrt{\frac{2E}{m}} = 2\sqrt{2mE}$। প্রতিটি দেওয়ালে প্রতি সেকেন্ডে সংঘটিত ধাক্কার সংখ্যা $\frac{1}{T} = \frac{1}{2L}\sqrt{\frac{2E}{m}}$। অতএব দেয়ালের ওপর গড় বল $ar{F} = \frac{\Delta p}{T} = \frac{2\sqrt{2mE}}{L\sqrt{2m/E}} = \frac{2E}{L}$।</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2106,14 +2021,9 @@
           <t>একটি লিফট $a_0$ সমত্বরণে ওপরের দিকে উঠছে। লিফটের ভেতর মেঝে থেকে $h$ উচ্চতায় থাকা $m$ ভরের একটি বস্তুকে মুক্তভাবে ফেলে দেওয়া হলো। লিফটের পর্যবেক্ষকের সাপেক্ষে কাজ-শক্তি উপপাদ্য প্রয়োগ করে মেঝে স্পর্শ করার মুহূর্তে বস্তুর বেগ নির্ণয় কর।</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>লিফটের অ-জড় প্রসঙ্গ কাঠামোতে কণার ওপর অভিকর্ষ বল $mg$ নিচের দিকে এবং ছদ্ম বল $m a_0$ নিচের দিকে ক্রিয়া করে। কার্যকর বল $F_{	ext{eff}} = m(g + a_0)$। কার্যকর বলের কৃতকাজ $W = F_{	ext{eff}} h = m(g + a_0)h$। লিফটের ফ্রেমে আদি বেগ শূন্য, ফলে কাজ-শক্তি উপপাদ্য অনুসারে: $\Delta K' = W \implies rac{1}{2}m v'^2 - 0 = m(g + a_0)h \implies v' = \sqrt{2(g + a_0)h}$। এটি প্রমাণ করে যে ছদ্ম বলের কাজ অন্তর্ভুক্ত করলে অজড় ফ্রেমেও কাজ-শক্তি উপপাদ্য হুবহু বৈধ থাকে।</t>
+          <t>লিফটের অ-জড় প্রসঙ্গ কাঠামোতে কণার ওপর অভিকর্ষ বল $mg$ নিচের দিকে এবং ছদ্ম বল $m a_0$ নিচের দিকে ক্রিয়া করে। কার্যকর বল $F_{\text{eff}} = m(g + a_0)$। কার্যকর বলের কৃতকাজ $W = F_{\text{eff}} h = m(g + a_0)h$। লিফটের ফ্রেমে আদি বেগ শূন্য, ফলে কাজ-শক্তি উপপাদ্য অনুসারে: $\Delta K' = W \implies \frac{1}{2}m v'^2 - 0 = m(g + a_0)h \implies v' = \sqrt{2(g + a_0)h}$। এটি প্রমাণ করে যে ছদ্ম বলের কাজ অন্তর্ভুক্ত করলে অজড় ফ্রেমেও কাজ-শক্তি উপপাদ্য হুবহু বৈধ থাকে।</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2156,14 +2066,9 @@
           <t>একটি অনুভূমিক মসৃণ টেবিলের ওপর $m_1$ ভরের ব্লক রাখা যা একটি হালকা সুতা ও টেবিলের প্রান্তে মসৃণ পুলির মাধ্যমে ঝুলন্ত $m_2$ ভরের ব্লকের সাথে যুক্ত। ঝুলন্ত ব্লকটি স্থির অবস্থা থেকে $h$ উচ্চতা নিচে নামলে কাজ-শক্তি উপপাদ্য দ্বারা উভয় ব্লকের সাধারণ বেগ নির্ণয় কর।</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>সুতা অপ্রসার্য হওয়ায় উভয় ব্লকের তাৎক্ষণিক দ্রুতি সমান ($v$)। সম্পূর্ণ সংস্থায় সুতার টান একটি অভ্যন্তরীণ বল, যার নেট কৃতকাজ শূন্য: $W_{	ext{tension}} = T h - T h = 0$। একমাত্র বাহ্যিক বল যা কাজ করে তা হলো $m_2$-এর ওজন: $W_{	ext{ext}} = m_2 g h$। সংস্থার মোট গতিশক্তির পরিবর্তন $\Delta K = rac{1}{2}(m_1 + m_2)v^2 - 0$। কাজ-শক্তি উপপাদ্য অনুসারে: $\Delta K = W_{	ext{ext}} \implies rac{1}{2}(m_1 + m_2)v^2 = m_2 g h \implies v = \sqrt{rac{2 m_2 g h}{m_1 + m_2}}$।</t>
+          <t>সুতা অপ্রসার্য হওয়ায় উভয় ব্লকের তাৎক্ষণিক দ্রুতি সমান ($v$)। সম্পূর্ণ সংস্থায় সুতার টান একটি অভ্যন্তরীণ বল, যার নেট কৃতকাজ শূন্য: $W_{\text{tension}} = T h - T h = 0$। একমাত্র বাহ্যিক বল যা কাজ করে তা হলো $m_2$-এর ওজন: $W_{\text{ext}} = m_2 g h$। সংস্থার মোট গতিশক্তির পরিবর্তন $\Delta K = \frac{1}{2}(m_1 + m_2)v^2 - 0$। কাজ-শক্তি উপপাদ্য অনুসারে: $\Delta K = W_{\text{ext}} \implies \frac{1}{2}(m_1 + m_2)v^2 = m_2 g h \implies v = \sqrt{\frac{2 m_2 g h}{m_1 + m_2}}$।</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2206,14 +2111,9 @@
           <t>$R$ ব্যাসার্ধের একটি উল্লম্ব মসৃণ বৃত্তাকার তারের রিংয়ের ওপর একটি ছোট পুঁতি (ভর $m$) চলতে পারে। রিংয়ের শীর্ষবিন্দুতে $k$ স্প্রিং ধ্রুবকের একটি স্প্রিং আটকানো যার স্বাভাবিক অপ্রসারিত দৈর্ঘ্য $R$ এবং অপর প্রান্ত পুঁতির সাথে যুক্ত। পুঁতিটিকে রিংয়ের অনুভূমিক বিন্দু থেকে স্থির অবস্থা থেকে ছেড়ে দিলে সর্বনিম্ন বিন্দুতে এর দ্রুতি কত হবে?</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>শীর্ষবিন্দু থেকে অনুভূমিক বিন্দুর দূরত্ব $\sqrt{R^2 + R^2} = \sqrt{2}R$। আদি প্রসারণ $x_1 = \sqrt{2}R - R = (\sqrt{2}-1)R$। আদি উচ্চতা সর্বনিম্ন বিন্দু থেকে $h_1 = R$। সর্বনিম্ন বিন্দুতে শীর্ষ থেকে দূরত্ব $2R$, ফলে চূড়ান্ত প্রসারণ $x_2 = 2R - R = R$। সর্বনিম্ন বিন্দুতে উচ্চতা $h_2 = 0$। শক্তির সংরক্ষণশীলতা: $K_1 + U_{g,1} + U_{s,1} = K_2 + U_{g,2} + U_{s,2} \implies 0 + mgR + rac{1}{2}k [(\sqrt{2}-1)R]^2 = rac{1}{2}m v^2 + 0 + rac{1}{2}k R^2$। সমীকরণ সমাধান করে: $rac{1}{2}m v^2 = mgR + rac{1}{2}k R^2 [(\sqrt{2}-1)^2 - 1] = mgR + rac{1}{2}k R^2 [2 - 2\sqrt{2} + 1 - 1] = mgR + k R^2 (1 - \sqrt{2})$। অতএব $v = \sqrt{2gR - rac{2k R^2(\sqrt{2}-1)}{m}}$ (বাস্তব মানের জন্য শর্ত সাপেক্ষে)।</t>
+          <t>শীর্ষবিন্দু থেকে অনুভূমিক বিন্দুর দূরত্ব $\sqrt{R^2 + R^2} = \sqrt{2}R$। আদি প্রসারণ $x_1 = \sqrt{2}R - R = (\sqrt{2}-1)R$। আদি উচ্চতা সর্বনিম্ন বিন্দু থেকে $h_1 = R$। সর্বনিম্ন বিন্দুতে শীর্ষ থেকে দূরত্ব $2R$, ফলে চূড়ান্ত প্রসারণ $x_2 = 2R - R = R$। সর্বনিম্ন বিন্দুতে উচ্চতা $h_2 = 0$। শক্তির সংরক্ষণশীলতা: $K_1 + U_{g,1} + U_{s,1} = K_2 + U_{g,2} + U_{s,2} \implies 0 + mgR + \frac{1}{2}k [(\sqrt{2}-1)R]^2 = \frac{1}{2}m v^2 + 0 + \frac{1}{2}k R^2$। সমীকরণ সমাধান করে: $\frac{1}{2}m v^2 = mgR + \frac{1}{2}k R^2 [(\sqrt{2}-1)^2 - 1] = mgR + \frac{1}{2}k R^2 [2 - 2\sqrt{2} + 1 - 1] = mgR + k R^2 (1 - \sqrt{2})$। অতএব $v = \sqrt{2gR - \frac{2k R^2(\sqrt{2}-1)}{m}}$ (বাস্তব মানের জন্য শর্ত সাপেক্ষে)।</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2253,17 +2153,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>$	heta$ নতি কোণের এবং $L$ দৈর্ঘ্যের একটি অমসৃণ হেলানো তলে $m$ ভরের একটি ব্লক স্থির অবস্থা থেকে ছেড়ে দেওয়া হলো। তলের ঘর্ষণ গুণাঙ্ক $\mu$ ($	an	heta &gt; \mu$)। ব্লকটি তলের পাদদেশে পৌঁছালে তার গতিশক্তি এবং ঘর্ষণজনিত কারণে উৎপন্ন তাপ শক্তির অনুপাত কত?</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>$\theta$ নতি কোণের এবং $L$ দৈর্ঘ্যের একটি অমসৃণ হেলানো তলে $m$ ভরের একটি ব্লক স্থির অবস্থা থেকে ছেড়ে দেওয়া হলো। তলের ঘর্ষণ গুণাঙ্ক $\mu$ ($\tan\theta &gt; \mu$)। ব্লকটি তলের পাদদেশে পৌঁছালে তার গতিশক্তি এবং ঘর্ষণজনিত কারণে উৎপন্ন তাপ শক্তির অনুপাত কত?</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>পাদদেশে উল্লম্ব উচ্চতা হ্রাস $h = L\sin	heta$। মহাকর্ষ বলের কৃতকাজ $W_g = mgh = mgL\sin	heta$। তলের লম্ব অভিলম্ব বল $N = mg\cos	heta$। ঘর্ষণ বল $f_k = \mu mg\cos	heta$। ঘর্ষণ বল দ্বারা কৃতকাজ $W_f = -f_k L = -\mu mgL\cos	heta$। উৎপন্ন তাপ শক্তি $Q = |W_f| = \mu mgL\cos	heta$। কাজ-শক্তি উপপাদ্য অনুসারে অর্জিত গতিশক্তি $K = W_g + W_f = mgL(\sin	heta - \mu\cos	heta)$। গতিশক্তি ও তাপের অনুপাত $rac{K}{Q} = rac{mgL(\sin	heta - \mu\cos	heta)}{\mu mgL\cos	heta} = rac{\sin	heta - \mu\cos	heta}{\mu\cos	heta} = rac{	an	heta}{\mu} - 1$।</t>
+          <t>পাদদেশে উল্লম্ব উচ্চতা হ্রাস $h = L\sin\theta$। মহাকর্ষ বলের কৃতকাজ $W_g = mgh = mgL\sin\theta$। তলের লম্ব অভিলম্ব বল $N = mg\cos\theta$। ঘর্ষণ বল $f_k = \mu mg\cos\theta$। ঘর্ষণ বল দ্বারা কৃতকাজ $W_f = -f_k L = -\mu mgL\cos\theta$। উৎপন্ন তাপ শক্তি $Q = |W_f| = \mu mgL\cos\theta$। কাজ-শক্তি উপপাদ্য অনুসারে অর্জিত গতিশক্তি $K = W_g + W_f = mgL(\sin\theta - \mu\cos\theta)$। গতিশক্তি ও তাপের অনুপাত $\frac{K}{Q} = \frac{mgL(\sin\theta - \mu\cos\theta)}{\mu mgL\cos\theta} = \frac{\sin\theta - \mu\cos\theta}{\mu\cos\theta} = \frac{\tan\theta}{\mu} - 1$।</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2306,14 +2201,9 @@
           <t>$m$ ভরের একটি ব্লক $k$ স্প্রিং ধ্রুবকের একটি স্প্রিং দ্বারা মেঝের সাথে যুক্ত এবং সাম্যাবস্থায় স্থির ছিল। হঠাৎ ব্লকটিকে অনুভূমিকভাবে $v_0$ বেগ দেওয়া হলো। ব্লকটি $d$ দূরত্বে অবস্থিত একটি অনড় স্থিতিস্থাপক দেয়ালের সাথে নিখুঁত স্থিতিস্থাপক ধাক্কা খেয়ে ফিরে এলে স্প্রিংটির সর্বাধিক প্রসারণ কত হবে?</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>দেয়ালে স্থিতিস্থাপক ধাক্কায় কোনো যান্ত্রিক শক্তির ক্ষয় হয় না ($e=1$)। দেয়ালের সাথে ধাক্কার ঠিক পূর্ব মুহূর্তে গতিশক্তি $K_{	ext{wall}} = rac{1}{2}m v_0^2 - rac{1}{2}k d^2$। ধাক্কার পর বেগ বিপরীতমুখী হয়ে একই গতিশক্তি নিয়ে ফিরে আসে। এরপর ব্লকটি সাম্যাবস্থা অতিক্রম করে বিপরীত দিকে সর্বাধিক প্রসারিত হয়। যেহেতু সম্পূর্ণ প্রক্রিয়ায় কোনো শক্তি অপচয় নেই, সেহেতু চূড়ান্ত মুহূর্তে যখন বেগ শূন্য হয়, তখন সমগ্র আদি গতিশক্তি স্প্রিংয়ের বিভব শক্তিতে রূপান্তরিত হয়: $rac{1}{2}k x_{\max}^2 = rac{1}{2}m v_0^2 \implies x_{\max} = v_0\sqrt{rac{m}{k}}$।</t>
+          <t>দেয়ালে স্থিতিস্থাপক ধাক্কায় কোনো যান্ত্রিক শক্তির ক্ষয় হয় না ($e=1$)। দেয়ালের সাথে ধাক্কার ঠিক পূর্ব মুহূর্তে গতিশক্তি $K_{\text{wall}} = \frac{1}{2}m v_0^2 - \frac{1}{2}k d^2$। ধাক্কার পর বেগ বিপরীতমুখী হয়ে একই গতিশক্তি নিয়ে ফিরে আসে। এরপর ব্লকটি সাম্যাবস্থা অতিক্রম করে বিপরীত দিকে সর্বাধিক প্রসারিত হয়। যেহেতু সম্পূর্ণ প্রক্রিয়ায় কোনো শক্তি অপচয় নেই, সেহেতু চূড়ান্ত মুহূর্তে যখন বেগ শূন্য হয়, তখন সমগ্র আদি গতিশক্তি স্প্রিংয়ের বিভব শক্তিতে রূপান্তরিত হয়: $\frac{1}{2}k x_{\max}^2 = \frac{1}{2}m v_0^2 \implies x_{\max} = v_0\sqrt{\frac{m}{k}}$।</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2353,19 +2243,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>একটি কণার গতিশক্তি $K = rac{p^2}{2m}$। যদি কণার ওপর প্রযুক্ত বল $F$ হয়, তবে প্রমাণ কর যে $rac{dK}{dt} = ec{F}\cdotec{v}$ এবং এটি পরিবর্তনশীল ভরের ক্ষেত্রে কীভাবে সংশোধিত হয়?</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>একটি কণার গতিশক্তি $K = \frac{p^2}{2m}$। যদি কণার ওপর প্রযুক্ত বল $F$ হয়, তবে প্রমাণ কর যে $\frac{dK}{dt} = ec{F}\cdotec{v}$ এবং এটি পরিবর্তনশীল ভরের ক্ষেত্রে কীভাবে সংশোধিত হয়?</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>স্থির ভরের ক্ষেত্রে: $rac{dK}{dt} = rac{d}{dt}\left(rac{1}{2}mec{v}\cdotec{v}+          <t>স্থির ভরের ক্ষেত্রে: $\frac{dK}{dt} = \frac{d}{dt}\left(\frac{1}{2}mec{v}\cdotec{v} ight) = m ec{v}\cdotrac{dec{v}}{dt} = \left(mrac{dec{v}}{dt}-ight)\cdotec{v} = ec{F}\cdotec{v} = P$ (তাৎক্ষণিক ক্ষমতা)। কাজ-শক্তি উপপাদ্যের ব্যবকলনীয় রূপ এটি। কিন্তু পরিবর্তনশীল ভরের ক্ষেত্রে (যেমন রকেট বা রেনড্রপ), ভরের সাথে অতিরিক্ত উপাদান গতিশক্তি বহন করে নিয়ে আসে বা নির্গত করে। ফলে কণার নিজস্ব গতিশক্তি পরিবর্তনের হার দাঁড়ায় $rac{dK}{dt} = ec{F}_{	ext{ext}}\cdotec{v} + rac{1}{2}rac{dm}{dt}v^2 + ec{F}_{	ext{thrust}}\cdotec{v}$, যেখানে ভর নির্গমনের আপেক্ষিক গতিশক্তিও অন্তর্ভুক্ত করতে হয়।</t>
+ight)\cdotec{v} = ec{F}\cdotec{v} = P$ (তাৎক্ষণিক ক্ষমতা)। কাজ-শক্তি উপপাদ্যের ব্যবকলনীয় রূপ এটি। কিন্তু পরিবর্তনশীল ভরের ক্ষেত্রে (যেমন রকেট বা রেনড্রপ), ভরের সাথে অতিরিক্ত উপাদান গতিশক্তি বহন করে নিয়ে আসে বা নির্গত করে। ফলে কণার নিজস্ব গতিশক্তি পরিবর্তনের হার দাঁড়ায় $\frac{dK}{dt} = ec{F}_{\text{ext}}\cdotec{v} + \frac{1}{2}\frac{dm}{dt}v^2 + ec{F}_{\text{thrust}}\cdotec{v}$, যেখানে ভর নির্গমনের আপেক্ষিক গতিশক্তিও অন্তর্ভুক্ত করতে হয়।</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2408,14 +2293,9 @@
           <t>$L$ দৈর্ঘ্যের দুটি সমান হালকা সুতার এক প্রান্ত সিলিংয়ের দুটি বিন্দুতে (দূরত্ব $2d$) আটকানো এবং অপর প্রান্তদ্বয় $m$ ভরের একটি বস্তুতে বাঁধা। বস্তুটিকে সিলিংয়ের সমান্তরাল রেখে উল্লম্বভাবে $y$ পরিমাণ নিচে টেনে ছেড়ে দেওয়া হলে সাম্যাবস্থা অতিক্রমকালে এর গতিশক্তি কত হবে?</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>টেনে ধরার সময় সুতার দৈর্ঘ্য $\sqrt{d^2 + y^2}$ হতে হবে, কিন্তু সুতা অপ্রসার্য হওয়ায় এটি একটি নির্দিষ্ট খিলান তৈরি করে। যদি সুতা দুটি স্থিতিস্থাপক হয় (স্প্রিং ধ্রুবক $k$), তবে আদি স্থিতিশক্তি ও চূড়ান্ত স্থিতিশক্তির পার্থক্য সরাসরি গতিশক্তিতে রূপান্তরিত হয়। মহাকর্ষ বলের কৃতকাজ $W_g = mgy$। কোনো শক্তি অপচয় না থাকলে সাম্যাবস্থায় গতিশক্তি $K = mgy + \Delta U_{	ext{elastic}}$।</t>
+          <t>টেনে ধরার সময় সুতার দৈর্ঘ্য $\sqrt{d^2 + y^2}$ হতে হবে, কিন্তু সুতা অপ্রসার্য হওয়ায় এটি একটি নির্দিষ্ট খিলান তৈরি করে। যদি সুতা দুটি স্থিতিস্থাপক হয় (স্প্রিং ধ্রুবক $k$), তবে আদি স্থিতিশক্তি ও চূড়ান্ত স্থিতিশক্তির পার্থক্য সরাসরি গতিশক্তিতে রূপান্তরিত হয়। মহাকর্ষ বলের কৃতকাজ $W_g = mgy$। কোনো শক্তি অপচয় না থাকলে সাম্যাবস্থায় গতিশক্তি $K = mgy + \Delta U_{\text{elastic}}$।</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2455,17 +2335,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>$R$ ব্যাসার্ধের একটি মসৃণ স্থির অনুভূমিক সিলিন্ডারের শীর্ষে $m$ ভরের একটি ছোট ব্লক স্থির ছিল। সামান্য বিচ্যুতির পর ব্লকটি পিছলে নামতে শুরু করে। সিলিন্ডারের পৃষ্ঠের সাথে ব্লকের কোণ যখন $	heta$ (উল্লম্বের সাথে), তখন অভিলম্ব প্রতিক্রিয়া বলের কৃতকাজ কত এবং ওই মুহূর্তে গতিশক্তি কত?</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>$R$ ব্যাসার্ধের একটি মসৃণ স্থির অনুভূমিক সিলিন্ডারের শীর্ষে $m$ ভরের একটি ছোট ব্লক স্থির ছিল। সামান্য বিচ্যুতির পর ব্লকটি পিছলে নামতে শুরু করে। সিলিন্ডারের পৃষ্ঠের সাথে ব্লকের কোণ যখন $\theta$ (উল্লম্বের সাথে), তখন অভিলম্ব প্রতিক্রিয়া বলের কৃতকাজ কত এবং ওই মুহূর্তে গতিশক্তি কত?</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>অভিলম্ব প্রতিক্রিয়া বল $N$ সর্বদা সিলিন্ডারের ব্যাসার্ধ বরাবর বহির্মুখী এবং ব্লকের তাৎক্ষণিক সরণ $dec{s}$ সর্বদা সিলিন্ডারের স্পর্শক বরাবর। যেহেতু $ec{N} \perp dec{s}$, সেহেতু প্রতিক্রিয়া বল দ্বারা কৃতকাজ সর্বদা শূন্য: $W_N = \int ec{N}\cdot dec{s} = 0$। কণার ওপর একমাত্র কার্যক্ষম বল হলো মহাকর্ষ বল। উল্লম্ব উচ্চতা হ্রাস $h = R(1 - \cos	heta)$। কাজ-শক্তি উপপাদ্য অনুসারে অর্জিত গতিশক্তি $K = W_g = mgh = mgR(1 - \cos	heta)$।</t>
+          <t>অভিলম্ব প্রতিক্রিয়া বল $N$ সর্বদা সিলিন্ডারের ব্যাসার্ধ বরাবর বহির্মুখী এবং ব্লকের তাৎক্ষণিক সরণ $dec{s}$ সর্বদা সিলিন্ডারের স্পর্শক বরাবর। যেহেতু $ec{N} \perp dec{s}$, সেহেতু প্রতিক্রিয়া বল দ্বারা কৃতকাজ সর্বদা শূন্য: $W_N = \int ec{N}\cdot dec{s} = 0$। কণার ওপর একমাত্র কার্যক্ষম বল হলো মহাকর্ষ বল। উল্লম্ব উচ্চতা হ্রাস $h = R(1 - \cos\theta)$। কাজ-শক্তি উপপাদ্য অনুসারে অর্জিত গতিশক্তি $K = W_g = mgh = mgR(1 - \cos\theta)$।</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2505,18 +2380,13 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>একটি অনুভূমিক মসৃণ মেঝেতে $M$ ভরের একটি মসৃণ কীলক (নতি কোণ $lpha$) রাখা। কীলকের শীর্ষবিন্দু থেকে $m$ ভরের একটি ব্লক স্থির অবস্থা থেকে ছেড়ে দেওয়া হলো। যখন ব্লকটি উল্লম্বভাবে $h$ উচ্চতা নিচে নামে, তখন অনুভূমিক ভরবেগ সংরক্ষণ এবং শক্তির সংরক্ষণশীলতা প্রয়োগ করে কীলকের বেগ $V$ নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>একটি অনুভূমিক মসৃণ মেঝেতে $M$ ভরের একটি মসৃণ কীলক (নতি কোণ $\alpha$) রাখা। কীলকের শীর্ষবিন্দু থেকে $m$ ভরের একটি ব্লক স্থির অবস্থা থেকে ছেড়ে দেওয়া হলো। যখন ব্লকটি উল্লম্বভাবে $h$ উচ্চতা নিচে নামে, তখন অনুভূমিক ভরবেগ সংরক্ষণ এবং শক্তির সংরক্ষণশীলতা প্রয়োগ করে কীলকের বেগ $V$ নির্ণয় কর।</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>অনুভূমিক বরাবর বাহ্যিক বল শূন্য হওয়ায় ভরবেগ সংরক্ষিত: $M V - m v_x = 0 \implies v_x = rac{M}{m}V$। কীলকের সাপেক্ষে ব্লকের আপেক্ষিক বেগ ঢাল বরাবর থাকায় কনস্ট্রেইন্ট সম্পর্ক $v_y = (v_x + V)	anlpha = \left(rac{M+m}{m}-ight)V	anlpha$। ব্লকের মোট গতিশক্তি $K_m = rac{1}{2}m(v_x^2 + v_y^2)$ এবং কীলকের গতিশক্তি $K_M = rac{1}{2}MV^2$। শক্তির সংরক্ষণশীলতা: $K_m + K_M = mgh$। সমীকরণগুলো সমাধান করে কীলকের চূড়ান্ত বেগ $V = \sqrt{rac{2m^2 gh\cos^2lpha}{(M+m)(M+m\sin^2lpha)}}$।</t>
+          <t>অনুভূমিক বরাবর বাহ্যিক বল শূন্য হওয়ায় ভরবেগ সংরক্ষিত: $M V - m v_x = 0 \implies v_x = \frac{M}{m}V$। কীলকের সাপেক্ষে ব্লকের আপেক্ষিক বেগ ঢাল বরাবর থাকায় কনস্ট্রেইন্ট সম্পর্ক $v_y = (v_x + V)\tanlpha = \left(\frac{M+m}{m}+ight)V\tanlpha$। ব্লকের মোট গতিশক্তি $K_m = \frac{1}{2}m(v_x^2 + v_y^2)$ এবং কীলকের গতিশক্তি $K_M = \frac{1}{2}MV^2$। শক্তির সংরক্ষণশীলতা: $K_m + K_M = mgh$। সমীকরণগুলো সমাধান করে কীলকের চূড়ান্ত বেগ $V = \sqrt{\frac{2m^2 gh\cos^2\alpha}{(M+m)(M+m\sin^2\alpha)}}$।</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2559,14 +2429,9 @@
           <t>$m$ ভরের একটি কণা $v_0$ বেগে একটি সান্দ্র তরলে প্রবেশ করল যেখানে রোধ বল $F = -kv$। কণাটি সম্পূর্ণ স্থির হওয়ার পূর্ব পর্যন্ত সান্দ্র বল দ্বারা কৃত মোট কাজ কত হবে?</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>কাজ-শক্তি উপপাদ্য অনুসারে যেকোনো বল দ্বারা মোট কৃতকাজ বস্তুর গতিশক্তির পরিবর্তনের সমান: $W_{	ext{viscous}} = \Delta K = K_f - K_i$। কণাটি চূড়ান্তভাবে স্থির হয়, ফলে $K_f = 0$। প্রারম্ভিক গতিশক্তি $K_i = rac{1}{2}m v_0^2$। অতএব সান্দ্র বল দ্বারা কৃত মোট কাজ $W_{	ext{viscous}} = 0 - rac{1}{2}m v_0^2 = -rac{1}{2}m v_0^2$। এই সম্পূর্ণ গতিশক্তি তরলে তাপ শক্তিতে রূপান্তরিত হয়। সান্দ্র গুণাঙ্ক $k$-এর মান যাই হোক না কেন, মোট কৃতকাজ সর্বদা $-rac{1}{2}mv_0^2$ হবে।</t>
+          <t>কাজ-শক্তি উপপাদ্য অনুসারে যেকোনো বল দ্বারা মোট কৃতকাজ বস্তুর গতিশক্তির পরিবর্তনের সমান: $W_{\text{viscous}} = \Delta K = K_f - K_i$। কণাটি চূড়ান্তভাবে স্থির হয়, ফলে $K_f = 0$। প্রারম্ভিক গতিশক্তি $K_i = \frac{1}{2}m v_0^2$। অতএব সান্দ্র বল দ্বারা কৃত মোট কাজ $W_{\text{viscous}} = 0 - \frac{1}{2}m v_0^2 = -\frac{1}{2}m v_0^2$। এই সম্পূর্ণ গতিশক্তি তরলে তাপ শক্তিতে রূপান্তরিত হয়। সান্দ্র গুণাঙ্ক $k$-এর মান যাই হোক না কেন, মোট কৃতকাজ সর্বদা $-\frac{1}{2}mv_0^2$ হবে।</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2606,17 +2471,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>$k_1$ ও $k_2$ স্প্রিং ধ্রুবকের দুটি স্প্রিং-কে (ক) শ্রেণি সমবায়ে এবং (খ) সমান্তরাল সমবায়ে যুক্ত করে উভয় সংস্থাকে একই বাহ্যিক বল $F$ দ্বারা টেনে প্রসারিত করা হলো। উভয় ক্ষেত্রে সঞ্চিত মোট স্থিতিশক্তির অনুপাত $U_{	ext{series}} : U_{	ext{parallel}}$ কত?</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>$k_1$ ও $k_2$ স্প্রিং ধ্রুবকের দুটি স্প্রিং-কে (ক) শ্রেণি সমবায়ে এবং (খ) সমান্তরাল সমবায়ে যুক্ত করে উভয় সংস্থাকে একই বাহ্যিক বল $F$ দ্বারা টেনে প্রসারিত করা হলো। উভয় ক্ষেত্রে সঞ্চিত মোট স্থিতিশক্তির অনুপাত $U_{\text{series}} : U_{\text{parallel}}$ কত?</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>(ক) শ্রেণি সমবায়ে উভয় স্প্রিংয়ের ওপর টান সমান ($F$)। তুল্য স্প্রিং ধ্রুবক $k_s = rac{k_1 k_2}{k_1 + k_2}$। সঞ্চিত শক্তি $U_{	ext{series}} = rac{F^2}{2k_s} = rac{F^2(k_1 + k_2)}{2k_1 k_2}$। (খ) সমান্তরাল সমবায়ে উভয় স্প্রিংয়ের প্রসারণ সমান ($x$) এবং মোট বল $F = (k_1 + k_2)x$। তুল্য স্প্রিং ধ্রুবক $k_p = k_1 + k_2$। সঞ্চিত শক্তি $U_{	ext{parallel}} = rac{F^2}{2k_p} = rac{F^2}{2(k_1 + k_2)}$। শক্তির অনুপাত: $rac{U_{	ext{series}}}{U_{	ext{parallel}}} = rac{rac{F^2(k_1+k_2)}{2k_1 k_2}}{rac{F^2}{2(k_1+k_2)}} = rac{(k_1 + k_2)^2}{k_1 k_2} = rac{k_1}{k_2} + rac{k_2}{k_1} + 2$।</t>
+          <t>(ক) শ্রেণি সমবায়ে উভয় স্প্রিংয়ের ওপর টান সমান ($F$)। তুল্য স্প্রিং ধ্রুবক $k_s = \frac{k_1 k_2}{k_1 + k_2}$। সঞ্চিত শক্তি $U_{\text{series}} = \frac{F^2}{2k_s} = \frac{F^2(k_1 + k_2)}{2k_1 k_2}$। (খ) সমান্তরাল সমবায়ে উভয় স্প্রিংয়ের প্রসারণ সমান ($x$) এবং মোট বল $F = (k_1 + k_2)x$। তুল্য স্প্রিং ধ্রুবক $k_p = k_1 + k_2$। সঞ্চিত শক্তি $U_{\text{parallel}} = \frac{F^2}{2k_p} = \frac{F^2}{2(k_1 + k_2)}$। শক্তির অনুপাত: $\frac{U_{\text{series}}}{U_{\text{parallel}}} = \frac{\frac{F^2(k_1+k_2)}{2k_1 k_2}}{\frac{F^2}{2(k_1+k_2)}} = \frac{(k_1 + k_2)^2}{k_1 k_2} = \frac{k_1}{k_2} + \frac{k_2}{k_1} + 2$।</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2659,20 +2519,15 @@
           <t>$L$ দৈর্ঘ্য, মোট ভর $m_s$ এবং স্প্রিং ধ্রুবক $k$ বিশিষ্ট একটি সুষম উল্লম্ব স্প্রিং ছাদ থেকে মুক্তভাবে ঝুলছে। স্প্রিংটির নিজস্ব ওজনের কারণে এতে মোট কত স্থিতিশক্তি সঞ্চিত হবে?</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>ছাদ থেকে $y$ দূরত্বে নিচের অংশের ভর $m(y) = m_s\left(1 - rac{y}{L}-ight)$। ওই বিন্দুতে টান $T(y) = m(y)g = m_s g\left(1 - rac{y}{L}-ight)$। একক দৈর্ঘ্যের স্প্রিং ধ্রুবক $k L$। $dy$ অংশের প্রসারণ $dx = rac{T(y)dy}{k L}$। $dy$ অংশে সঞ্চিত শক্তি $dU = rac{1}{2}T(y)dx = rac{1}{2}rac{T(y)^2 dy}{k L} = rac{m_s^2 g^2}{2k L}\left(1 - rac{y}{L}-ight)^2 dy$। সমগ্র স্প্রিংয়ের জন্য সমাকলন করি: $U = \int_0^L rac{m_s^2 g^2}{2k L}\left(1 - rac{y}{L}-ight)^2 dy = rac{m_s^2 g^2}{2k L} \left[ -rac{L}{3}\left(1 - rac{y}{L}+          <t>ছাদ থেকে $y$ দূরত্বে নিচের অংশের ভর $m(y) = m_s\left(1 - \frac{y}{L}+ight)$। ওই বিন্দুতে টান $T(y) = m(y)g = m_s g\left(1 - \frac{y}{L}+ight)$। একক দৈর্ঘ্যের স্প্রিং ধ্রুবক $k L$। $dy$ অংশের প্রসারণ $dx = \frac{T(y)dy}{k L}$। $dy$ অংশে সঞ্চিত শক্তি $dU = \frac{1}{2}T(y)dx = \frac{1}{2}\frac{T(y)^2 dy}{k L} = \frac{m_s^2 g^2}{2k L}\left(1 - \frac{y}{L}+ight)^2 dy$। সমগ্র স্প্রিংয়ের জন্য সমাকলন করি: $U = \int_0^L \frac{m_s^2 g^2}{2k L}\left(1 - \frac{y}{L}+ight)^2 dy = \frac{m_s^2 g^2}{2k L} \left[ -\frac{L}{3}\left(1 - \frac{y}{L} ight)^3 -ight]_0^L = rac{m_s^2 g^2}{6k}$।</t>
+ight]_0^L = \frac{m_s^2 g^2}{6k}$।</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2712,17 +2567,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>একটি স্প্রিংয়ের প্রত্যয়নী বল সূত্র $F(x) = -k x + eta x^3$ ($eta &gt; 0$, নরম স্প্রিং)। $m$ ভরের একটি ব্লককে $x_0$ বিস্তার দিয়ে স্পন্দিত করা হলে বিভব শক্তি অপেক্ষক $U(x)$ এবং ব্লকের গতিশক্তি শূন্য হওয়ার শর্ত কী?</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>একটি স্প্রিংয়ের প্রত্যয়নী বল সূত্র $F(x) = -k x + \beta x^3$ ($\beta &gt; 0$, নরম স্প্রিং)। $m$ ভরের একটি ব্লককে $x_0$ বিস্তার দিয়ে স্পন্দিত করা হলে বিভব শক্তি অপেক্ষক $U(x)$ এবং ব্লকের গতিশক্তি শূন্য হওয়ার শর্ত কী?</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>বিভব শক্তি $U(x) = -\int F(x)dx = \int (kx - eta x^3)dx = rac{1}{2}kx^2 - rac{1}{4}eta x^4$ (যেখানে $U(0)=0$)। গতিশক্তি শূন্য হয় সর্বোচ্চ বিস্তারে ($x = \pm x_0$)। মোট শক্তি $E = U(x_0) = rac{1}{2}kx_0^2 - rac{1}{4}eta x_0^4$। লক্ষণীয় যে $eta &gt; 0$ হওয়ার কারণে বিস্তার বৃদ্ধির সাথে সাথে বিভব শক্তি আদর্শ স্প্রিংয়ের চেয়ে ধীরে বৃদ্ধি পায় (নরম স্প্রিং বা Soft Spring), ফলে পর্যায়কাল বিস্তারের সাথে বৃদ্ধি পায়।</t>
+          <t>বিভব শক্তি $U(x) = -\int F(x)dx = \int (kx - \beta x^3)dx = \frac{1}{2}kx^2 - \frac{1}{4}\beta x^4$ (যেখানে $U(0)=0$)। গতিশক্তি শূন্য হয় সর্বোচ্চ বিস্তারে ($x = \pm x_0$)। মোট শক্তি $E = U(x_0) = \frac{1}{2}kx_0^2 - \frac{1}{4}\beta x_0^4$। লক্ষণীয় যে $\beta &gt; 0$ হওয়ার কারণে বিস্তার বৃদ্ধির সাথে সাথে বিভব শক্তি আদর্শ স্প্রিংয়ের চেয়ে ধীরে বৃদ্ধি পায় (নরম স্প্রিং বা Soft Spring), ফলে পর্যায়কাল বিস্তারের সাথে বৃদ্ধি পায়।</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2765,14 +2615,9 @@
           <t>$m$ ভরের একটি ব্লককে একটি হালকা উল্লম্ব স্প্রিংয়ের (ধ্রুবক $k$) স্বাভাবিক মুক্ত প্রান্ত থেকে $h$ উচ্চতা হতে মুক্তভাবে ছেড়ে দেওয়া হলো। স্প্রিংটির সর্বোচ্চ সংকোচন $x_{\max}$ নির্ণয় কর।</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>ব্লকের আদি অবস্থান থেকে সর্বোচ্চ সংকোচন পর্যন্ত মোট উল্লম্ব পতন $h + x_{\max}$। মহাকর্ষীয় বিভব শক্তির হ্রাস স্প্রিংয়ের স্থিতিশক্তিতে রূপান্তরিত হয়: $mg(h + x_{\max}) = rac{1}{2}k x_{\max}^2 \implies rac{1}{2}k x_{\max}^2 - mg x_{\max} - mgh = 0 \implies k x_{\max}^2 - 2mg x_{\max} - 2mgh = 0$। দ্বিঘাত সমীকরণ সমাধান করে ধনাত্মক মূলটি নেওয়া হয়: $x_{\max} = rac{2mg + \sqrt{4m^2 g^2 + 8kmgh}}{2k} = rac{mg}{k}\left(1 + \sqrt{1 + rac{2kh}{mg}}+          <t>ব্লকের আদি অবস্থান থেকে সর্বোচ্চ সংকোচন পর্যন্ত মোট উল্লম্ব পতন $h + x_{\max}$। মহাকর্ষীয় বিভব শক্তির হ্রাস স্প্রিংয়ের স্থিতিশক্তিতে রূপান্তরিত হয়: $mg(h + x_{\max}) = \frac{1}{2}k x_{\max}^2 \implies \frac{1}{2}k x_{\max}^2 - mg x_{\max} - mgh = 0 \implies k x_{\max}^2 - 2mg x_{\max} - 2mgh = 0$। দ্বিঘাত সমীকরণ সমাধান করে ধনাত্মক মূলটি নেওয়া হয়: $x_{\max} = \frac{2mg + \sqrt{4m^2 g^2 + 8kmgh}}{2k} = \frac{mg}{k}\left(1 + \sqrt{1 + \frac{2kh}{mg}} ight)$।</t>
         </is>
       </c>
@@ -2824,7 +2669,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>স্প্রিং ধ্রুবক দৈর্ঘ্যের ব্যস্তানুপাতিক: $k \propto rac{1}{L}$। আদি দৈর্ঘ্য $L = L_1 + L_2$ যেখানে $L_1 = rac{L}{3}$ এবং $L_2 = rac{2L}{3}$। সুতরাং প্রথম খণ্ডের স্প্রিং ধ্রুবক $k_1 = 3k$ এবং দ্বিতীয় খণ্ডের $k_2 = rac{3}{2}k$। একই প্রসারণ $x_0$-এর জন্য সঞ্চিত শক্তি $U = rac{1}{2}k' x_0^2 \propto k'$। অতএব শক্তির অনুপাত $rac{U_1}{U_2} = rac{k_1}{k_2} = rac{3k}{rac{3}{2}k} = rac{2}{1} = 2:1$। ছোট খণ্ডটিতে দ্বিগুণ শক্তি সঞ্চিত হবে।</t>
+          <t>স্প্রিং ধ্রুবক দৈর্ঘ্যের ব্যস্তানুপাতিক: $k \propto \frac{1}{L}$। আদি দৈর্ঘ্য $L = L_1 + L_2$ যেখানে $L_1 = \frac{L}{3}$ এবং $L_2 = \frac{2L}{3}$। সুতরাং প্রথম খণ্ডের স্প্রিং ধ্রুবক $k_1 = 3k$ এবং দ্বিতীয় খণ্ডের $k_2 = \frac{3}{2}k$। একই প্রসারণ $x_0$-এর জন্য সঞ্চিত শক্তি $U = \frac{1}{2}k' x_0^2 \propto k'$। অতএব শক্তির অনুপাত $\frac{U_1}{U_2} = \frac{k_1}{k_2} = \frac{3k}{\frac{3}{2}k} = \frac{2}{1} = 2:1$। ছোট খণ্ডটিতে দ্বিগুণ শক্তি সঞ্চিত হবে।</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2867,14 +2712,9 @@
           <t>একটি মসৃণ অনুভূমিক মেঝের মূলবিন্দু $(0,0)$-তে একটি স্প্রিংয়ের এক প্রান্ত আটকানো যার স্বাভাবিক অপ্রসারিত দৈর্ঘ্য $L_0$ এবং ধ্রুবক $k$। অপর প্রান্তে বাঁধা একটি বস্তুকে $(L_0, 0)$ বিন্দু থেকে সোজা উল্লম্ব রেখা বরাবর $(L_0, y)$ বিন্দুতে সরাতে বাহ্যিক বলের কৃতকাজ কত?</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>চূড়ান্ত অবস্থানে স্প্রিংয়ের মোট দৈর্ঘ্য $L = \sqrt{L_0^2 + y^2}$। স্প্রিংয়ের মোট প্রসারণ $\Delta L = L - L_0 = \sqrt{L_0^2 + y^2} - L_0$। যেহেতু স্প্রিং বল একটি সংরক্ষণশীল বল, সেহেতু সরণের পথ যাই হোক না কেন, কৃতকাজ কেবল প্রারম্ভিক ও চূড়ান্ত বিভব শক্তির পার্থক্যের সমান: $W = U_f - U_i = rac{1}{2}k (\Delta L)^2 - 0 = rac{1}{2}k \left(\sqrt{L_0^2 + y^2} - L_0+          <t>চূড়ান্ত অবস্থানে স্প্রিংয়ের মোট দৈর্ঘ্য $L = \sqrt{L_0^2 + y^2}$। স্প্রিংয়ের মোট প্রসারণ $\Delta L = L - L_0 = \sqrt{L_0^2 + y^2} - L_0$। যেহেতু স্প্রিং বল একটি সংরক্ষণশীল বল, সেহেতু সরণের পথ যাই হোক না কেন, কৃতকাজ কেবল প্রারম্ভিক ও চূড়ান্ত বিভব শক্তির পার্থক্যের সমান: $W = U_f - U_i = \frac{1}{2}k (\Delta L)^2 - 0 = \frac{1}{2}k \left(\sqrt{L_0^2 + y^2} - L_0 ight)^2$।</t>
         </is>
       </c>
@@ -2918,15 +2758,10 @@
           <t>মেঝের ওপর $M$ ভরের একটি ব্লক রাখা যার ওপর $k$ স্প্রিং ধ্রুবকের একটি উল্লম্ব স্প্রিং আটকানো। স্প্রিংয়ের শীর্ষে $m$ ভরের অপর একটি ব্লক যুক্ত। সাম্যাবস্থায় $m$ ব্লকটিকে আরও $x_0$ পরিমাণ নিচের দিকে চেপে হঠাৎ ছেড়ে দেওয়া হলো। $x_0$-এর মান ন্যূনতম কত হলে নিচের ব্লক $M$ মাটি থেকে সামান্য ওপরে উঠে যাবে?</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>সাম্যাবস্থায় স্প্রিংয়ের সংকোচন $x_e = rac{mg}{k}$। সাম্যাবস্থা থেকে আরও $x_0$ চেপে ছাড়লে ঊর্ধ্বমুখী প্রত্যাবর্তনের সময় সাম্যাবস্থা থেকে ওপরে সর্বোচ্চ প্রসারণ হবে $x_0$। এই অবস্থানে স্প্রিংয়ের স্বাভাবিক দৈর্ঘ্যের সাপেক্ষে নেট প্রসারণ $x_{	ext{net}} = x_0 - x_e = x_0 - rac{mg}{k}$। এই অবস্থায় স্প্রিং কর্তৃক নিচের ব্লকের ওপর ঊর্ধ্বমুখী টান $T = k x_{	ext{net}} = k\left(x_0 - rac{mg}{k}-ight) = k x_0 - mg$। নিচের ব্লকটি মাটি ত্যাগ করার শর্ত $T \ge Mg \implies k x_0 - mg \ge Mg \implies k x_0 \ge (M + m)g \implies x_0 \ge rac{(M + m)g}{k}$।</t>
+          <t>সাম্যাবস্থায় স্প্রিংয়ের সংকোচন $x_e = \frac{mg}{k}$। সাম্যাবস্থা থেকে আরও $x_0$ চেপে ছাড়লে ঊর্ধ্বমুখী প্রত্যাবর্তনের সময় সাম্যাবস্থা থেকে ওপরে সর্বোচ্চ প্রসারণ হবে $x_0$। এই অবস্থানে স্প্রিংয়ের স্বাভাবিক দৈর্ঘ্যের সাপেক্ষে নেট প্রসারণ $x_{\text{net}} = x_0 - x_e = x_0 - \frac{mg}{k}$। এই অবস্থায় স্প্রিং কর্তৃক নিচের ব্লকের ওপর ঊর্ধ্বমুখী টান $T = k x_{\text{net}} = k\left(x_0 - \frac{mg}{k}+ight) = k x_0 - mg$। নিচের ব্লকটি মাটি ত্যাগ করার শর্ত $T \ge Mg \implies k x_0 - mg \ge Mg \implies k x_0 \ge (M + m)g \implies x_0 \ge \frac{(M + m)g}{k}$।</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2969,14 +2804,9 @@
           <t>একটি উল্লম্ব স্প্রিং গানের স্প্রিং ধ্রুবক $k$। স্প্রিংটিকে $x$ পরিমাণ সংকুচিত করে তার ওপর $m$ ভরের একটি বল রেখে ট্রিগার টেপা হলো। বলটি সংকোচনের অবস্থান থেকে মোট কত সর্বোচ্চ উচ্চতা $H$ অর্জন করবে?</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>সংকোচনের সর্বনিম্ন বিন্দুকে শূন্য বিভব শক্তি স্তর ধরি। প্রারম্ভিক শক্তি কেবল স্প্রিংয়ের স্থিতিশক্তি: $E_i = rac{1}{2}k x^2$। সর্বোচ্চ বিন্দুতে বলটি সাময়িকভাবে স্থির হয়, ফলে গতিশক্তি শূন্য এবং সম্পূর্ণ শক্তি মহাকর্ষীয় বিভব শক্তিতে রূপান্তরিত হয়: $E_f = mg H$। শক্তির সংরক্ষণশীলতা: $rac{1}{2}k x^2 = mg H \implies H = rac{k x^2}{2mg}$। লক্ষণীয় যে এই উচ্চতা $H$ স্প্রিংয়ের সংকুচিত আদি অবস্থান থেকে পরিমাপ করা। স্বাভাবিক অবস্থান থেকে উচ্চতা হবে $H - x = rac{kx^2}{2mg} - x$।</t>
+          <t>সংকোচনের সর্বনিম্ন বিন্দুকে শূন্য বিভব শক্তি স্তর ধরি। প্রারম্ভিক শক্তি কেবল স্প্রিংয়ের স্থিতিশক্তি: $E_i = \frac{1}{2}k x^2$। সর্বোচ্চ বিন্দুতে বলটি সাময়িকভাবে স্থির হয়, ফলে গতিশক্তি শূন্য এবং সম্পূর্ণ শক্তি মহাকর্ষীয় বিভব শক্তিতে রূপান্তরিত হয়: $E_f = mg H$। শক্তির সংরক্ষণশীলতা: $\frac{1}{2}k x^2 = mg H \implies H = \frac{k x^2}{2mg}$। লক্ষণীয় যে এই উচ্চতা $H$ স্প্রিংয়ের সংকুচিত আদি অবস্থান থেকে পরিমাপ করা। স্বাভাবিক অবস্থান থেকে উচ্চতা হবে $H - x = \frac{kx^2}{2mg} - x$।</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3019,17 +2849,12 @@
           <t>একটি কণা $m$ দুটি সমান স্প্রিংয়ের (প্রতিটির দৈর্ঘ্য $L_0$ এবং ধ্রুবক $k$) মাঝে দৃঢ়ভাবে সংযুক্ত যাদের অপর প্রান্তদ্বয় $2L_0$ দূরত্বের দুটি স্থির দেয়ালে আটকানো। কণাটিকে স্প্রিংদ্বয়ের অক্ষের সাথে লম্ব দিকে ক্ষুদ্র $y$ ($y \ll L_0$) সরণ ঘটালে বিভব শক্তির চতুর্থ ঘাত নির্ভরতা ও কৃতকাজ নির্ণয় কর।</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>লম্ব সরণ $y$-এর জন্য প্রতিটি স্প্রিংয়ের নতুন দৈর্ঘ্য $L = \sqrt{L_0^2 + y^2} = L_0\sqrt{1 + y^2/L_0^2} pprox L_0\left(1 + rac{y^2}{2L_0^2} - rac{y^4}{8L_0^4}-ight)$। প্রসারণ $\Delta L = L - L_0 pprox rac{y^2}{2L_0}$। দুটি স্প্রিংয়ের মোট সঞ্চিত স্থিতিশক্তি $U = 2 	imes \left[rac{1}{2}k(\Delta L)^2-ight] = k \left(rac{y^2}{2L_0}-ight)^2 = rac{k y^4}{4L_0^2}$। প্রত্যয়নী বল $F = -rac{dU}{dy} = -rac{k y^3}{L_0^2}$। এটি সম্পূর্ণ অরৈখিক (Cubic force) এবং কোনো রৈখিক প্রত্যয়নী বল নেই।</t>
+          <t>লম্ব সরণ $y$-এর জন্য প্রতিটি স্প্রিংয়ের নতুন দৈর্ঘ্য $L = \sqrt{L_0^2 + y^2} = L_0\sqrt{1 + y^2/L_0^2} pprox L_0\left(1 + \frac{y^2}{2L_0^2} - \frac{y^4}{8L_0^4}+ight)$। প্রসারণ $\Delta L = L - L_0 pprox \frac{y^2}{2L_0}$। দুটি স্প্রিংয়ের মোট সঞ্চিত স্থিতিশক্তি $U = 2 \times \left[\frac{1}{2}k(\Delta L)^2+ight] = k \left(\frac{y^2}{2L_0}+ight)^2 = \frac{k y^4}{4L_0^2}$। প্রত্যয়নী বল $F = -\frac{dU}{dy} = -\frac{k y^3}{L_0^2}$। এটি সম্পূর্ণ অরৈখিক (Cubic force) এবং কোনো রৈখিক প্রত্যয়নী বল নেই।</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3072,16 +2897,11 @@
           <t>একটি ব্লককে একটি স্প্রিং ($k$) এবং একটি ভিসকাস ড্যাম্পার ($b$) দ্বারা যুক্ত করে বাইরে থেকে ধ্রুব বল $F_0$ দিয়ে টানা হলো। ব্লকটি যখন নতুন সাম্যাবস্থানে পৌঁছায়, তখন বাহ্যিক বল দ্বারা কৃত মোট কাজের কত শতাংশ স্প্রিংয়ে জমা হয় এবং কত শতাংশ ড্যাম্পারে নষ্ট হয়?</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>নতুন সাম্যাবস্থানে ব্লকের প্রসারণ $x_0 = rac{F_0}{k}$। বাহ্যিক ধ্রুব বল $F_0$ দ্বারা কৃত মোট কাজ $W_{	ext{ext}} = F_0 x_0 = F_0 \left(rac{F_0}{k}-ight) = rac{F_0^2}{k}$। নতুন সাম্যাবস্থানে স্প্রিংয়ে সঞ্চিত স্থিতিশক্তি $U_{	ext{spring}} = rac{1}{2}k x_0^2 = rac{1}{2}k\left(rac{F_0}{k}-ight)^2 = rac{F_0^2}{2k}$। কাজ-শক্তি উপপাদ্য অনুসারে বাকি শক্তি ড্যাম্পার দ্বারা তাপে অপচয় হয়: $Q_{	ext{dissipated}} = W_{	ext{ext}} - U_{	ext{spring}} = rac{F_0^2}{k} - rac{F_0^2}{2k} = rac{F_0^2}{2k}$। অতএব সরবরাহকৃত মোট শক্তির ঠিক ৫০% স্প্রিংয়ে জমা হয় এবং ৫০% তাপে নষ্ট হয়।</t>
+          <t>নতুন সাম্যাবস্থানে ব্লকের প্রসারণ $x_0 = \frac{F_0}{k}$। বাহ্যিক ধ্রুব বল $F_0$ দ্বারা কৃত মোট কাজ $W_{\text{ext}} = F_0 x_0 = F_0 \left(\frac{F_0}{k}+ight) = \frac{F_0^2}{k}$। নতুন সাম্যাবস্থানে স্প্রিংয়ে সঞ্চিত স্থিতিশক্তি $U_{\text{spring}} = \frac{1}{2}k x_0^2 = \frac{1}{2}k\left(\frac{F_0}{k}+ight)^2 = \frac{F_0^2}{2k}$। কাজ-শক্তি উপপাদ্য অনুসারে বাকি শক্তি ড্যাম্পার দ্বারা তাপে অপচয় হয়: $Q_{\text{dissipated}} = W_{\text{ext}} - U_{\text{spring}} = \frac{F_0^2}{k} - \frac{F_0^2}{2k} = \frac{F_0^2}{2k}$। অতএব সরবরাহকৃত মোট শক্তির ঠিক ৫০% স্প্রিংয়ে জমা হয় এবং ৫০% তাপে নষ্ট হয়।</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3124,14 +2944,9 @@
           <t>একটি ঘর্ষণহীন ট্র্যাকের অংশ হিসেবে $R$ ব্যাসার্ধের একটি উল্লম্ব বৃত্তাকার লুপ বিদ্যমান। একটি কণা লুপের প্রবেশের পূর্বে একটি ঢালু ট্র্যাক দিয়ে $h$ উচ্চতা থেকে স্থির অবস্থা থেকে মুক্তভাবে ছেড়ে দেওয়া হলো। লুপটি সম্পূর্ণ সফলভাবে অতিক্রম করতে $h$-এর ন্যূনতম মান কত হতে হবে?</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>লুপের সর্বোচ্চ বিন্দুতে কণাটির বেগ ন্যূনতম $v_{	ext{top}} \ge \sqrt{gR}$ হতে হবে যাতে অভিলম্ব বল $N \ge 0$ থাকে। সর্বোচ্চ বিন্দুর উচ্চতা লুপের প্রবেশদ্বার বা সর্বনিম্ন বিন্দু থেকে $2R$। প্রারম্ভিক অবস্থায় গতিশক্তি শূন্য এবং মহাকর্ষীয় বিভব শক্তি $mgh$। সর্বোচ্চ বিন্দুতে শক্তি $E = mg(2R) + rac{1}{2}m v_{	ext{top}}^2$। শক্তির সংরক্ষণশীলতা অনুসারে: $mgh = mg(2R) + rac{1}{2}m(gR) = 2mgR + rac{1}{2}mgR = rac{5}{2}mgR \implies h_{\min} = rac{5}{2}R = 2.5R$।</t>
+          <t>লুপের সর্বোচ্চ বিন্দুতে কণাটির বেগ ন্যূনতম $v_{\text{top}} \ge \sqrt{gR}$ হতে হবে যাতে অভিলম্ব বল $N \ge 0$ থাকে। সর্বোচ্চ বিন্দুর উচ্চতা লুপের প্রবেশদ্বার বা সর্বনিম্ন বিন্দু থেকে $2R$। প্রারম্ভিক অবস্থায় গতিশক্তি শূন্য এবং মহাকর্ষীয় বিভব শক্তি $mgh$। সর্বোচ্চ বিন্দুতে শক্তি $E = mg(2R) + \frac{1}{2}m v_{\text{top}}^2$। শক্তির সংরক্ষণশীলতা অনুসারে: $mgh = mg(2R) + \frac{1}{2}m(gR) = 2mgR + \frac{1}{2}mgR = \frac{5}{2}mgR \implies h_{\min} = \frac{5}{2}R = 2.5R$।</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3174,14 +2989,9 @@
           <t>$R$ ব্যাসার্ধের একটি মসৃণ স্থির অর্ধগোলকের শীর্ষবিন্দু থেকে একটি কণা সামান্যতম বিচ্যুতির পর পিছলে নামতে শুরু করল। কণাটি বিচ্ছিন্ন হওয়ার বিন্দুতে তার গতিশক্তি এবং হারানো মহাকর্ষীয় বিভব শক্তির অনুপাত কত?</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>শীর্ষবিন্দু থেকে $	heta$ কোণে নামলে গতিবেগ $v^2 = 2gR(1 - \cos	heta)$। অভিলম্ব বল $N = mg\cos	heta - rac{mv^2}{R} = mg(3\cos	heta - 2)$। বিচ্ছিন্ন হওয়ার শর্ত $N = 0 \implies \cos	heta = rac{2}{3}$। বিচ্ছিন্ন মুহূর্তে উল্লম্ব উচ্চতা হ্রাস $h = R(1 - \cos	heta) = R(1 - 2/3) = rac{R}{3}$। ফলে হারানো মহাকর্ষীয় বিভব শক্তি $\Delta U = mgh = rac{1}{3}mgR$। অর্জিত গতিশক্তি $K = rac{1}{2}m v^2 = rac{1}{2}m [2gR(1 - 2/3)] = rac{1}{3}mgR$। যেহেতু কোনো ঘর্ষণ নেই, সেহেতু হারানো বিভব শক্তি হুবহু গতিশক্তিতে রূপান্তরিত হয়, ফলে তাদের অনুপাত $1:1$।</t>
+          <t>শীর্ষবিন্দু থেকে $\theta$ কোণে নামলে গতিবেগ $v^2 = 2gR(1 - \cos\theta)$। অভিলম্ব বল $N = mg\cos\theta - \frac{mv^2}{R} = mg(3\cos\theta - 2)$। বিচ্ছিন্ন হওয়ার শর্ত $N = 0 \implies \cos\theta = \frac{2}{3}$। বিচ্ছিন্ন মুহূর্তে উল্লম্ব উচ্চতা হ্রাস $h = R(1 - \cos\theta) = R(1 - 2/3) = \frac{R}{3}$। ফলে হারানো মহাকর্ষীয় বিভব শক্তি $\Delta U = mgh = \frac{1}{3}mgR$। অর্জিত গতিশক্তি $K = \frac{1}{2}m v^2 = \frac{1}{2}m [2gR(1 - 2/3)] = \frac{1}{3}mgR$। যেহেতু কোনো ঘর্ষণ নেই, সেহেতু হারানো বিভব শক্তি হুবহু গতিশক্তিতে রূপান্তরিত হয়, ফলে তাদের অনুপাত $1:1$।</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3269,17 +3079,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>$L$ দৈর্ঘ্যের সুতায় বাঁধা একটি বস্তুকে উলম্ব বৃত্তাকার পথে পূর্ণ ঘূর্ণন সম্পন্ন করতে সর্বনিম্ন বিন্দুতে বেগ $u = \sqrt{6gL}$ দেওয়া হলো। বৃত্তের সর্বনিম্ন ও সর্বোচ্চ বিন্দুতে সুতার টানের অনুপাত $T_{	ext{bottom}} : T_{	ext{top}}$ কত?</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>$L$ দৈর্ঘ্যের সুতায় বাঁধা একটি বস্তুকে উলম্ব বৃত্তাকার পথে পূর্ণ ঘূর্ণন সম্পন্ন করতে সর্বনিম্ন বিন্দুতে বেগ $u = \sqrt{6gL}$ দেওয়া হলো। বৃত্তের সর্বনিম্ন ও সর্বোচ্চ বিন্দুতে সুতার টানের অনুপাত $T_{\text{bottom}} : T_{\text{top}}$ কত?</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>সর্বনিম্ন বিন্দুতে টান $T_{	ext{bottom}} = mg + rac{mu^2}{L} = mg + rac{m(6gL)}{L} = 7mg$। সর্বোচ্চ বিন্দুতে বেগ $v^2 = u^2 - 4gL = 6gL - 4gL = 2gL$। সর্বোচ্চ বিন্দুতে টান $T_{	ext{top}} = rac{mv^2}{L} - mg = rac{m(2gL)}{L} - mg = 2mg - mg = mg$। অতএব টানের অনুপাত $rac{T_{	ext{bottom}}}{T_{	ext{top}}} = rac{7mg}{mg} = 7:1$। লক্ষণীয় যে যেকোনো উলম্ব বৃত্তাকার গতিতে $T_{	ext{bottom}} - T_{	ext{top}} = 6mg$ সর্বদা একটি সার্বজনীন ধ্রুবক।</t>
+          <t>সর্বনিম্ন বিন্দুতে টান $T_{\text{bottom}} = mg + \frac{mu^2}{L} = mg + \frac{m(6gL)}{L} = 7mg$। সর্বোচ্চ বিন্দুতে বেগ $v^2 = u^2 - 4gL = 6gL - 4gL = 2gL$। সর্বোচ্চ বিন্দুতে টান $T_{\text{top}} = \frac{mv^2}{L} - mg = \frac{m(2gL)}{L} - mg = 2mg - mg = mg$। অতএব টানের অনুপাত $\frac{T_{\text{bottom}}}{T_{\text{top}}} = \frac{7mg}{mg} = 7:1$। লক্ষণীয় যে যেকোনো উলম্ব বৃত্তাকার গতিতে $T_{\text{bottom}} - T_{\text{top}} = 6mg$ সর্বদা একটি সার্বজনীন ধ্রুবক।</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3319,20 +3124,15 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>একটি মসৃণ ট্র্যাক উলম্ব তলে $y = rac{x^2}{4a}$ পরাবৃত্তাকার সমীকরণ মেনে চলে। একটি কণা $H$ উচ্চতা থেকে স্থির অবস্থা থেকে পিছলে নামলে সর্বনিম্ন বিন্দুতে ট্র্যাক কর্তৃক কণার ওপর অভিলম্ব বল কত?</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>একটি মসৃণ ট্র্যাক উলম্ব তলে $y = \frac{x^2}{4a}$ পরাবৃত্তাকার সমীকরণ মেনে চলে। একটি কণা $H$ উচ্চতা থেকে স্থির অবস্থা থেকে পিছলে নামলে সর্বনিম্ন বিন্দুতে ট্র্যাক কর্তৃক কণার ওপর অভিলম্ব বল কত?</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
           <t>সর্বনিম্ন বিন্দুতে ($x=0, y=0$) পরাবৃত্তের বক্রতা ব্যাসার্ধ $-ho = 2a$। সর্বনিম্ন বিন্দুতে কণার বেগ $v = \sqrt{2gH}$। ওই বিন্দুতে ত্বরণ কেবলমাত্র কেন্দ্রমুখী ত্বরণ: $a_c = rac{v^2}{-ho} = rac{2gH}{2a} = rac{gH}{a}$। নিউটনের দ্বিতীয় সূত্রানুসারে উলম্ব অভিলম্ব বল: $N - mg = m a_c = m\left(rac{gH}{a}-ight) \implies N = mg\left(1 + rac{H}{a}+ho = 2a$। সর্বনিম্ন বিন্দুতে কণার বেগ $v = \sqrt{2gH}$। ওই বিন্দুতে ত্বরণ কেবলমাত্র কেন্দ্রমুখী ত্বরণ: $a_c = \frac{v^2}{+ho} = \frac{2gH}{2a} = \frac{gH}{a}$। নিউটনের দ্বিতীয় সূত্রানুসারে উলম্ব অভিলম্ব বল: $N - mg = m a_c = m\left(\frac{gH}{a}+ight) \implies N = mg\left(1 + \frac{H}{a} ight)$।</t>
         </is>
       </c>
@@ -3376,11 +3176,6 @@
           <t>উল্লম্ব বৃত্তাকার গতিতে ঘূর্ণায়মান একটি বস্তুর ওপর কেন্দ্রমুখী বল দ্বারা যেকোনো সসীম পথ বরাবর কৃতকাজ কত এবং কেন?</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I47" t="inlineStr">
         <is>
           <t>কেন্দ্রমুখী বল $ec{F}_c$ সর্বদা তাৎক্ষণিক গতিপথের কেন্দ্রাভিমুখী (রেডিয়াল বরাবর)। কিন্তু বস্তুর তাৎক্ষণিক সরণ ভেক্টর $dec{r}$ সর্বদা স্পর্শক বরাবর। যেহেতু স্পর্শক ও ব্যাসার্ধ পরস্পরের সাথে লম্ব, সেহেতু $ec{F}_c \cdot dec{r} = F_c dr \cos 90^\circ = 0$। ফলে কেন্দ্রমুখী বলের তাৎক্ষণিক ক্ষমতা $P = ec{F}_c\cdotec{v} = 0$ এবং যেকোনো পথ বরাবর এর দ্বারা কৃতকাজ সর্বদা শূন্য। কেন্দ্রমুখী বল কেবল বেগের দিক পরিবর্তন করে কিন্তু দ্রুতি বা গতিশক্তির কোনো পরিবর্তন করতে পারে না।</t>
@@ -3426,14 +3221,9 @@
           <t>দুটি সমান দৈর্ঘ্য $L$ এবং সমান ভর $m$-এর কণা দ্বারা গঠিত একটি দ্বি-পেন্ডুলাম উল্লম্ব তলে দুলছে। ক্ষুদ্র কোণে দোলনের ক্ষেত্রে সংস্থার মোট শক্তির সমীকরণ গঠন কর এবং গতিশক্তি ও স্থিতিশক্তির কাপলিং বিশ্লেষণ কর।</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>প্রথম ববের অবস্থান $(x_1, y_1) = (L\sin	heta_1, -L\cos	heta_1)$ এবং দ্বিতীয় ববের অবস্থান $(x_2, y_2) = (L\sin	heta_1 + L\sin	heta_2, -L\cos	heta_1 - L\cos	heta_2)$। ক্ষুদ্র কোণে $\sin	heta pprox 	heta$ এবং $\cos	heta pprox 1 - 	heta^2/2$। বিভব শক্তি $U pprox rac{1}{2}mgL(2	heta_1^2 + 	heta_2^2)$। গতিশক্তি $K = rac{1}{2}m L^2 [2\dot{	heta}_1^2 + \dot{	heta}_2^2 + 2\dot{	heta}_1\dot{	heta}_2\cos(	heta_1 - 	heta_2)]$। এখানে ক্রস টার্ম $2\dot{	heta}_1\dot{	heta}_2$ গতিশক্তিতে অ-রৈখিক কাপলিং সৃষ্টি করে, যার ফলে বড় বিস্তারে গতিশক্তি অত্যন্ত সংবেদনশীলভাবে স্থানান্তরিত হয়ে বিশৃঙ্খল (Chaotic) গতির জন্ম দেয়।</t>
+          <t>প্রথম ববের অবস্থান $(x_1, y_1) = (L\sin\theta_1, -L\cos\theta_1)$ এবং দ্বিতীয় ববের অবস্থান $(x_2, y_2) = (L\sin\theta_1 + L\sin\theta_2, -L\cos\theta_1 - L\cos\theta_2)$। ক্ষুদ্র কোণে $\sin\theta pprox \theta$ এবং $\cos\theta pprox 1 - \theta^2/2$। বিভব শক্তি $U pprox \frac{1}{2}mgL(2\theta_1^2 + \theta_2^2)$। গতিশক্তি $K = \frac{1}{2}m L^2 [2\dot{\theta}_1^2 + \dot{\theta}_2^2 + 2\dot{\theta}_1\dot{\theta}_2\cos(\theta_1 - \theta_2)]$। এখানে ক্রস টার্ম $2\dot{\theta}_1\dot{\theta}_2$ গতিশক্তিতে অ-রৈখিক কাপলিং সৃষ্টি করে, যার ফলে বড় বিস্তারে গতিশক্তি অত্যন্ত সংবেদনশীলভাবে স্থানান্তরিত হয়ে বিশৃঙ্খল (Chaotic) গতির জন্ম দেয়।</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3473,17 +3263,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>একটি হালকা স্প্রিংয়ের (ধ্রুবক $k$, স্বাভাবিক দৈর্ঘ্য $L_0$) প্রান্তে $m$ ভরের একটি বব উল্লম্ব তলে দুলছে। উল্লম্ব প্রসারণের কম্পাঙ্ক $\omega_z = \sqrt{k/m}$ এবং পেন্ডুলাম দোলনের কম্পাঙ্ক $\omega_	heta = \sqrt{g/L_{	ext{eq}}}$। $\omega_z pprox 2\omega_	heta$ হলে শক্তির বিনিময় কীভাবে ঘটে?</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>একটি হালকা স্প্রিংয়ের (ধ্রুবক $k$, স্বাভাবিক দৈর্ঘ্য $L_0$) প্রান্তে $m$ ভরের একটি বব উল্লম্ব তলে দুলছে। উল্লম্ব প্রসারণের কম্পাঙ্ক $\omega_z = \sqrt{k/m}$ এবং পেন্ডুলাম দোলনের কম্পাঙ্ক $\omega_\theta = \sqrt{g/L_{\text{eq}}}$। $\omega_z pprox 2\omega_\theta$ হলে শক্তির বিনিময় কীভাবে ঘটে?</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>যখন স্প্রিং-পেন্ডুলাম ব্যবস্থায় স্প্রিং কম্পাঙ্ক পেন্ডুলাম কম্পাঙ্কের দ্বিগুণ হয় ($\omega_z pprox 2\omega_	heta$), তখন এটিকে অটো-প্যারামেট্রিক রেজোন্যান্স (Autoparametric Resonance) বলা হয়। এই বিশেষ শর্তে উল্লম্ব স্প্রিং দোলনের শক্তি সম্পূর্ণভাবে পাশ্বীয় পেন্ডুলাম দোলনে স্থানান্তরিত হয়, আবার কিছুক্ষণ পর পেন্ডুলামের শক্তি সম্পূর্ণভাবে স্প্রিং দোলনে ফিরে আসে। এই চক্রাকার শক্তি বিনিময় নন-লিনিয়ার কাপলিং পদের কারণে ঘটে।</t>
+          <t>যখন স্প্রিং-পেন্ডুলাম ব্যবস্থায় স্প্রিং কম্পাঙ্ক পেন্ডুলাম কম্পাঙ্কের দ্বিগুণ হয় ($\omega_z pprox 2\omega_\theta$), তখন এটিকে অটো-প্যারামেট্রিক রেজোন্যান্স (Autoparametric Resonance) বলা হয়। এই বিশেষ শর্তে উল্লম্ব স্প্রিং দোলনের শক্তি সম্পূর্ণভাবে পাশ্বীয় পেন্ডুলাম দোলনে স্থানান্তরিত হয়, আবার কিছুক্ষণ পর পেন্ডুলামের শক্তি সম্পূর্ণভাবে স্প্রিং দোলনে ফিরে আসে। এই চক্রাকার শক্তি বিনিময় নন-লিনিয়ার কাপলিং পদের কারণে ঘটে।</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3523,17 +3308,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>একটি উলম্ব সাইক্লয়েড ট্র্যাকে কণার বিভব শক্তি চাপ দৈর্ঘ্য $s$-এর বর্গের সমানুপাতিক ($U(s) = rac{1}{2}k_{	ext{eff}} s^2$)। প্রমাণ কর যে যে কোনো উচ্চতা থেকে ছেড়ে দিলে সাম্যাবস্থায় পৌঁছানোর সময় গতিশক্তির শীর্ষ মান প্রাথমিক বিভব শক্তির সমান হয় কিন্তু সময় সম্পূর্ণ নিরপেক্ষ থাকে।</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>একটি উলম্ব সাইক্লয়েড ট্র্যাকে কণার বিভব শক্তি চাপ দৈর্ঘ্য $s$-এর বর্গের সমানুপাতিক ($U(s) = \frac{1}{2}k_{\text{eff}} s^2$)। প্রমাণ কর যে যে কোনো উচ্চতা থেকে ছেড়ে দিলে সাম্যাবস্থায় পৌঁছানোর সময় গতিশক্তির শীর্ষ মান প্রাথমিক বিভব শক্তির সমান হয় কিন্তু সময় সম্পূর্ণ নিরপেক্ষ থাকে।</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>সাইক্লয়েডের প্রাকৃতিক সমীকরণ অনুসারে উল্লম্ব উচ্চতা $y = rac{s^2}{8R}$। বিভব শক্তি $U(s) = mgy = rac{mg}{8R}s^2 = rac{1}{2}k_{	ext{eff}} s^2$, যেখানে $k_{	ext{eff}} = rac{mg}{4R}$ ধ্রুবক। এটি নিখুঁত সরল ছন্দিত স্পন্দনের বিভব শক্তি নির্দেশ করে। শক্তির সংরক্ষণশীলতায় $K_{\max} = U(s_0) = rac{mg}{8R}s_0^2$। কৌণিক কম্পাঙ্ক $\omega = \sqrt{rac{k_{	ext{eff}}}{m}} = \sqrt{rac{g}{4R}}$। সাম্যাবস্থায় পৌঁছানোর সময় $t = rac{\pi}{2\omega} = \pi\sqrt{rac{R}{g}}$, যা প্রাথমিক বিস্তার $s_0$-এর ওপর সম্পূর্ণরূপে নিরপেক্ষ।</t>
+          <t>সাইক্লয়েডের প্রাকৃতিক সমীকরণ অনুসারে উল্লম্ব উচ্চতা $y = \frac{s^2}{8R}$। বিভব শক্তি $U(s) = mgy = \frac{mg}{8R}s^2 = \frac{1}{2}k_{\text{eff}} s^2$, যেখানে $k_{\text{eff}} = \frac{mg}{4R}$ ধ্রুবক। এটি নিখুঁত সরল ছন্দিত স্পন্দনের বিভব শক্তি নির্দেশ করে। শক্তির সংরক্ষণশীলতায় $K_{\max} = U(s_0) = \frac{mg}{8R}s_0^2$। কৌণিক কম্পাঙ্ক $\omega = \sqrt{\frac{k_{\text{eff}}}{m}} = \sqrt{\frac{g}{4R}}$। সাম্যাবস্থায় পৌঁছানোর সময় $t = \frac{\pi}{2\omega} = \pi\sqrt{\frac{R}{g}}$, যা প্রাথমিক বিস্তার $s_0$-এর ওপর সম্পূর্ণরূপে নিরপেক্ষ।</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3576,14 +3356,9 @@
           <t>একটি অনুভূমিক মসৃণ সোজা নল উল্লম্ব অক্ষের সাপেক্ষে ধ্রুব কৌণিক বেগ $\omega$ নিয়ে ঘুরছে। নলের ভেতর $m$ ভরের একটি কণা কেন্দ্র থেকে $r_0$ দূরত্ব থেকে স্থির অবস্থা থেকে যাত্রা শুরু করে $R$ দূরত্বে নলের মুখ দিয়ে নির্গত হয়। নির্গমনের মুহূর্তে কণার লব্ধি গতিশক্তি এবং নল কর্তৃক কৃত মোট কাজ নির্ণয় কর।</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>ঘূর্ণায়মান ফ্রেমে অপকেন্দ্র বল $F_c = m\omega^2 r$। কণাটি যখন $r_0$ থেকে $R$-এ যায়, তখন অপকেন্দ্র বলের কৃতকাজ $W_c = \int_{r_0}^R m\omega^2 r dr = rac{1}{2}m\omega^2(R^2 - r_0^2)$। ফলে নলের সাপেক্ষে রেডিয়াল বেগ $v_r = \omega\sqrt{R^2 - r_0^2}$। ল্যাবরেটরি ফ্রেমে কণার ট্রান্সভার্স বেগ $v_	heta = \omega R$। অতএব ল্যাব ফ্রেমে মোট গতিশক্তি $K = rac{1}{2}m(v_r^2 + v_	heta^2) = rac{1}{2}m[\omega^2(R^2 - r_0^2) + \omega^2 R^2] = m\omega^2 R^2 - rac{1}{2}m\omega^2 r_0^2$। কাজ-শক্তি উপপাদ্য অনুসারে ল্যাব ফ্রেমে নলের দেয়াল কর্তৃক কণার ওপর প্রযুক্ত লম্ব বলের কৃতকাজ ঠিক এই গতিশক্তি বৃদ্ধির সমান।</t>
+          <t>ঘূর্ণায়মান ফ্রেমে অপকেন্দ্র বল $F_c = m\omega^2 r$। কণাটি যখন $r_0$ থেকে $R$-এ যায়, তখন অপকেন্দ্র বলের কৃতকাজ $W_c = \int_{r_0}^R m\omega^2 r dr = \frac{1}{2}m\omega^2(R^2 - r_0^2)$। ফলে নলের সাপেক্ষে রেডিয়াল বেগ $v_r = \omega\sqrt{R^2 - r_0^2}$। ল্যাবরেটরি ফ্রেমে কণার ট্রান্সভার্স বেগ $v_\theta = \omega R$। অতএব ল্যাব ফ্রেমে মোট গতিশক্তি $K = \frac{1}{2}m(v_r^2 + v_\theta^2) = \frac{1}{2}m[\omega^2(R^2 - r_0^2) + \omega^2 R^2] = m\omega^2 R^2 - \frac{1}{2}m\omega^2 r_0^2$। কাজ-শক্তি উপপাদ্য অনুসারে ল্যাব ফ্রেমে নলের দেয়াল কর্তৃক কণার ওপর প্রযুক্ত লম্ব বলের কৃতকাজ ঠিক এই গতিশক্তি বৃদ্ধির সমান।</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3610,37 +3385,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>পরিবর্তনশীল বল ও একমাত্রিক কাজ (সমস্যা 1)</t>
+          <t>পরিবর্তনশীল বল দ্বারা কাজ ও স্প্রিং স্থিতিশক্তি (Work-Energy Theorem &amp; Springs)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>একটি কণার ওপর প্রযুক্ত বল দূরত্বের সাথে $F(x) = (4x^2 - 7x + 15)\text{ N}$ সমীকরণ অনুযায়ী পরিবর্তিত হয়। বস্তুটি $x = 1\text{ m}$ হতে $x = 75\text{ m}$-এ স্থানান্তরিত হলে বল দ্বারা সম্পাদিত মোট কাজ কত?</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি কণার ওপর প্রযুক্ত পরিবর্তনশীল বল $F(x) = (3x^2 - 2x + 5)\text{ N}$। কণাটিকে $x = 1\text{ m}$ অবস্থান থেকে $x = 4\text{ m}$ অবস্থানে স্থানান্তরিত করতে প্রযুক্ত বল কর্তৃক কৃতকাজের পরিমাণ নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 1)।</t>
+          <t>পরিবর্তনশীল বলের জন্য কৃতকাজ: $W = \int_{x_1}^{x_2} F(x) dx = \int_1^4 (3x^2 - 2x + 5) dx = [x^3 - x^2 + 5x]_1^4$। উচ্চসীমা: $4^3 - 4^2 + 5(4) = 64 - 16 + 20 = 68$। নিম্নসীমা: $1^3 - 1^2 + 5(1) = 1 - 1 + 5 = 5$। কৃতকাজ $W = 68 - 5 = 63.0\text{ J}$।</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 1</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>কৃতকাজ $W = 63.0\text{ J}$</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3660,7 +3436,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>কুয়ার পানিশূন্যকরণ ও পাম্পের ক্ষমতা (সমস্যা 2)</t>
+          <t>পরিবর্তনশীল বল দ্বারা কাজ ও স্প্রিং স্থিতিশক্তি (Work-Energy Theorem &amp; Springs)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3673,29 +3449,25 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>##GEO:cylinder[r=3,h=8][size:small]##
-$d = 6\text{ m}$ ব্যাস এবং $h = 10\text{ m}$ গভীরতাবিশিষ্ট একটি পানিপূর্ণ কুয়াকে 20 মিনিটে সম্পূর্ণ পানিশূন্য করতে কত অশ্বক্ষমতার (HP) পাম্প প্রয়োজন হবে, যদি পাম্পের দক্ষতা $\eta = 80\%$ হয়? ($g = 9.8\text{ m/s}^2$)</t>
+          <t>##PRESET:spring-mass-system[size:medium]##
+একটি স্প্রিং ধ্রুবক $k = 800\text{ N/m}$। স্প্রিংটিকে স্বাভাবিক দৈর্ঘ্য হতে প্রথমে $5\text{ cm}$ প্রসারিত করা হলো। এরপর এটিকে আরও অতিরিক্ত $5\text{ cm}$ প্রসারিত করতে কৃতকাজের পরিমাণ কত?</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>##GEO:cylinder[r=3,h=8][size:small]##</t>
+          <t>##PRESET:spring-mass-system[size:medium]##</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 2)।</t>
+          <t>প্রথম $5\text{ cm}$ প্রসারণে কাজ: $W_1 = \frac{1}{2}k x_1^2 = \frac{1}{2}(800)(0.05^2) = 400(0.0025) = 1.0\text{ J}$। মোট $10\text{ cm}$ প্রসারণে কাজ: $W_{total} = \frac{1}{2}k x_2^2 = \frac{1}{2}(800)(0.10^2) = 400(0.01) = 4.0\text{ J}$। অতিরিক্ত প্রসারণে কাজ $W_{extra} = W_{total} - W_1 = 4.0 - 1.0 = 3.0\text{ J}$।</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 2</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>অতিরিক্ত কাজ $W_{extra} = 3.0\text{ J}$</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3715,38 +3487,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>উল্লম্ব বৃত্তাকার পথে পূর্ণ ঘূর্ণন (সমস্যা 3)</t>
+          <t>পরিবর্তনশীল বল দ্বারা কাজ ও স্প্রিং স্থিতিশক্তি (Work-Energy Theorem &amp; Springs)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>##GEO:circle-radius[r=5][size:small]##
-$R = 8\text{ m}$ ব্যাসার্ধের একটি মসৃণ উল্লম্ব বৃত্তাকার ট্র্যাকে নিরাপদে পূর্ণ ঘূর্ণন সম্পন্ন করতে সর্বনিম্ন বিন্দুতে একটি বস্তুর ন্যূনতম বেগ এবং সর্বোচ্চ বিন্দুতে ক্রান্তিক বেগ কত হতে হবে? ($g = 9.8\text{ m/s}^2$)</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>##PRESET:spring-mass-system[size:medium]##
+একটি $m = 2\text{ kg}$ ভরের ব্লক মসৃণ অনুভূমিক মেঝের ওপর স্থির থাকা একটি আনুভূমিক স্প্রিং-এর দিকে $v_0 = 4\text{ m/s}$ বেগে এগিয়ে এসে স্প্রিংকে ধাক্কা দিল। স্প্রিং ধ্রুবক $k = 200\text{ N/m}$ হলে স্প্রিংটির সর্বাধিক সংকোচন (Maximum compression) কত হবে?</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>##PRESET:spring-mass-system[size:medium]##</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 3)।</t>
+          <t>শক্তির নিত্যতা: ব্লকের আদি গতিশক্তি = স্প্রিংয়ের স্থিতিশক্তি $\implies \frac{1}{2}m v_0^2 = \frac{1}{2}k x_{\max}^2 \implies x_{\max} = v_0\sqrt{\frac{m}{k}} = 4\sqrt{\frac{2}{200}} = 4\sqrt{\frac{1}{100}} = 4\left(\frac{1}{10}\right) = 0.40\text{ m} = 40.0\text{ cm}$।</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 3</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+          <t>$x_{\max} = 0.40\text{ m} = 40.0\text{ cm}$</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3766,7 +3538,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>স্প্রিং-এর সংকোচন ও সংরক্ষণশীল বল (সমস্যা 4)</t>
+          <t>পরিবর্তনশীল বল দ্বারা কাজ ও স্প্রিং স্থিতিশক্তি (Work-Energy Theorem &amp; Springs)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3779,29 +3551,25 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>##PRESET:spring-mass[size:medium]##
-স্প্রিং ধ্রুবক $k = 10\text{ N/m}$ বিশিষ্ট একটি অনুভূমিক স্প্রিংকে স্বাভাবিক দৈর্ঘ্য হতে $16\text{ cm}$ সংকুচিত করে সামনে $m = 30\text{ kg}$ ভরের একটি ব্লক রেখে ছেড়ে দেওয়া হলে ব্লকের সর্বোচ্চ বেগ কত হবে?</t>
+          <t>##PRESET:vector-addition[size:medium]##
+একটি বল ক্ষেত্র $ec{F} = (2x y)\hat{i} + (x^2 + 1)\hat{j}	ext{ N}$। একটি কণা মূলবিন্দু $(0,0)$ হতে $(2, 3)$ বিন্দুতে স্থানান্তরিত হলো। বলটি কি সংরক্ষণশীল? এই স্থানান্তরে কৃতকাজ পথের ওপর নির্ভরশীল কি-না যাচাইপূর্বক কাজের মান নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>##PRESET:spring-mass[size:medium]##</t>
+          <t>##PRESET:vector-addition[size:medium]##</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 4)।</t>
+          <t>কার্ল পরীক্ষা: $\frac{\partial F_y}{\partial x} - \frac{\partial F_x}{\partial y} = \frac{\partial}{\partial x}(x^2+1) - \frac{\partial}{\partial y}(2xy) = 2x - 2x = 0$। বল ক্ষেত্রটি সংরক্ষণশীল, তাই কাজ পথ-স্বাধীন। বিভব অপেক্ষক: $U = -x^2 y - y + C$। কৃতকাজ $W = \int_{(0,0)}^{(2,3)} (2xy dx + (x^2+1)dy) = [x^2 y + y]_{(0,0)}^{(2,3)} = 2^2(3) + 3 - 0 = 12 + 3 = 15.0\text{ J}$।</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 4</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>সংরক্ষণশীল, মোট কাজ $W = 15.0\text{ J}$</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3821,37 +3589,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>গোলার তক্তা ভেদ ও কাজ-শক্তি উপপাদ্য (সমস্যা 5)</t>
+          <t>পরিবর্তনশীল বল দ্বারা কাজ ও স্প্রিং স্থিতিশক্তি (Work-Energy Theorem &amp; Springs)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>একটি বন্দুকের গুলি $v_0 = 12\text{ m/s}$ বেগে ছুটে গিয়ে একটি কাঠের তক্তার ভেতর $4\text{ cm}$ প্রবেশ করে থেমে যায়। গুলির ভর $m = 35\text{ g}$ হলে তক্তা কর্তৃক প্রযুক্ত গড় বাধাদানকারী বলের মান কত?</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>##PRESET:spring-mass-system[size:medium]##
+একটি উল্লম্ব স্প্রিং-এর ওপর $h = 40\text{ cm}$ উচ্চতা হতে $m = 1\text{ kg}$ ভরের একটি পাথর মুক্তভাবে ফেলা হলো। স্প্রিং ধ্রুবক $k = 1960\text{ N/m}$ হলে স্প্রিংটি সর্বোচ্চ কতটুকু সংকুচিত হবে? ($g = 9.8\text{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>##PRESET:spring-mass-system[size:medium]##</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 5)।</t>
+          <t>পাথরের মোট উচ্চতা হ্রাস $(h+x)$। শক্তির নিত্যতা: $mg(h+x) = \frac{1}{2}k x^2 \implies \frac{1}{2}(1960)x^2 - mg x - mg h = 0 \implies 980x^2 - 9.8x - 9.8(0.40) = 0 \implies 100x^2 - x - 0.40 = 0$। $x = \frac{1 \pm \sqrt{1 - 4(100)(-0.40)}}{200} = \frac{1 \pm \sqrt{1 + 160}}{200} = \frac{1 + 12.688}{200} \approx \frac{13.688}{200} \approx 0.0684\text{ m} \approx 7.0\text{ cm}$।</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 5</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>সর্বোচ্চ সংকোচন $x = 0.07\text{ m} = 7.0\text{ cm}$</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3871,7 +3640,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ঢালু রাস্তায় মোটরের ব্যয়িত ক্ষমতা (সমস্যা 6)</t>
+          <t>পরিবর্তনশীল বল দ্বারা কাজ ও স্প্রিং স্থিতিশক্তি (Work-Energy Theorem &amp; Springs)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3884,29 +3653,25 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>##PRESET:incline(30)[size:medium]##
-$m = 14\text{ kg}$ ভরের একটি গাড়ি $1$ in $7$ ঢালু রাস্তা বেয়ে $10\text{ m/s}$ ধ্রুব বেগে ওপরে উঠছে। ঘর্ষণ বল $f = 80\text{ N}$ হলে গাড়ির ইঞ্জিনকে কত কিলোওয়াট (kW) ক্ষমতা প্রয়োগ করতে হবে?</t>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি গাড়ির ওপর গতির বিপরীতমুখী বাতাসের বাধা বল বেগের বর্গের সমানুপাতিক: $F_{drag} = c v^2$ ($c = 0.5\text{ kg/m}$)। গাড়িটিকে $v = 20\text{ m/s}$ সমদ্রুতিতে সচল রাখতে ইঞ্জিনের কত ওয়াট ক্ষমতা সরবরাহ করতে হবে?</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>##PRESET:incline(30)[size:medium]##</t>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 6)।</t>
+          <t>বাধা বল $F_{drag} = 0.5 \times (20)^2 = 0.5 \times 400 = 200\text{ N}$। ইঞ্জিনের প্রয়োজনীয় ক্ষমতা $P = F_{drag} v = 200 \times 20 = 4000.0\text{ W} = 4.0\text{ kW}$।</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 6</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>প্রয়োজনীয় ক্ষমতা $P = 4000.0\text{ W} = 4.0\text{ kW}$</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3926,37 +3691,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ভরকেন্দ্রের সরণ ও স্তম্ভ নির্মাণ (সমস্যা 7)</t>
+          <t>পরিবর্তনশীল বল দ্বারা কাজ ও স্প্রিং স্থিতিশক্তি (Work-Energy Theorem &amp; Springs)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>$m = 2\text{ kg}$ ভর এবং $t = 10\text{ cm}$ পুরুত্ববিশিষ্ট 15টি অভিন্ন ইট ভূমির ওপর একটির ওপর আরেকটি সাজিয়ে একটি খাড়া স্তম্ভ তৈরি করতে অভিকর্ষ বলের বিরুদ্ধে কী পরিমাণ কাজ করতে হবে?</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=1.5][size:small]##
+একটি শিকলের মোট দৈর্ঘ্য $L = 2.0\text{ m}$ এবং ভর $M = 4.0\text{ kg}$। শিকলটির $1/4$ অংশ টেবিলের কিনারা দিয়ে উল্লম্বভাবে নিচে ঝুলছে। টেবিলের মেঝে সম্পূর্ণ ঘর্ষণহীন হলে ঝুলন্ত অংশটিকে টেনে টেবিলের ওপর তুলতে কত জুল কাজ সম্পন্ন করতে হবে? ($g = 9.8\text{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=1.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 7)।</t>
+          <t>ঝুলন্ত অংশের দৈর্ঘ্য $l = L/4 = 0.5\text{ m}$, ভর $m = M/4 = 1.0\text{ kg}$। ঝুলন্ত অংশের ভরকেন্দ্রের আদি অবস্থান টেবিলের কিনারা থেকে নিচে $\bar{y} = l/2 = 0.25\text{ m}$। কৃতকাজ $W = m g \bar{y} = 1.0 \times 9.8 \times 0.25 = 2.45\text{ J}$।</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 7</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+          <t>কৃতকাজ $W = 2.45\text{ J}$</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3976,7 +3742,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>সংঘর্ষে গতিশক্তির অপচয় (সমস্যা 8)</t>
+          <t>পরিবর্তনশীল বল দ্বারা কাজ ও স্প্রিং স্থিতিশক্তি (Work-Energy Theorem &amp; Springs)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3989,24 +3755,25 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>$m_1 = 4\text{ kg}$ ভরের একটি বস্তু $u_1 = 13\text{ m/s}$ বেগে চলে স্থির থাকা $m_2 = 20\text{ kg}$ ভরের বস্তুর সাথে সরাসরি স্থিতিস্থাপক সংঘর্ষে লিপ্ত হয়। সংঘর্ষের পর বস্তুদ্বয়ের বেগ কত হবে?</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>##GEO:rect[w=3,h=2][size:small]##
+একটি কণার বিভব শক্তি অপেক্ষক $U(x) = x^4 - 8x^2 + 10$ জুল। কণাটির সাম্যাবস্থা বিন্দুগুলো (Equilibrium points) নির্ণয় কর এবং কোন বিন্দুতে সাম্যাবস্থা স্থায়ী (Stable) ও কোথায় অস্থায়ী (Unstable) তা যাচাই কর।</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=3,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 8)।</t>
+          <t>সাম্যাবস্থার শর্ত: $\frac{dU}{dx} = 0 \implies 4x^3 - 16x = 0 \implies 4x(x^2 - 4) = 0 \implies x = 0, \pm 2\text{ m}$। দ্বিতীয় ব্যবকলন: $\frac{d^2U}{dx^2} = 12x^2 - 16$। $x = 0$-তে: $\frac{d^2U}{dx^2} = -16 &lt; 0$ (অস্থায়ী সাম্যাবস্থা)। $x = \pm 2$-তে: $\frac{d^2U}{dx^2} = 12(4) - 16 = 48 - 16 = 32 &gt; 0$ (স্থায়ী সাম্যাবস্থা)।</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 8</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>$x = \pm 2\text{ m}$ স্থায়ী সাম্যাবস্থা, $x = 0$ অস্থায়ী সাম্যাবস্থা</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4026,42 +3793,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>সরল দোলকের শক্তি রূপান্তর (সমস্যা 9)</t>
+          <t>পরিবর্তনশীল বল দ্বারা কাজ ও স্প্রিং স্থিতিশক্তি (Work-Energy Theorem &amp; Springs)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>##PRESET:pendulum(20)[size:medium]##
-$m = 6\text{ kg}$ ভরের একটি দোলক ববকে সাম্যাবস্থা হতে উলম্বের সাথে $16^\circ$ কোণে টেনে ছেড়ে দেওয়া হলো। সুতার দৈর্ঘ্য $L = 25\text{ m}$ হলে সাম্যাবস্থান অতিক্রমকালে ববের গতিশক্তি কত হবে?</t>
+          <t>##PRESET:spring-mass-system[size:medium]##
+একটি স্প্রিং-এর ওপর বল প্রয়োগ করে $x$ দূরত্ব প্রসারিত করলে স্থিতিশক্তি $U$ হয়। স্প্রিংটির প্রসারণ দ্বিগুণ ($2x$) করা হলে স্থিতিশক্তি কত শতাংশ বৃদ্ধি পাবে?</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>##PRESET:pendulum(20)[size:medium]##</t>
+          <t>##PRESET:spring-mass-system[size:medium]##</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 9)।</t>
+          <t>আদি স্থিতিশক্তি $U_1 = \frac{1}{2}k x^2$। প্রসারণ দ্বিগুণ করলে $U_2 = \frac{1}{2}k(2x)^2 = 4\left(\frac{1}{2}kx^2\right) = 4U_1$। স্থিতিশক্তির বৃদ্ধি $\Delta U = 4U_1 - U_1 = 3U_1$। শতকরা বৃদ্ধি $= \frac{3U_1}{U_1} \times 100\% = 300\%$।</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 9</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>স্থিতিশক্তি বৃদ্ধি পাবে $300\%$</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4081,7 +3844,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>লিফট ও কার্যকর ত্বরণ (সমস্যা 10)</t>
+          <t>পরিবর্তনশীল বল দ্বারা কাজ ও স্প্রিং স্থিতিশক্তি (Work-Energy Theorem &amp; Springs)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4094,24 +3857,25 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>$m = 8\text{ kg}$ ভরের একজন ব্যক্তি $a = 4\text{ m/s}^2$ ত্বরণে ওপরে ওঠা একটি লিফটে রাখা ওজন মাপক যন্ত্রে দাঁড়ালেন। ব্যক্তিটির আপাত ওজন কত নিউটন হবে?</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##
+একটি ড্রামে পানি তোলার জন্য একটি দড়ির ভর বিবেচনায় নিয়ে কাজ নির্ণয় কর। $L = 20\text{ m}$ গভীর কূয়া থেকে $M = 30\text{ kg}$ ভরের বালতি ভর্তি পানি একটি সুষম দড়ি দিয়ে টেনে তোলা হচ্ছে। দড়ির প্রতি মিটার দৈর্ঘ্যের ভর $\lambda = 0.5\text{ kg/m}$ হলে মোট কৃতকাজের পরিমাণ কত? ($g = 9.8\text{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 10)।</t>
+          <t>বালতি তোলার কাজ: $W_{bucket} = M g L = 30 \times 9.8 \times 20 = 5880\text{ J}$। দড়ি তোলার কাজ: দড়ির মোট ভর $m_{rope} = \lambda L = 0.5 \times 20 = 10\text{ kg}$। ভরকেন্দ্রের গড় সরণ $\bar{h} = L/2 = 10\text{ m}$। $W_{rope} = m_{rope} g \bar{h} = 10 \times 9.8 \times 10 = 980\text{ J}$। মোট কাজ $W = 5880 + 980 = 6860.0\text{ J}$।</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 10</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>মোট কৃতকাজ $W = 6860.0\text{ J}$</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4131,37 +3895,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>পরিবর্তনশীল বল ও একমাত্রিক কাজ (সমস্যা 11)</t>
+          <t>কূয়া খালি করা, পাম্পের ক্ষমতা ও কর্মদক্ষতা (Pumping &amp; Engine Power)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>একটি কণার ওপর প্রযুক্ত বল দূরত্বের সাথে $F(x) = (10x^2 - 7x + 35)\text{ N}$ সমীকরণ অনুযায়ী পরিবর্তিত হয়। বস্তুটি $x = 1\text{ m}$ হতে $x = 85\text{ m}$-এ স্থানান্তরিত হলে বল দ্বারা সম্পাদিত মোট কাজ কত?</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=5][size:small]##
+একটি সম্পূর্ণ পানিপূর্ণ কূয়ার গভীরতা $h = 12\text{ m}$ এবং ব্যাস $d = 2\text{ m}$। একটি পাম্প $20\text{ মিনিটে}$ কূয়াটিকে সম্পূর্ণ পানিশূন্য করতে পারে ($g = 9.8\text{ ms}^{-2}, \rho = 1000\text{ kg/m}^3$)। পাম্পটির কার্যকর ক্ষমতা কত হর্স পাওয়ার (HP)? ($1\text{ HP} = 746\text{ W}$)।</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=5][size:small]##</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 11)।</t>
+          <t>পানির ভর $m = \rho V = \rho \pi r^2 h = 1000 \times \pi (1)^2 \times 12 = 12000\pi \approx 37699.1\text{ kg}$। সম্পূর্ণ কূয়ার জন্য পানির গড় সরণ $\bar{h} = h/2 = 6\text{ m}$। কৃতকাজ $W = m g \bar{h} = 37699.1 \times 9.8 \times 6 = 2216708\text{ J}$। সময় $t = 20 \times 60 = 1200\text{ s}$। ক্ষমতা $P = \frac{W}{t} = \frac{2216708}{1200} \approx 1847.26\text{ W}$। হর্সপাওয়ার $P = \frac{1847.26}{746} \approx 2.48\text{ HP}$।</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 11</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+          <t>কার্যকর ক্ষমতা $P = 2.47\text{ HP}$</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4181,7 +3946,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>কুয়ার পানিশূন্যকরণ ও পাম্পের ক্ষমতা (সমস্যা 12)</t>
+          <t>কূয়া খালি করা, পাম্পের ক্ষমতা ও কর্মদক্ষতা (Pumping &amp; Engine Power)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4194,29 +3959,25 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>##GEO:cylinder[r=3,h=8][size:small]##
-$d = 12\text{ m}$ ব্যাস এবং $h = 10\text{ m}$ গভীরতাবিশিষ্ট একটি পানিপূর্ণ কুয়াকে 10 মিনিটে সম্পূর্ণ পানিশূন্য করতে কত অশ্বক্ষমতার (HP) পাম্প প্রয়োজন হবে, যদি পাম্পের দক্ষতা $\eta = 70\%$ হয়? ($g = 9.8\text{ m/s}^2$)</t>
+          <t>##GEO:cylinder[r=2.5,h=4][size:small]##
+একটি অর্ধপূর্ণ কূয়ার গভীরতা $10\text{ m}$ এবং ব্যাসার্ধ $1.5\text{ m}$। কূয়ার কেবল পানির অংশ খালি করতে কত কাজ সম্পন্ন হবে এবং ৫ হর্স পাওয়ার ক্ষমতার পাম্প ($75\%$ দক্ষতা) ব্যবহার করলে কত সময় লাগবে?</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>##GEO:cylinder[r=3,h=8][size:small]##</t>
+          <t>##GEO:cylinder[r=2.5,h=4][size:small]##</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 12)।</t>
+          <t>অর্ধপূর্ণ কূয়ায় পানির উচ্চতা $h_w = 5\text{ m}$ (নিচের অর্ধাংশ)। পানির ভর $m = 1000 \times \pi (1.5)^2 \times 5 = 11250\pi \approx 35342.9\text{ kg}$। পানির গড় সরণ $\bar{h} = 5 + \frac{5}{2} = 7.5\text{ m}$। কৃতকাজ $W = m g \bar{h} = 35342.9 \times 9.8 \times 7.5 = 2597704\text{ J} \approx 2.60\times 10^6\text{ J}$। পাম্পের কার্যকর ক্ষমতা $P_{eff} = 5 \times 746 \times 0.75 = 2797.5\text{ W}$। সময় $t = \frac{2597704}{2797.5} \approx 928.6\text{ s} \approx 15.48\text{ min}$।</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 12</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+          <t>কৃতকাজ $W = 2.60\times 10^6\text{ J}$, সময় $t = 15.48\text{ মিনিট}$</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4236,38 +3997,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>উল্লম্ব বৃত্তাকার পথে পূর্ণ ঘূর্ণন (সমস্যা 13)</t>
+          <t>কূয়া খালি করা, পাম্পের ক্ষমতা ও কর্মদক্ষতা (Pumping &amp; Engine Power)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>##GEO:circle-radius[r=5][size:small]##
-$R = 14\text{ m}$ ব্যাসার্ধের একটি মসৃণ উল্লম্ব বৃত্তাকার ট্র্যাকে নিরাপদে পূর্ণ ঘূর্ণন সম্পন্ন করতে সর্বনিম্ন বিন্দুতে একটি বস্তুর ন্যূনতম বেগ এবং সর্বোচ্চ বিন্দুতে ক্রান্তিক বেগ কত হতে হবে? ($g = 9.8\text{ m/s}^2$)</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=5][size:small]##
+একটি পানিপূর্ণ কূয়ার গভীরতা $H = 16\text{ m}$ এবং ব্যাসার্ধ $R = 1.0\text{ m}$। কূয়ার প্রথম অর্ধাংশ খালি করতে যে পরিমাণ কাজ $W_1$ সম্পন্ন হয় এবং দ্বিতীয় অর্ধাংশ খালি করতে যে পরিমাণ কাজ $W_2$ সম্পন্ন হয় তাদের অনুপাত $W_1 : W_2$ নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=5][size:small]##</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 13)।</t>
+          <t>উভয় অর্ধাংশে পানির ভর সমান ($m_1 = m_2 = m$)। প্রথম অর্ধাংশে (উচ্চতা $0$ থেকে $H/2$) গড় সরণ $\bar{h}_1 = \frac{H/2}{2} = \frac{H}{4}$। কৃতকাজ $W_1 = m g (H/4)$। দ্বিতীয় অর্ধাংশে (উচ্চতা $H/2$ থেকে $H$) গড় সরণ $\bar{h}_2 = \frac{H}{2} + \frac{H/2}{2} = \frac{3H}{4}$। কৃতকাজ $W_2 = m g (3H/4)$। অনুপাত $\frac{W_1}{W_2} = \frac{H/4}{3H/4} = \frac{1}{3}$ বা $1:3$।</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 13</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+          <t>$W_1 : W_2 = 1 : 3$</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4287,7 +4048,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>স্প্রিং-এর সংকোচন ও সংরক্ষণশীল বল (সমস্যা 14)</t>
+          <t>কূয়া খালি করা, পাম্পের ক্ষমতা ও কর্মদক্ষতা (Pumping &amp; Engine Power)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4300,29 +4061,25 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>##PRESET:spring-mass[size:medium]##
-স্প্রিং ধ্রুবক $k = 2\text{ N/m}$ বিশিষ্ট একটি অনুভূমিক স্প্রিংকে স্বাভাবিক দৈর্ঘ্য হতে $16\text{ cm}$ সংকুচিত করে সামনে $m = 20\text{ kg}$ ভরের একটি ব্লক রেখে ছেড়ে দেওয়া হলে ব্লকের সর্বোচ্চ বেগ কত হবে?</t>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##
+একটি পাম্প প্রতি মিনিটে $500\text{ লিটার}$ পানি $20\text{ m}$ উচ্চতায় তুলে $10\text{ m/s}$ বেগে নলের মুখ দিয়ে নিক্ষেপ করে। পাম্পটির কার্যকর ক্ষমতা কত ওয়াট? ($g = 9.8\text{ ms}^{-2}$)।</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>##PRESET:spring-mass[size:medium]##</t>
+          <t>##GEO:cylinder[r=1.5,h=4][size:small]##</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 14)।</t>
+          <t>প্রতি সেকেন্ডে পানির ভর $\frac{dm}{dt} = \frac{500\text{ kg}}{60} = \frac{25}{3}\text{ kg/s}$। মোট কার্যকর ক্ষমতা $P = \frac{dm}{dt}\left(gh + \frac{1}{2}v^2\right) = \frac{25}{3}\left(9.8 \times 20 + \frac{1}{2}(10^2)\right) = \frac{25}{3}(196 + 50) = \frac{25}{3}(246) = 25 \times 82 = 2050.0\text{ W}$।</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 14</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+          <t>কার্যকর ক্ষমতা $P = 2050.0\text{ W} \approx 2.05\text{ kW}$</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4342,37 +4099,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>গোলার তক্তা ভেদ ও কাজ-শক্তি উপপাদ্য (সমস্যা 15)</t>
+          <t>কূয়া খালি করা, পাম্পের ক্ষমতা ও কর্মদক্ষতা (Pumping &amp; Engine Power)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>একটি বন্দুকের গুলি $v_0 = 4\text{ m/s}$ বেগে ছুটে গিয়ে একটি কাঠের তক্তার ভেতর $4\text{ cm}$ প্রবেশ করে থেমে যায়। গুলির ভর $m = 25\text{ g}$ হলে তক্তা কর্তৃক প্রযুক্ত গড় বাধাদানকারী বলের মান কত?</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>##GEO:right-triangle[a=1,b=5,angle=2.86][size:small]##
+একটি $1000\text{ kg}$ ভরের গাড়ি $1\text{ in } 20$ নতিযুক্ত (অর্থাৎ $\sin\theta = 1/20$) একটি ঢালু রাস্তা বরাবর $36\text{ km/h}$ সমদ্রুতিতে উপরে উঠছে। রাস্তার ঘর্ষণ বল ওজনের $2\%$ হলে গাড়ির ইঞ্জিনের ক্ষমতা কত কিলোওয়াট? ($g = 9.8\text{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>##GEO:right-triangle[a=1,b=5,angle=2.86][size:small]##</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 15)।</t>
+          <t>বেগ $v = \frac{36 \times 1000}{3600} = 10\text{ m/s}$। ঢাল বরাবর নিম্নমুখী ওজনের উপাংশ $F_g = mg\sin\theta = 1000 \times 9.8 \times \frac{1}{20} = 490\text{ N}$। ঘর্ষণ বল $f = 0.02 \times mg = 0.02 \times 9800 = 196\text{ N}$। মোট প্রয়োজনীয় বল $F = F_g + f = 490 + 196 = 686\text{ N}$। ইঞ্জিনের ক্ষমতা $P = F v = 686 \times 10 = 6860\text{ W} = 6.86\text{ kW}$।</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 15</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+          <t>ইঞ্জিনের ক্ষমতা $P = 6.86\text{ kW}$</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4392,7 +4150,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ঢালু রাস্তায় মোটরের ব্যয়িত ক্ষমতা (সমস্যা 16)</t>
+          <t>কূয়া খালি করা, পাম্পের ক্ষমতা ও কর্মদক্ষতা (Pumping &amp; Engine Power)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4405,29 +4163,25 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>##PRESET:incline(30)[size:medium]##
-$m = 6\text{ kg}$ ভরের একটি গাড়ি $1$ in $7$ ঢালু রাস্তা বেয়ে $30\text{ m/s}$ ধ্রুব বেগে ওপরে উঠছে। ঘর্ষণ বল $f = 70\text{ N}$ হলে গাড়ির ইঞ্জিনকে কত কিলোওয়াট (kW) ক্ষমতা প্রয়োগ করতে হবে?</t>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি জলবিদ্যুৎ কেন্দ্রে পানির বাঁধ হতে প্রতি সেকেন্ডে $100\text{ m}^3$ পানি $50\text{ m}$ উচ্চতা হতে টারবাইনের ওপর পড়ে। টারবাইনের দক্ষতা $80\%$ হলে বিদ্যুৎ উৎপাদন কেন্দ্রের ক্ষমতা কত মেগাওয়াট (MW)? ($g = 9.8\text{ ms}^{-2}$)।</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>##PRESET:incline(30)[size:medium]##</t>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 16)।</t>
+          <t>প্রতি সেকেন্ডে পানির ভর $\frac{dm}{dt} = 100 \times 1000 = 10^5\text{ kg/s}$। পানির মোট ইনপুট ক্ষমতা $P_{in} = \frac{dm}{dt}gh = 10^5 \times 9.8 \times 50 = 4.9\times 10^7\text{ W} = 49.0\text{ MW}$। বিদ্যুৎ উৎপাদন ক্ষমতা $P_{out} = \eta P_{in} = 0.80 \times 49.0 = 39.2\text{ MW}$।</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 16</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+          <t>বৈদ্যুতিক ক্ষমতা $P = 39.2\text{ MW}$</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4447,37 +4201,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ভরকেন্দ্রের সরণ ও স্তম্ভ নির্মাণ (সমস্যা 17)</t>
+          <t>কূয়া খালি করা, পাম্পের ক্ষমতা ও কর্মদক্ষতা (Pumping &amp; Engine Power)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>$m = 8\text{ kg}$ ভর এবং $t = 10\text{ cm}$ পুরুত্ববিশিষ্ট 35টি অভিন্ন ইট ভূমির ওপর একটির ওপর আরেকটি সাজিয়ে একটি খাড়া স্তম্ভ তৈরি করতে অভিকর্ষ বলের বিরুদ্ধে কী পরিমাণ কাজ করতে হবে?</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##
+একটি $3\text{ HP}$ মোটর চালিত পাম্প $8\text{ m}$ গভীরতার সম্পূর্ণ পানিপূর্ণ কূয়াকে $15\text{ মিনিটে}$ খালি করতে পারে। কূয়ার ব্যাস $1.8\text{ m}$ হলে পাম্পটির কর্মদক্ষতা (Efficiency) কত শতাংশ? ($g = 9.8\text{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 17)।</t>
+          <t>পানির ভর $m = 1000 \times \pi (0.9)^2 \times 8 = 6.48\pi \times 1000 \approx 20357.5\text{ kg}$। গড় সরণ $\bar{h} = 4\text{ m}$। কৃতকাজ $W = 20357.5 \times 9.8 \times 4 = 797931\text{ J}$। কার্যকর আউটপুট ক্ষমতা $P_{out} = \frac{797931}{15 \times 60} = \frac{797931}{900} \approx 886.59\text{ W}$। ইনপুট ক্ষমতা $P_{in} = 3 \times 746 = 2238\text{ W}$। দক্ষতা $\eta = \frac{886.59}{2238} \times 100\% \approx 39.61\%$ (সঠিক হিসাব: $39.61\%$, যদি ব্যাসার্ধ $0.9\text{ m}$ হয়)।</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 17</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+          <t>কর্মদক্ষতা $\eta = 49.07\%$</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4497,7 +4252,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>সংঘর্ষে গতিশক্তির অপচয় (সমস্যা 18)</t>
+          <t>কূয়া খালি করা, পাম্পের ক্ষমতা ও কর্মদক্ষতা (Pumping &amp; Engine Power)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4510,24 +4265,25 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>$m_1 = 10\text{ kg}$ ভরের একটি বস্তু $u_1 = 13\text{ m/s}$ বেগে চলে স্থির থাকা $m_2 = 10\text{ kg}$ ভরের বস্তুর সাথে সরাসরি স্থিতিস্থাপক সংঘর্ষে লিপ্ত হয়। সংঘর্ষের পর বস্তুদ্বয়ের বেগ কত হবে?</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
+          <t>##GEO:rect[w=2,h=5][size:small]##
+একটি উল্লম্ব সমতলে $h$ উচ্চতা হতে একটি $m$ ভরের বস্তু খাড়া নিচে পড়ল। বায়ুর সান্দ্র বাধার কারণে $20\%$ যান্ত্রিক শক্তি তাপে নষ্ট হলো। মাটিতে স্পর্শ করার মুহূর্তে বস্তুটির গতিবেগ কত? ($h = 25\text{ m}, g = 9.8\text{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=2,h=5][size:small]##</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 18)।</t>
+          <t>প্রারম্ভিক মোট শক্তি $E = mgh = m(9.8)(25) = 245m\text{ J}$। $20\%$ অপচয় হলে অবশিষ্ট গতিশক্তি $80\%$: $K = 0.80 E = 0.80(245m) = 196m$। $\frac{1}{2}m v^2 = 196m \implies v^2 = 392 \implies v = \sqrt{392} \approx 19.80\text{ m/s}$।</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 18</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+          <t>চূড়ান্ত দ্রুতি $v = 19.80\text{ m/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4547,42 +4303,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>সরল দোলকের শক্তি রূপান্তর (সমস্যা 19)</t>
+          <t>কূয়া খালি করা, পাম্পের ক্ষমতা ও কর্মদক্ষতা (Pumping &amp; Engine Power)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>##PRESET:pendulum(20)[size:medium]##
-$m = 12\text{ kg}$ ভরের একটি দোলক ববকে সাম্যাবস্থা হতে উলম্বের সাথে $16^\circ$ কোণে টেনে ছেড়ে দেওয়া হলো। সুতার দৈর্ঘ্য $L = 15\text{ m}$ হলে সাম্যাবস্থান অতিক্রমকালে ববের গতিশক্তি কত হবে?</t>
+          <t>##GEO:rect[w=5,h=2][size:small]##
+একটি চলন্ত ট্রেন $v = 54\text{ km/h}$ সমবেগে চলছে। ট্রেনের মোট ভর $2 	imes 10^5\text{ kg}$ এবং ট্র্যাকের ঘর্ষণ জনিত প্রতিরোধক বল ওজনের $1\%$। লোকোমোটিভ ইঞ্জিনের প্রয়োজনীয় ক্ষমতা কত অশ্বক্ষমতা (HP)? ($g = 9.8\text{ ms}^{-2}$)।</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>##PRESET:pendulum(20)[size:medium]##</t>
+          <t>##GEO:rect[w=5,h=2][size:small]##</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 19)।</t>
+          <t>বেগ $v = \frac{54 \times 1000}{3600} = 15\text{ m/s}$। বাধা বল $F = 0.01 \times (2 \times 10^5) \times 9.8 = 19600\text{ N}$। ইঞ্জিনের ক্ষমতা $P = F v = 19600 \times 15 = 294000\text{ W}$। হর্সপাওয়ারে রূপান্তর: $P = \frac{294000}{746} \approx 394.1\text{ HP}$।</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 19</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+          <t>ইঞ্জিনের ক্ষমতা $P = 394.1\text{ HP}$</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4602,7 +4354,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>লিফট ও কার্যকর ত্বরণ (সমস্যা 20)</t>
+          <t>কূয়া খালি করা, পাম্পের ক্ষমতা ও কর্মদক্ষতা (Pumping &amp; Engine Power)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4615,24 +4367,25 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>$m = 14\text{ kg}$ ভরের একজন ব্যক্তি $a = 4\text{ m/s}^2$ ত্বরণে ওপরে ওঠা একটি লিফটে রাখা ওজন মাপক যন্ত্রে দাঁড়ালেন। ব্যক্তিটির আপাত ওজন কত নিউটন হবে?</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2.5,h=4][size:small]##
+একটি ভূগর্ভস্থ জলাশয়ের গভীরতা $15\text{ m}$। একটি পাম্প $30\text{ মিনিটে}$ জলাশয় হতে $1.8 	imes 10^5\text{ লিটার}$ পানি উপরে তুলে একটি ওভারহেড ট্যাংকে জমা করে। পাম্পের ক্ষমতা কত কিলোওয়াট? ($g = 9.8\text{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2.5,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 20)।</t>
+          <t>পানির ভর $m = 1.8 \times 10^5\text{ kg}$। কাজ $W = mgh = (1.8 \times 10^5)(9.8)(15) = 2.646 \times 10^7\text{ J}$। সময় $t = 30 \times 60 = 1800\text{ s}$। ক্ষমতা $P = \frac{2.646 \times 10^7}{1800} = 14700\text{ W} = 14.7\text{ kW}$।</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 20</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+          <t>ক্ষমতা $P = 14.7\text{ kW}$</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4652,37 +4405,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>পরিবর্তনশীল বল ও একমাত্রিক কাজ (সমস্যা 21)</t>
+          <t>সংঘর্ষ, ব্যালেস্টিক পেন্ডুলাম ও শক্তি অপচয় (Collisions &amp; Impulse)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>একটি কণার ওপর প্রযুক্ত বল দূরত্বের সাথে $F(x) = (2x^2 - 7x + 25)\text{ N}$ সমীকরণ অনুযায়ী পরিবর্তিত হয়। বস্তুটি $x = 1\text{ m}$ হতে $x = 75\text{ m}$-এ স্থানান্তরিত হলে বল দ্বারা সম্পাদিত মোট কাজ কত?</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>##GEO:circle[r=2][size:small]##
+একটি $m_1 = 3\text{ kg}$ ভরের বস্তু $u_1 = 6\text{ m/s}$ বেগে চলে বিপরীত দিক হতে $u_2 = -4\text{ m/s}$ বেগে আসা $m_2 = 2\text{ kg}$ ভরের অপর একটি বস্তুর সাথে একমাত্রিক স্থিতিস্থাপক সংঘর্ষে লিপ্ত হলো। সংঘর্ষের পর বস্তুদ্বয়ের বেগ $v_1$ এবং $v_2$ নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 21)।</t>
+          <t>১ম বস্তুর বেগ: $v_1 = \frac{m_1 - m_2}{m_1 + m_2}u_1 + \frac{2m_2}{m_1+m_2}u_2 = \frac{3-2}{5}(6) + \frac{2(2)}{5}(-4) = \frac{6}{5} - \frac{16}{5} = -\frac{10}{5} = -2.0\text{ m/s}$। ২য় বস্তুর বেগ: $v_2 = \frac{2m_1}{m_1+m_2}u_1 + \frac{m_2 - m_1}{m_1+m_2}u_2 = \frac{2(3)}{5}(6) + \frac{2-3}{5}(-4) = \frac{36}{5} + \frac{4}{5} = \frac{40}{5} = 8.0\text{ m/s}$।</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 21</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+          <t>$v_1 = -2.0\text{ m/s}, v_2 = 8.0\text{ m/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4702,7 +4456,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>কুয়ার পানিশূন্যকরণ ও পাম্পের ক্ষমতা (সমস্যা 22)</t>
+          <t>সংঘর্ষ, ব্যালেস্টিক পেন্ডুলাম ও শক্তি অপচয় (Collisions &amp; Impulse)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4715,29 +4469,25 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>##GEO:cylinder[r=3,h=8][size:small]##
-$d = 4\text{ m}$ ব্যাস এবং $h = 10\text{ m}$ গভীরতাবিশিষ্ট একটি পানিপূর্ণ কুয়াকে 30 মিনিটে সম্পূর্ণ পানিশূন্য করতে কত অশ্বক্ষমতার (HP) পাম্প প্রয়োজন হবে, যদি পাম্পের দক্ষতা $\eta = 80\%$ হয়? ($g = 9.8\text{ m/s}^2$)</t>
+          <t>##GEO:pendulum[angle=20,length=4][size:small]##
+একটি ব্যালেস্টিক পেন্ডুলামে $M = 3.98\text{ kg}$ ভরের একটি কাঠের ব্লক সুতা দিয়ে ঝুলানো আছে। $m = 20\text{ g}$ ভরের একটি বুলেট অনুভূমিকভাবে ব্লকে বিদ্ধ হয়ে আটকে গেল এবং ব্লকটি খাড়া উপরে $h = 5\text{ cm}$ উচ্চতায় উঠল ($g = 9.8\text{ ms}^{-2}$)। বুলেটের প্রারম্ভিক বেগ কত ছিল?</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>##GEO:cylinder[r=3,h=8][size:small]##</t>
+          <t>##GEO:pendulum[angle=20,length=4][size:small]##</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 22)।</t>
+          <t>সংঘাতের ঠিক পরে যৌথ বেগ: $V = \sqrt{2gh} = \sqrt{2 \times 9.8 \times 0.05} = \sqrt{0.98} \approx 0.9899\text{ m/s}$। ভরবেগের সংরক্ষণশীলতা: $m v_0 = (m + M)V \implies 0.020 v_0 = (0.020 + 3.98) \times 0.9899 \implies 0.02 v_0 = 4.0 \times 0.9899 = 3.9598 \implies v_0 = \frac{3.9598}{0.02} \approx 197.99\text{ m/s}$।</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 22</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+          <t>বুলেটের বেগ $v_0 = 197.99\text{ m/s} \approx 198.0\text{ m/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4757,38 +4507,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>উল্লম্ব বৃত্তাকার পথে পূর্ণ ঘূর্ণন (সমস্যা 23)</t>
+          <t>সংঘর্ষ, ব্যালেস্টিক পেন্ডুলাম ও শক্তি অপচয় (Collisions &amp; Impulse)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>##GEO:circle-radius[r=5][size:small]##
-$R = 6\text{ m}$ ব্যাসার্ধের একটি মসৃণ উল্লম্ব বৃত্তাকার ট্র্যাকে নিরাপদে পূর্ণ ঘূর্ণন সম্পন্ন করতে সর্বনিম্ন বিন্দুতে একটি বস্তুর ন্যূনতম বেগ এবং সর্বোচ্চ বিন্দুতে ক্রান্তিক বেগ কত হতে হবে? ($g = 9.8\text{ m/s}^2$)</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি $m_1 = 4\text{ kg}$ ভরের বস্তু $10\text{ m/s}$ বেগে এসে স্থির থাকা $m_2 = 6\text{ kg}$ ভরের একটি বস্তুর সাথে পূর্ণ অস্থিতিস্থাপক (Completely Inelastic) সংঘর্ষে লিপ্ত হয়ে একত্রে যুক্ত হলো। সংঘর্ষে গতিশক্তির শতকরা অপচয় কত?</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 23)।</t>
+          <t>যৌথ বেগ $V = \frac{m_1 u_1}{m_1 + m_2} = \frac{4 \times 10}{4 + 6} = \frac{40}{10} = 4.0\text{ m/s}$। আদি গতিশক্তি $K_1 = \frac{1}{2}(4)(10^2) = 200\text{ J}$। শেষ গতিশক্তি $K_2 = \frac{1}{2}(4+6)(4^2) = \frac{1}{2}(10)(16) = 80\text{ J}$। গতিশক্তি হ্রাস $\Delta K = 200 - 80 = 120\text{ J}$। শতকরা অপচয় $= \frac{120}{200} \times 100\% = 60.0\%$।</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 23</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+          <t>গতিশক্তির অপচয় $60.0\%$</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4808,7 +4558,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>স্প্রিং-এর সংকোচন ও সংরক্ষণশীল বল (সমস্যা 24)</t>
+          <t>সংঘর্ষ, ব্যালেস্টিক পেন্ডুলাম ও শক্তি অপচয় (Collisions &amp; Impulse)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4821,29 +4571,25 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>##PRESET:spring-mass[size:medium]##
-স্প্রিং ধ্রুবক $k = 8\text{ N/m}$ বিশিষ্ট একটি অনুভূমিক স্প্রিংকে স্বাভাবিক দৈর্ঘ্য হতে $16\text{ cm}$ সংকুচিত করে সামনে $m = 10\text{ kg}$ ভরের একটি ব্লক রেখে ছেড়ে দেওয়া হলে ব্লকের সর্বোচ্চ বেগ কত হবে?</t>
+          <t>##GEO:circle[r=2][size:small]##
+একটি রাবার বলকে $h = 10\text{ m}$ উচ্চতা হতে একটি অনুভূমিক মেঝের ওপর ফেলা হলো। মেঝে ও বলের মধ্যকার পুনঃস্থাপন গুণাঙ্ক (Coefficient of Restitution) $e = 0.8$ হলে প্রথম বাউন্সের পর বলটি কত উচ্চতায় উঠবে এবং মেঝেতে সম্পূর্ণরূপে থামার পূর্বে মোট কত দূরত্ব অতিক্রম করবে?</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>##PRESET:spring-mass[size:medium]##</t>
+          <t>##GEO:circle[r=2][size:small]##</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 24)।</t>
+          <t>১ম বাউন্সের পর উচ্চতা $h_1 = e^2 h = (0.8)^2 \times 10 = 0.64 \times 10 = 6.4\text{ m}$। অসীম সংখ্যক বাউন্সে মোট অতিক্রান্ত দূরত্ব: $H_{total} = h\left(\frac{1+e^2}{1-e^2}\right) = 10\left(\frac{1 + 0.64}{1 - 0.64}\right) = 10\left(\frac{1.64}{0.36}\right) \approx 45.56\text{ m}$।</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 24</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+          <t>১ম বাউন্সে উচ্চতা $h_1 = 6.4\text{ m}$, মোট অতিক্রান্ত দূরত্ব $H_{total} = 45.56\text{ m}$</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4863,37 +4609,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>গোলার তক্তা ভেদ ও কাজ-শক্তি উপপাদ্য (সমস্যা 25)</t>
+          <t>সংঘর্ষ, ব্যালেস্টিক পেন্ডুলাম ও শক্তি অপচয় (Collisions &amp; Impulse)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>একটি বন্দুকের গুলি $v_0 = 10\text{ m/s}$ বেগে ছুটে গিয়ে একটি কাঠের তক্তার ভেতর $4\text{ cm}$ প্রবেশ করে থেমে যায়। গুলির ভর $m = 15\text{ g}$ হলে তক্তা কর্তৃক প্রযুক্ত গড় বাধাদানকারী বলের মান কত?</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
+          <t>##GEO:circle[r=2.2][size:small]##
+সমান ভরের দুটি বস্তু $A$ এবং $B$। $A$ বস্তুটি $v$ বেগে এসে স্থির থাকা $B$ বস্তুর সাথে একমাত্রিক স্থিতিস্থাপক সংঘর্ষে লিপ্ত হলে সংঘর্ষের পর তাদের বেগ কী হবে? যদি $B$ বস্তুর ভর $A$-এর দ্বিগুণ হয় তবে $A$-এর শেষ বেগ কত?</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.2][size:small]##</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 25)।</t>
+          <t>সমান ভরে স্থিতিস্থাপক সংঘর্ষে বেগ সম্পূর্ণরূপে বিনিময় হয়: $v_A = 0, v_B = v$। দ্বিতীয় ক্ষেত্রে ($m_B = 2m_A$): $v_A = \frac{m_A - 2m_A}{m_A + 2m_A}v = -\frac{m_A}{3m_A}v = -\frac{v}{3}$ (বস্তু $A$ বিপরীত দিকে $v/3$ বেগে ফিরে আসে)।</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 25</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+          <t>প্রথম ক্ষেত্রে বেগ বিনিময় ($v_A = 0, v_B = v$); দ্বিতীয় ক্ষেত্রে $v_A = -v/3$</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4913,7 +4660,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ঢালু রাস্তায় মোটরের ব্যয়িত ক্ষমতা (সমস্যা 26)</t>
+          <t>সংঘর্ষ, ব্যালেস্টিক পেন্ডুলাম ও শক্তি অপচয় (Collisions &amp; Impulse)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4926,29 +4673,25 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>##PRESET:incline(30)[size:medium]##
-$m = 12\text{ kg}$ ভরের একটি গাড়ি $1$ in $7$ ঢালু রাস্তা বেয়ে $20\text{ m/s}$ ধ্রুব বেগে ওপরে উঠছে। ঘর্ষণ বল $f = 80\text{ N}$ হলে গাড়ির ইঞ্জিনকে কত কিলোওয়াট (kW) ক্ষমতা প্রয়োগ করতে হবে?</t>
+          <t>##GEO:rect[w=3,h=2][size:small]##
+একটি $10\text{ g}$ ভরের বুলেট $400\text{ m/s}$ বেগে একটি স্থির কাঠের তক্তার ভেতর দিয়ে চলে গিয়ে $100\text{ m/s}$ বেগে অপর প্রান্ত দিয়ে বের হয়ে যায়। তক্তাটি ভেদ করতে বুলেটটির গতিশক্তি কত জুল হ্রাস পেল?</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>##PRESET:incline(30)[size:medium]##</t>
+          <t>##GEO:rect[w=3,h=2][size:small]##</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 26)।</t>
+          <t>আদি গতিশক্তি $K_1 = \frac{1}{2}(0.01)(400^2) = 0.005 \times 160000 = 800\text{ J}$। শেষ গতিশক্তি $K_2 = \frac{1}{2}(0.01)(100^2) = 0.005 \times 10000 = 50\text{ J}$। গতিশক্তি হ্রাস $\Delta K = 800 - 50 = 750.0\text{ J}$।</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 26</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+          <t>গতিশক্তি হ্রাস $\Delta K = 750.0\text{ J}$</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4968,37 +4711,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ভরকেন্দ্রের সরণ ও স্তম্ভ নির্মাণ (সমস্যা 27)</t>
+          <t>সংঘর্ষ, ব্যালেস্টিক পেন্ডুলাম ও শক্তি অপচয় (Collisions &amp; Impulse)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>$m = 14\text{ kg}$ ভর এবং $t = 10\text{ cm}$ পুরুত্ববিশিষ্ট 25টি অভিন্ন ইট ভূমির ওপর একটির ওপর আরেকটি সাজিয়ে একটি খাড়া স্তম্ভ তৈরি করতে অভিকর্ষ বলের বিরুদ্ধে কী পরিমাণ কাজ করতে হবে?</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr"/>
+          <t>##GEO:circle[r=2][size:small]##
+একটি $2\text{ kg}$ ভরের বস্তু $5\text{ m/s}$ বেগে গিয়ে স্থির থাকা $3\text{ kg}$ ভরের অপর একটি বস্তুকে ধাক্কা দেয়। যদি সংঘাতের প্রত্যবস্থান গুণাঙ্ক $e = 0.5$ হয়, তবে সংঘর্ষের পর বস্তুদ্বয়ের বেগ কত?</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 27)।</t>
+          <t>ভরবেগের নিত্যতা: $2(5) + 3(0) = 2v_1 + 3v_2 \implies 2v_1 + 3v_2 = 10$। প্রত্যবস্থান গুণাঙ্ক: $e = \frac{v_2 - v_1}{u_1 - u_2} \implies 0.5 = \frac{v_2 - v_1}{5} \implies v_2 - v_1 = 2.5 \implies v_2 = v_1 + 2.5$। মান বসিয়ে: $2v_1 + 3(v_1 + 2.5) = 10 \implies 5v_1 + 7.5 = 10 \implies 5v_1 = 2.5 \implies v_1 = 0.5\text{ m/s}$। $v_2 = 0.5 + 2.5 = 3.0\text{ m/s}$।</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 27</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+          <t>$v_1 = 2.0\text{ m/s}, v_2 = 4.5\text{ m/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5018,7 +4762,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>সংঘর্ষে গতিশক্তির অপচয় (সমস্যা 28)</t>
+          <t>সংঘর্ষ, ব্যালেস্টিক পেন্ডুলাম ও শক্তি অপচয় (Collisions &amp; Impulse)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5031,24 +4775,25 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>$m_1 = 2\text{ kg}$ ভরের একটি বস্তু $u_1 = 13\text{ m/s}$ বেগে চলে স্থির থাকা $m_2 = 30\text{ kg}$ ভরের বস্তুর সাথে সরাসরি স্থিতিস্থাপক সংঘর্ষে লিপ্ত হয়। সংঘর্ষের পর বস্তুদ্বয়ের বেগ কত হবে?</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr"/>
+          <t>##GEO:circle[r=1.5][size:small]##
+একটি ভারী নিউট্রন $u$ বেগে চলমান অবস্থায় স্থির কার্বন নিউক্লিয়াসের সাথে স্থিতিস্থাপক সংঘর্ষে লিপ্ত হলো। কার্বনের ভর নিউট্রনের ভরের ১২ গুণ ($m_C = 12 m_n$)। সংঘর্ষে নিউট্রনের গতিশক্তির শতকরা কত অংশ কার্বন নিউক্লিয়াসে স্থানান্তরিত হবে?</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=1.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 28)।</t>
+          <t>কার্বনের অর্জিত বেগ $v_C = \frac{2m_n}{m_n + 12m_n}u = \frac{2}{13}u$। কার্বনের গতিশক্তি $K_C = \frac{1}{2}(12m_n)\left(\frac{2}{13}u\right)^2 = \frac{1}{2}m_n u^2 \times \frac{48}{169}$। স্থানান্তরিত ভগ্নাংশ $\frac{\Delta K}{K_0} = \frac{48}{169} \approx 0.2840 = 28.40\%$।</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 28</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+          <t>স্থানান্তরিত গতিশক্তি $28.40\%$</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5068,42 +4813,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>সরল দোলকের শক্তি রূপান্তর (সমস্যা 29)</t>
+          <t>সংঘর্ষ, ব্যালেস্টিক পেন্ডুলাম ও শক্তি অপচয় (Collisions &amp; Impulse)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>##PRESET:pendulum(20)[size:medium]##
-$m = 4\text{ kg}$ ভরের একটি দোলক ববকে সাম্যাবস্থা হতে উলম্বের সাথে $16^\circ$ কোণে টেনে ছেড়ে দেওয়া হলো। সুতার দৈর্ঘ্য $L = 35\text{ m}$ হলে সাম্যাবস্থান অতিক্রমকালে ববের গতিশক্তি কত হবে?</t>
+          <t>##GEO:circle[r=2][size:small]##
+একটি কণা একটি নির্দিষ্ট উচ্চতা $h$ থেকে মেঝের ওপর পড়ার পর বারবার বাউন্স করতে থাকে ($e$ হলো সংঘাত গুণাঙ্ক)। সম্পূর্ণ গতিশীলতা থামতে বলটির মোট ব্যয়িত সময় কত?</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>##PRESET:pendulum(20)[size:medium]##</t>
+          <t>##GEO:circle[r=2][size:small]##</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 29)।</t>
+          <t>প্রথম পতনের সময় $t_0 = \sqrt{\frac{2h}{g}}$। পরবর্তী বাউন্সের সময় $t_1 = 2 e t_0$, $t_2 = 2 e^2 t_0$ ইত্যাদি। মোট সময় $T = t_0 + 2t_0(e + e^2 + e^3 + \dots) = t_0\left(1 + \frac{2e}{1-e}\right) = t_0\left(\frac{1+e}{1-e}\right) = \sqrt{\frac{2h}{g}}\left(\frac{1+e}{1-e}\right)$।</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 29</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+          <t>$T_{total} = \sqrt{\frac{2h}{g}}\left(\frac{1+e}{1-e}\right)$</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5123,7 +4864,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>লিফট ও কার্যকর ত্বরণ (সমস্যা 30)</t>
+          <t>সংঘর্ষ, ব্যালেস্টিক পেন্ডুলাম ও শক্তি অপচয় (Collisions &amp; Impulse)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5136,24 +4877,25 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>$m = 6\text{ kg}$ ভরের একজন ব্যক্তি $a = 4\text{ m/s}^2$ ত্বরণে ওপরে ওঠা একটি লিফটে রাখা ওজন মাপক যন্ত্রে দাঁড়ালেন। ব্যক্তিটির আপাত ওজন কত নিউটন হবে?</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr"/>
+          <t>##GEO:rect[w=3,h=2][size:small]##
+একটি হাতুড়ির ভর $1.5\text{ kg}$। হাতুড়িটি $8\text{ m/s}$ বেগে একটি উল্লম্ব পেরেকের মাথায় আঘাত করে পেরেকের সাথে একসাথে কাঠের তক্তার ভেতর $4\text{ cm}$ ঢুকে থেমে যায়। পেরেকটি কর্তৃক হাতুড়ির ওপর প্রযুক্ত গড় প্রতিরোধকারী বল কত?</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=3,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 30)।</t>
+          <t>হাতুড়ির আদি গতিশক্তি $K = \frac{1}{2}m v^2 = \frac{1}{2}(1.5)(8^2) = 0.75(64) = 48\text{ J}$। কাজ-শক্তি উপপাদ্য: $F \times d = K \implies F \times 0.04 = 48 \implies F = \frac{48}{0.04} = 1200.0\text{ N}$।</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 30</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+          <t>গড় প্রতিরোধ বল $F = 1200.0\text{ N}$</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5173,37 +4915,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>পরিবর্তনশীল বল ও একমাত্রিক কাজ (সমস্যা 31)</t>
+          <t>উল্লম্ব বৃত্তাকার গতি ও যান্ত্রিক শক্তির নিত্যতা (Vertical Loop &amp; Energy Conservation)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>একটি কণার ওপর প্রযুক্ত বল দূরত্বের সাথে $F(x) = (8x^2 - 7x + 15)\text{ N}$ সমীকরণ অনুযায়ী পরিবর্তিত হয়। বস্তুটি $x = 1\text{ m}$ হতে $x = 85\text{ m}$-এ স্থানান্তরিত হলে বল দ্বারা সম্পাদিত মোট কাজ কত?</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr"/>
+          <t>##GEO:circle[r=3][size:small]##
+একটি $L = 1.0\text{ m}$ দীর্ঘ সুতার একপ্রান্তে $m = 500\text{ g}$ ভরের একটি পাথর বেঁধে উল্লম্ব তলে বৃত্তাকার পথে ঘোরানো হচ্ছে। বৃত্তের সর্বনিম্ন বিন্দুতে পাথরটির বেগ কত হলে সুতাটি না কুঁকড়ে উল্লম্ব বৃত্তটি সম্পূর্ণরূপে সফল হবে? সর্বোচ্চ ও সর্বনিম্ন বিন্দুতে সুতার টান বলের পার্থক্য কত? ($g = 9.8\text{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 31)।</t>
+          <t>উল্লম্ব বৃত্ত সম্পূর্ণ করতে সর্বনিম্ন বিন্দুতে বেগ $v_L = \sqrt{5gL} = \sqrt{5(9.8)(1.0)} = \sqrt{49} = 7.0\text{ m/s}$। সর্বোচ্চ বিন্দুতে টান $T_T = \frac{m v_T^2}{L} - mg = 0$ (সীমান্তিক)। সর্বনিম্ন বিন্দুতে টান $T_L = \frac{m v_L^2}{L} + mg = 5mg + mg = 6mg$। টানের পার্থক্য $\Delta T = T_L - T_T = 6mg = 6(0.5)(9.8) = 29.4\text{ N}$।</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 31</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+          <t>সর্বনিম্ন বেগ $v_{\min} = 7.0\text{ m/s}$, টানের পার্থক্য $\Delta T = 29.4\text{ N}$</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5223,12 +4966,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>কুয়ার পানিশূন্যকরণ ও পাম্পের ক্ষমতা (সমস্যা 32)</t>
+          <t>উল্লম্ব বৃত্তাকার গতি ও যান্ত্রিক শক্তির নিত্যতা (Vertical Loop &amp; Energy Conservation)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -5236,29 +4979,25 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>##GEO:cylinder[r=3,h=8][size:small]##
-$d = 10\text{ m}$ ব্যাস এবং $h = 10\text{ m}$ গভীরতাবিশিষ্ট একটি পানিপূর্ণ কুয়াকে 20 মিনিটে সম্পূর্ণ পানিশূন্য করতে কত অশ্বক্ষমতার (HP) পাম্প প্রয়োজন হবে, যদি পাম্পের দক্ষতা $\eta = 70\%$ হয়? ($g = 9.8\text{ m/s}^2$)</t>
+          <t>##GEO:circle[r=3.5][size:small]##
+একটি রোলারকাস্টার ট্র্যাকের লুপের ব্যাসার্ধ $R = 10\text{ m}$। লুপের শীর্ষবিন্দুতে আরোহীদের আসন হতে ছিটকে না পড়ার জন্য গাড়িটির সর্বনিম্ন কত দ্রুতি থাকতে হবে? গাড়িটিকে একটি মসৃণ ট্র্যাকের কত উচ্চতা $h$ হতে মুক্তভাবে ছাড়তে হবে? ($g = 9.8\text{ ms}^{-2}$)।</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>##GEO:cylinder[r=3,h=8][size:small]##</t>
+          <t>##GEO:circle[r=3.5][size:small]##</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 32)।</t>
+          <t>শীর্ষবিন্দুতে ন্যূনতম দ্রুতি $v_T = \sqrt{gR} = \sqrt{9.8 \times 10} = \sqrt{98} \approx 9.90\text{ m/s}$। শক্তির নিত্যতা অনুসারে আদি উচ্চতা: $mgh = mg(2R) + \frac{1}{2}mv_T^2 = 2mgR + \frac{1}{2}mgR = 2.5mgR \implies h = 2.5R = 2.5(10) = 25.0\text{ m}$।</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 32</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+          <t>শীর্ষ দ্রুতি $v_T = 9.90\text{ m/s}$, প্রারম্ভিক উচ্চতা $h = 25.0\text{ m}$</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5278,38 +5017,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>উল্লম্ব বৃত্তাকার পথে পূর্ণ ঘূর্ণন (সমস্যা 33)</t>
+          <t>উল্লম্ব বৃত্তাকার গতি ও যান্ত্রিক শক্তির নিত্যতা (Vertical Loop &amp; Energy Conservation)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>##GEO:circle-radius[r=5][size:small]##
-$R = 12\text{ m}$ ব্যাসার্ধের একটি মসৃণ উল্লম্ব বৃত্তাকার ট্র্যাকে নিরাপদে পূর্ণ ঘূর্ণন সম্পন্ন করতে সর্বনিম্ন বিন্দুতে একটি বস্তুর ন্যূনতম বেগ এবং সর্বোচ্চ বিন্দুতে ক্রান্তিক বেগ কত হতে হবে? ($g = 9.8\text{ m/s}^2$)</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি মসৃণ নিরেট অর্ধগোলকের ব্যাসার্ধ $R = 2.0\text{ m}$। অর্ধগোলকটির শীর্ষবিন্দুতে একটি ক্ষুদ্র বস্তু স্থির রাখা ছিল। সামান্য নাড়া দিলে বস্তুটি পিছলে গড়িয়ে নামতে শুরু করে। উল্লম্ব অক্ষের সাথে কত কোণে এবং ভূমি হতে কত উচ্চতায় পৌঁছালে বস্তুটি অর্ধগোলকের পৃষ্ঠ ত্যাগ করবে?</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 33)।</t>
+          <t>উল্লম্বের সাথে কোণ $\theta$ হলে উচ্চতা হ্রাস $y = R(1-\cos\theta)$। বেগ $v = \sqrt{2gy} = \sqrt{2gR(1-\cos\theta)}$। তলের লম্ব প্রতিক্রিয়া $N = mg\cos\theta - \frac{mv^2}{R}$। পৃষ্ঠ ত্যাগের মুহূর্তে $N = 0 \implies mg\cos\theta = \frac{m}{R}(2gR(1-\cos\theta)) \implies \cos\theta = 2 - 2\cos\theta \implies 3\cos\theta = 2 \implies \cos\theta = \frac{2}{3}$। উচ্চতা $h = R\cos\theta = \frac{2}{3}R = \frac{2}{3}(2.0) \approx 1.33\text{ m}$।</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 33</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+          <t>$\theta = \cos^{-1}(2/3) \approx 48.19^\circ$, উচ্চতা $h = \frac{2}{3}R = 1.33\text{ m}$</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5329,12 +5068,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>স্প্রিং-এর সংকোচন ও সংরক্ষণশীল বল (সমস্যা 34)</t>
+          <t>উল্লম্ব বৃত্তাকার গতি ও যান্ত্রিক শক্তির নিত্যতা (Vertical Loop &amp; Energy Conservation)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -5342,29 +5081,25 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>##PRESET:spring-mass[size:medium]##
-স্প্রিং ধ্রুবক $k = 14\text{ N/m}$ বিশিষ্ট একটি অনুভূমিক স্প্রিংকে স্বাভাবিক দৈর্ঘ্য হতে $16\text{ cm}$ সংকুচিত করে সামনে $m = 30\text{ kg}$ ভরের একটি ব্লক রেখে ছেড়ে দেওয়া হলে ব্লকের সর্বোচ্চ বেগ কত হবে?</t>
+          <t>##GEO:pendulum[angle=45,length=4][size:small]##
+একটি সাধারণ দোলকের ববের ভর $200\text{ g}$ এবং সুতার দৈর্ঘ্য $1.5\text{ m}$। ববটিকে অনুভূমিক অবস্থান পর্যন্ত তুলে ছেড়ে দেওয়া হলো ($g = 9.8\text{ ms}^{-2}$)। সাম্যাবস্থান অতিক্রম করার মুহূর্তে সুতার টান বলের মান কত?</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>##PRESET:spring-mass[size:medium]##</t>
+          <t>##GEO:pendulum[angle=45,length=4][size:small]##</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 34)।</t>
+          <t>অনুভূমিক অবস্থান হতে সাম্যাবস্থানে নামলে উচ্চতা হ্রাস $h = L = 1.5\text{ m}$। অর্জিত বেগ $v = \sqrt{2gL} = \sqrt{2(9.8)(1.5)} = \sqrt{29.4}\text{ m/s}$। সাম্যাবস্থানে টান $T = mg + \frac{mv^2}{L} = mg + \frac{m(2gL)}{L} = mg + 2mg = 3mg = 3(0.2)(9.8) = 5.88\text{ N}$।</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 34</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+          <t>সুতার টান $T = 5.88\text{ N}$</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5384,37 +5119,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>গোলার তক্তা ভেদ ও কাজ-শক্তি উপপাদ্য (সমস্যা 35)</t>
+          <t>উল্লম্ব বৃত্তাকার গতি ও যান্ত্রিক শক্তির নিত্যতা (Vertical Loop &amp; Energy Conservation)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>একটি বন্দুকের গুলি $v_0 = 2\text{ m/s}$ বেগে ছুটে গিয়ে একটি কাঠের তক্তার ভেতর $4\text{ cm}$ প্রবেশ করে থেমে যায়। গুলির ভর $m = 35\text{ g}$ হলে তক্তা কর্তৃক প্রযুক্ত গড় বাধাদানকারী বলের মান কত?</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>##GEO:rect[w=3,h=2][size:small]##
+একটি কণার বিভব শক্তি অপেক্ষক $U(r) = rac{A}{r^2} - rac{B}{r}$ ($A, B$ ধনাত্মক ধ্রুবক)। কণাটির সাম্যাবস্থা দূরত্ব $r_0$ এবং বিচ্ছিন্নকরণ শক্তি (Binding energy) নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=3,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 35)।</t>
+          <t>সাম্যাবস্থার জন্য: $\frac{dU}{dr} = 0 \implies -\frac{2A}{r^3} + \frac{B}{r^2} = 0 \implies \frac{B}{r^2} = \frac{2A}{r^3} \implies r_0 = \frac{2A}{B}$। সর্বনিম্ন বিভব শক্তি $U(r_0) = \frac{A}{(2A/B)^2} - \frac{B}{(2A/B)} = \frac{B^2}{4A} - \frac{B^2}{2A} = -\frac{B^2}{4A}$। অতএব বন্ধন শক্তি $E_b = -U(r_0) = \frac{B^2}{4A}$।</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 35</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+          <t>$r_0 = \frac{2A}{B}$, বন্ধন শক্তি $E_b = \frac{B^2}{4A}$</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5434,12 +5170,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ঢালু রাস্তায় মোটরের ব্যয়িত ক্ষমতা (সমস্যা 36)</t>
+          <t>উল্লম্ব বৃত্তাকার গতি ও যান্ত্রিক শক্তির নিত্যতা (Vertical Loop &amp; Energy Conservation)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -5447,29 +5183,25 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>##PRESET:incline(30)[size:medium]##
-$m = 4\text{ kg}$ ভরের একটি গাড়ি $1$ in $7$ ঢালু রাস্তা বেয়ে $10\text{ m/s}$ ধ্রুব বেগে ওপরে উঠছে। ঘর্ষণ বল $f = 70\text{ N}$ হলে গাড়ির ইঞ্জিনকে কত কিলোওয়াট (kW) ক্ষমতা প্রয়োগ করতে হবে?</t>
+          <t>##GEO:circle[r=2.8][size:small]##
+একটি উল্লম্ব বৃত্তে ঘূর্ণনরত কোনো বস্তুর অনুভূমিক অবস্থানে (Horizontal position) সুতার টান বল কত হবে, যদি সর্বনিম্ন বিন্দুতে বেগ $v_L = \sqrt{5gR}$ হয়?</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>##PRESET:incline(30)[size:medium]##</t>
+          <t>##GEO:circle[r=2.8][size:small]##</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 36)।</t>
+          <t>অনুভূমিক অবস্থানে উচ্চতা $h = R$। শক্তির নিত্যতা: $\frac{1}{2}m v_H^2 + mgR = \frac{1}{2}m(5gR) \implies v_H^2 = 5gR - 2gR = 3gR$। অনুভূমিক অবস্থানে ওজনের কোনো উপাংশ ব্যাসার্ধ বরাবর থাকে না, তাই সম্পূর্ণ কেন্দ্রমুখী বল সুতার টান যোগান দেয়: $T = \frac{m v_H^2}{R} = \frac{m(3gR)}{R} = 3mg$।</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 36</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+          <t>$T = 3mg$</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5489,37 +5221,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>ভরকেন্দ্রের সরণ ও স্তম্ভ নির্মাণ (সমস্যা 37)</t>
+          <t>উল্লম্ব বৃত্তাকার গতি ও যান্ত্রিক শক্তির নিত্যতা (Vertical Loop &amp; Energy Conservation)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>$m = 6\text{ kg}$ ভর এবং $t = 10\text{ cm}$ পুরুত্ববিশিষ্ট 15টি অভিন্ন ইট ভূমির ওপর একটির ওপর আরেকটি সাজিয়ে একটি খাড়া স্তম্ভ তৈরি করতে অভিকর্ষ বলের বিরুদ্ধে কী পরিমাণ কাজ করতে হবে?</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr"/>
+          <t>##GEO:rect[w=3,h=2][size:small]##
+একটি $0.5\text{ kg}$ ভরের কণা $xy$-তলে এমন একটি বলের প্রভাবে চলছে যার স্থানাঙ্ক $x(t) = 3t$ এবং $y(t) = 4t^2$। $t = 0$ হতে $t = 2\text{ s}$ সময়ে কণাটির ওপর মোট বল দ্বারা কৃতকাজ কত?</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=3,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 37)।</t>
+          <t>বেগ $v_x = 3\text{ m/s}$ (ধ্রুব), $v_y = 8t$। $t=0$-তে $v_1 = \sqrt{3^2 + 0} = 3\text{ m/s}$। $t=2$-এ $v_x = 3, v_y = 16 \implies v_2^2 = 3^2 + 16^2 = 9 + 256 = 265\text{ (m/s)}^2$। কাজ-শক্তি উপপাদ্য: $W = \Delta K = \frac{1}{2}m(v_2^2 - v_1^2) = \frac{1}{2}(0.5)(265 - 9) = 0.25(256) = 64.0\text{ J}$।</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 37</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+          <t>মোট কৃতকাজ $W = 64.0\text{ J}$</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5539,12 +5272,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>সংঘর্ষে গতিশক্তির অপচয় (সমস্যা 38)</t>
+          <t>উল্লম্ব বৃত্তাকার গতি ও যান্ত্রিক শক্তির নিত্যতা (Vertical Loop &amp; Energy Conservation)</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -5552,24 +5285,25 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>$m_1 = 8\text{ kg}$ ভরের একটি বস্তু $u_1 = 13\text{ m/s}$ বেগে চলে স্থির থাকা $m_2 = 20\text{ kg}$ ভরের বস্তুর সাথে সরাসরি স্থিতিস্থাপক সংঘর্ষে লিপ্ত হয়। সংঘর্ষের পর বস্তুদ্বয়ের বেগ কত হবে?</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
+          <t>##PRESET:spring-mass-system[size:medium]##
+একটি স্প্রিং বন্দুকের স্প্রিং ধ্রুবক $k = 400\text{ N/m}$। স্প্রিংটিকে $10\text{ cm}$ সংকুচিত করে $20\text{ g}$ ভরের একটি গুলি আটকে উল্লম্বভাবে ছোঁড়া হলো। গুলিটি সর্বোচ্চ কত উচ্চতায় উঠবে? ($g = 10\text{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>##PRESET:spring-mass-system[size:medium]##</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 38)।</t>
+          <t>স্প্রিংয়ের সঞ্চিত শক্তি $E_s = \frac{1}{2}k x^2 = \frac{1}{2}(400)(0.10^2) = 200(0.01) = 2.0\text{ J}$। সর্বোচ্চ উচ্চতায় সম্পূর্ণ শক্তি বিভব শক্তিতে রূপান্তর: $mgh = E_s \implies (0.020)(10)h = 2.0 \implies 0.2h = 2.0 \implies h = 10.0\text{ m}$।</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 38</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+          <t>সর্বোচ্চ উচ্চতা $h = 10.0\text{ m}$</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5589,42 +5323,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>সরল দোলকের শক্তি রূপান্তর (সমস্যা 39)</t>
+          <t>উল্লম্ব বৃত্তাকার গতি ও যান্ত্রিক শক্তির নিত্যতা (Vertical Loop &amp; Energy Conservation)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>##PRESET:pendulum(20)[size:medium]##
-$m = 10\text{ kg}$ ভরের একটি দোলক ববকে সাম্যাবস্থা হতে উলম্বের সাথে $16^\circ$ কোণে টেনে ছেড়ে দেওয়া হলো। সুতার দৈর্ঘ্য $L = 25\text{ m}$ হলে সাম্যাবস্থান অতিক্রমকালে ববের গতিশক্তি কত হবে?</t>
+          <t>##GEO:right-triangle[a=2,b=3.46,angle=30][size:small]##
+একটি ব্লককে একটি রুক্ষ আনত তলের শীর্ষ হতে ছেড়ে দেওয়া হলো। তলের দৈর্ঘ্য $4\text{ m}$ এবং নতি কোণ $30^\circ$। ব্লকের ওপর ঘর্ষণ বলের বিরুদ্ধে কাজ $19.6\text{ J}$ হলে এবং ব্লকের ভর $2\text{ kg}$ হলে তলদেশে ব্লকের গতিশক্তি কত? ($g = 9.8\text{ ms}^{-2}$)।</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>##PRESET:pendulum(20)[size:medium]##</t>
+          <t>##GEO:right-triangle[a=2,b=3.46,angle=30][size:small]##</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 39)।</t>
+          <t>শীর্ষে মোট বিভব শক্তি $U = mgh = mg(L\sin 30^\circ) = 2(9.8)(4 \times 0.5) = 2(9.8)(2) = 39.2\text{ J}$। ঘর্ষণে অপচয় $W_f = 19.6\text{ J}$। তলদেশে গতিশক্তি $K = U - W_f = 39.2 - 19.6 = 19.6\text{ J}$।</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 39</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+          <t>গতিশক্তি $K = 19.6\text{ J}$</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5644,12 +5374,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>লিফট ও কার্যকর ত্বরণ (সমস্যা 40)</t>
+          <t>উল্লম্ব বৃত্তাকার গতি ও যান্ত্রিক শক্তির নিত্যতা (Vertical Loop &amp; Energy Conservation)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -5657,24 +5387,25 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>$m = 12\text{ kg}$ ভরের একজন ব্যক্তি $a = 4\text{ m/s}^2$ ত্বরণে ওপরে ওঠা একটি লিফটে রাখা ওজন মাপক যন্ত্রে দাঁড়ালেন। ব্যক্তিটির আপাত ওজন কত নিউটন হবে?</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr"/>
+          <t>##PRESET:spring-mass-system[size:medium]##
+একটি $M$ ভরের ব্লক একটি মসৃণ অনুভূমিক সমতলে রাখা আছে। এর সাথে যুক্ত একটি স্প্রিং-এর অপর প্রান্তে $m$ ভরের অপর একটি ব্লক যুক্ত। স্প্রিংটিকে $x_0$ প্রসারিত করে ছেড়ে দিলে উভয় ব্লক গতিশীল হয়। $m$ ভরের ব্লকের সর্বাধিক গতিশক্তি কত হবে?</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>##PRESET:spring-mass-system[size:medium]##</t>
+        </is>
+      </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 40)।</t>
+          <t>ভরকেন্দ্র স্থির থাকায় ভরবেগের নিত্যতা: $m v_1 = M v_2$। আপেক্ষিক গতিশক্তি বিভাজন অনুসারে ক্ষুদ্রতর ভর বেশি গতিশক্তি লাভ করে: $K_m = \frac{M}{M+m} E_{total} = \frac{1}{2}\left(\frac{M}{M+m}\right)k x_0^2$।</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 40</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
+          <t>$K_{\max} = \frac{1}{2}\left(\frac{M}{M+m}\right)k x_0^2$</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5694,37 +5425,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>পরিবর্তনশীল বল ও একমাত্রিক কাজ (সমস্যা 41)</t>
+          <t>উন্নত শক্তি রূপান্তর ও গতিশক্তি-ভরবেগ সম্পর্ক (Advanced Work-Energy &amp; Power)</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>একটি কণার ওপর প্রযুক্ত বল দূরত্বের সাথে $F(x) = (14x^2 - 7x + 35)\text{ N}$ সমীকরণ অনুযায়ী পরিবর্তিত হয়। বস্তুটি $x = 1\text{ m}$ হতে $x = 75\text{ m}$-এ স্থানান্তরিত হলে বল দ্বারা সম্পাদিত মোট কাজ কত?</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি গাড়ি $v = 72\text{ km/h}$ সমদ্রুতিতে অনুভূমিক রাস্তায় চলছে। ইঞ্জিনের ক্ষমতা $20\text{ kW}$ হলে রাস্তার লব্ধি প্রতিরোধক বল কত? যদি গাড়িটি হঠাৎ ইঞ্জিন বন্ধ করে দেয় এবং মন্দন ধ্রুব থাকে, তবে গাড়িটি কত দূর গিয়ে থামবে? (গাড়ির ভর $1000\text{ kg}$)।</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 41)।</t>
+          <t>বেগ $v = \frac{72 \times 1000}{3600} = 20\text{ m/s}$। ক্ষমতা $P = F v \implies F = \frac{P}{v} = \frac{20000}{20} = 1000.0\text{ N}$। মন্দন $a = \frac{F}{m} = \frac{1000}{1000} = 1.0\text{ m/s}^2$। থামার দূরত্ব $s = \frac{v^2}{2a} = \frac{20^2}{2(1)} = \frac{400}{2} = 200.0\text{ m}$।</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 41</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
+          <t>বাধা বল $F = 1000.0\text{ N}$, থামার দূরত্ব $s = 200.0\text{ m}$</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5744,7 +5476,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>কুয়ার পানিশূন্যকরণ ও পাম্পের ক্ষমতা (সমস্যা 42)</t>
+          <t>উন্নত শক্তি রূপান্তর ও গতিশক্তি-ভরবেগ সম্পর্ক (Advanced Work-Energy &amp; Power)</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -5757,29 +5489,25 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>##GEO:cylinder[r=3,h=8][size:small]##
-$d = 2\text{ m}$ ব্যাস এবং $h = 10\text{ m}$ গভীরতাবিশিষ্ট একটি পানিপূর্ণ কুয়াকে 10 মিনিটে সম্পূর্ণ পানিশূন্য করতে কত অশ্বক্ষমতার (HP) পাম্প প্রয়োজন হবে, যদি পাম্পের দক্ষতা $\eta = 80\%$ হয়? ($g = 9.8\text{ m/s}^2$)</t>
+          <t>##PRESET:spring-mass-system[size:medium]##
+একটি $M$ ভরের কাঠের ব্লকের সাথে যুক্ত স্প্রিং ধ্রুবক $k$। $m$ ভরের একটি বুলেট $v_0$ বেগে অনুভূমিকভাবে এসে ব্লকে বিদ্ধ হলে স্প্রিংটির সর্বোচ্চ সংকোচন $x_{\max}$ কত হবে?</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>##GEO:cylinder[r=3,h=8][size:small]##</t>
+          <t>##PRESET:spring-mass-system[size:medium]##</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 42)।</t>
+          <t>সংঘর্ষে ভরবেগের নিত্যতা: $m v_0 = (M+m)V \implies V = \frac{m v_0}{M+m}$। সংঘাতের পর যৌথ গতিশক্তি স্প্রিংয়ের স্থিতিশক্তিতে রূপান্তর: $\frac{1}{2}(M+m)V^2 = \frac{1}{2}k x_{\max}^2 \implies x_{\max} = V\sqrt{\frac{M+m}{k}} = \frac{m v_0}{M+m}\sqrt{\frac{M+m}{k}} = \frac{m v_0}{\sqrt{k(M+m)}}$।</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 42</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+          <t>$x_{\max} = \frac{m v_0}{\sqrt{k(M+m)}}$</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5799,38 +5527,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>উল্লম্ব বৃত্তাকার পথে পূর্ণ ঘূর্ণন (সমস্যা 43)</t>
+          <t>উন্নত শক্তি রূপান্তর ও গতিশক্তি-ভরবেগ সম্পর্ক (Advanced Work-Energy &amp; Power)</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>##GEO:circle-radius[r=5][size:small]##
-$R = 4\text{ m}$ ব্যাসার্ধের একটি মসৃণ উল্লম্ব বৃত্তাকার ট্র্যাকে নিরাপদে পূর্ণ ঘূর্ণন সম্পন্ন করতে সর্বনিম্ন বিন্দুতে একটি বস্তুর ন্যূনতম বেগ এবং সর্বোচ্চ বিন্দুতে ক্রান্তিক বেগ কত হতে হবে? ($g = 9.8\text{ m/s}^2$)</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
+          <t>##GEO:rect[w=5,h=2][size:small]##
+একটি ট্রেন $108\text{ km/h}$ বেগে চলছে। ইঞ্জিনের ক্ষমতা $1.2\text{ MW}$। ট্রেনটির ওপর প্রযুক্ত মোট বাধানকারী বলের মান কত নিউটন?</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=5,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 43)।</t>
+          <t>বেগ $v = \frac{108 \times 1000}{3600} = 30\text{ m/s}$। ক্ষমতা $P = F v \implies F = \frac{P}{v} = \frac{1.2 \times 10^6\text{ W}}{30\text{ m/s}} = 40000.0\text{ N} = 40.0\text{ kN}$।</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 43</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
+          <t>প্রতিরোধক বল $F = 40000.0\text{ N} = 40.0\text{ kN}$</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5850,7 +5578,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>স্প্রিং-এর সংকোচন ও সংরক্ষণশীল বল (সমস্যা 44)</t>
+          <t>উন্নত শক্তি রূপান্তর ও গতিশক্তি-ভরবেগ সম্পর্ক (Advanced Work-Energy &amp; Power)</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -5863,29 +5591,25 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>##PRESET:spring-mass[size:medium]##
-স্প্রিং ধ্রুবক $k = 6\text{ N/m}$ বিশিষ্ট একটি অনুভূমিক স্প্রিংকে স্বাভাবিক দৈর্ঘ্য হতে $16\text{ cm}$ সংকুচিত করে সামনে $m = 20\text{ kg}$ ভরের একটি ব্লক রেখে ছেড়ে দেওয়া হলে ব্লকের সর্বোচ্চ বেগ কত হবে?</t>
+          <t>##GEO:circle[r=2][size:small]##
+একটি বস্তু $h$ উচ্চতা থেকে মেঝের ওপর পড়ার পর প্রতি বাউন্সে তার গতিশক্তির $25\%$ হারায়। ৩য় বাউন্সের পর বস্তুটি প্রারম্ভিক উচ্চতার শতকরা কত উচ্চতায় উঠবে?</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>##PRESET:spring-mass[size:medium]##</t>
+          <t>##GEO:circle[r=2][size:small]##</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 44)।</t>
+          <t>গতিশক্তি $25\%$ হ্রাসের অর্থ প্রতি বাউন্সে স্থিতিশক্তি/উচ্চতা $75\%$ বা $0.75$ অংশ হয় ($e^2 = 0.75$)। ১ম বাউন্সে $h_1 = 0.75h$, ২য় বাউন্সে $h_2 = (0.75)^2 h$, ৩য় বাউন্সে $h_3 = (0.75)^3 h = 0.421875 h \approx 42.19\%$।</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 44</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+          <t>উচ্চতা $h_3 = 0.422 h$ ($42.19\%$ উচ্চতা)</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5905,37 +5629,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>গোলার তক্তা ভেদ ও কাজ-শক্তি উপপাদ্য (সমস্যা 45)</t>
+          <t>উন্নত শক্তি রূপান্তর ও গতিশক্তি-ভরবেগ সম্পর্ক (Advanced Work-Energy &amp; Power)</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>একটি বন্দুকের গুলি $v_0 = 8\text{ m/s}$ বেগে ছুটে গিয়ে একটি কাঠের তক্তার ভেতর $4\text{ cm}$ প্রবেশ করে থেমে যায়। গুলির ভর $m = 25\text{ g}$ হলে তক্তা কর্তৃক প্রযুক্ত গড় বাধাদানকারী বলের মান কত?</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+          <t>##PRESET:vector-addition[size:medium]##
+একটি কণার ওপর প্রযুক্ত বল $ec{F} = (4x\hat{i} + 3y^2\hat{j})	ext{ N}$। কণাটি $(0,0)$ হতে $(2, 3)$ বিন্দুতে সরলরেখা বরাবর স্থানান্তরিত হলে মোট কৃতকাজ কত?</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>##PRESET:vector-addition[size:medium]##</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 45)।</t>
+          <t>$W = \int_0^2 4x dx + \int_0^3 3y^2 dy = [2x^2]_0^2 + [y^3]_0^3 = 2(4) + 27 = 8 + 27 = 35.0\text{ J}$।</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 45</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
+          <t>মোট কাজ $W = 35.0\text{ J}$</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5955,7 +5680,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>ঢালু রাস্তায় মোটরের ব্যয়িত ক্ষমতা (সমস্যা 46)</t>
+          <t>উন্নত শক্তি রূপান্তর ও গতিশক্তি-ভরবেগ সম্পর্ক (Advanced Work-Energy &amp; Power)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -5968,29 +5693,25 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>##PRESET:incline(30)[size:medium]##
-$m = 10\text{ kg}$ ভরের একটি গাড়ি $1$ in $7$ ঢালু রাস্তা বেয়ে $30\text{ m/s}$ ধ্রুব বেগে ওপরে উঠছে। ঘর্ষণ বল $f = 80\text{ N}$ হলে গাড়ির ইঞ্জিনকে কত কিলোওয়াট (kW) ক্ষমতা প্রয়োগ করতে হবে?</t>
+          <t>##GEO:rect[w=3,h=2][size:small]##
+একটি কণার বিভব শক্তি $U(x) = rac{a}{x^2} - rac{b}{x}$। কণাটির ওপর প্রযুক্ত বল কখন শূন্য হবে এবং সাম্যাবস্থায় কণাটির বাঁধাই শক্তি (Binding Energy) কত?</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>##PRESET:incline(30)[size:medium]##</t>
+          <t>##GEO:rect[w=3,h=2][size:small]##</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 46)।</t>
+          <t>বল $F(x) = -\frac{dU}{dx} = -\left(-\frac{2a}{x^3} + \frac{b}{x^2}\right) = \frac{2a}{x^3} - \frac{b}{x^2}$। সাম্যাবস্থায় $F=0 \implies \frac{b}{x^2} = \frac{2a}{x^3} \implies x_0 = \frac{2a}{b}$। বিভব $U(x_0) = \frac{a}{(2a/b)^2} - \frac{b}{(2a/b)} = \frac{b^2}{4a} - \frac{b^2}{2a} = -\frac{b^2}{4a}$। বাঁধাই শক্তি $E_b = |U(x_0)| = \frac{b^2}{4a}$।</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 46</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
+          <t>$x_0 = \frac{2a}{b}, E_b = \frac{b^2}{4a}$</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6010,37 +5731,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>ভরকেন্দ্রের সরণ ও স্তম্ভ নির্মাণ (সমস্যা 47)</t>
+          <t>উন্নত শক্তি রূপান্তর ও গতিশক্তি-ভরবেগ সম্পর্ক (Advanced Work-Energy &amp; Power)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>$m = 12\text{ kg}$ ভর এবং $t = 10\text{ cm}$ পুরুত্ববিশিষ্ট 35টি অভিন্ন ইট ভূমির ওপর একটির ওপর আরেকটি সাজিয়ে একটি খাড়া স্তম্ভ তৈরি করতে অভিকর্ষ বলের বিরুদ্ধে কী পরিমাণ কাজ করতে হবে?</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##
+একটি পাম্প দিয়ে $10\text{ m}$ গভীর কূয়ার নিচের অর্ধেক খালি করা হচ্ছে ($r = 1.2\text{ m}$)। পানির ভর $m$ এবং কৃতকাজের সঠিক রাশিমালা ও মান নির্ণয় কর ($g = 9.8\text{ ms}^{-2}, \rho = 1000\text{ kg/m}^3$)।</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 47)।</t>
+          <t>নিচের অর্ধেকের গভীরতা $5\\text{ m}$ হতে $10\\text{ m}$ পর্যন্ত। পানির আয়তন $V = \pi r^2 (5) = \pi (1.2^2)(5) = 7.2\pi \approx 22.62\text{ m}^3$। ভর $m = 22619.5\text{ kg}$। ভরকেন্দ্রের গড় সরণ $\bar{h} = 5 + 2.5 = 7.5\text{ m}$। কৃতকাজ $W = m g \bar{h} = 22619.5 \times 9.8 \times 7.5 \approx 1662533\text{ J} \approx 1.66\times 10^6\text{ J}$।</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 47</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
+          <t>পানির ভর $m = 22619.5\text{ kg}$, কৃতকাজ $W = 1.66\times 10^6\text{ J}$</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6060,7 +5782,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>সংঘর্ষে গতিশক্তির অপচয় (সমস্যা 48)</t>
+          <t>উন্নত শক্তি রূপান্তর ও গতিশক্তি-ভরবেগ সম্পর্ক (Advanced Work-Energy &amp; Power)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6073,24 +5795,25 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>$m_1 = 14\text{ kg}$ ভরের একটি বস্তু $u_1 = 13\text{ m/s}$ বেগে চলে স্থির থাকা $m_2 = 10\text{ kg}$ ভরের বস্তুর সাথে সরাসরি স্থিতিস্থাপক সংঘর্ষে লিপ্ত হয়। সংঘর্ষের পর বস্তুদ্বয়ের বেগ কত হবে?</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr"/>
+          <t>##GEO:pendulum[angle=60,length=4][size:small]##
+একটি সরল দোলক উল্লম্বের সাথে $60^\circ$ কোণ হতে ছেড়ে দেওয়া হলো। ববের ভর $m = 100\text{ g}$ এবং দৈর্ঘ্য $L = 1.0\text{ m}$ হলে সাম্যাবস্থানে ববের গতিশক্তি এবং বেগ কত? ($g = 9.8\text{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>##GEO:pendulum[angle=60,length=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 48)।</t>
+          <t>উচ্চতা হ্রাস $h = L(1 - \cos 60^\circ) = 1.0(1 - 0.5) = 0.5\text{ m}$। গতিশক্তি $K = mgh = 0.1 \times 9.8 \times 0.5 = 0.49\text{ J}$। বেগ $v = \sqrt{2gh} = \sqrt{2(9.8)(0.5)} = \sqrt{9.8} \approx 3.13\text{ m/s}$।</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 48</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
+          <t>গতিশক্তি $K = 0.49\text{ J}$, বেগ $v = 3.13\text{ m/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6110,42 +5833,38 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>সরল দোলকের শক্তি রূপান্তর (সমস্যা 49)</t>
+          <t>উন্নত শক্তি রূপান্তর ও গতিশক্তি-ভরবেগ সম্পর্ক (Advanced Work-Energy &amp; Power)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>##PRESET:pendulum(20)[size:medium]##
-$m = 2\text{ kg}$ ভরের একটি দোলক ববকে সাম্যাবস্থা হতে উলম্বের সাথে $16^\circ$ কোণে টেনে ছেড়ে দেওয়া হলো। সুতার দৈর্ঘ্য $L = 15\text{ m}$ হলে সাম্যাবস্থান অতিক্রমকালে ববের গতিশক্তি কত হবে?</t>
+          <t>##GEO:circle[r=2][size:small]##
+একটি কণার গতিশক্তি $K$ এবং ভরবেগ $p$-এর মধ্যে সম্পর্ক $K = rac{p^2}{2m}$। যদি ভরবেগ $50\%$ বৃদ্ধি পায়, তবে গতিশক্তি কত শতাংশ বৃদ্ধি পাবে?</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>##PRESET:pendulum(20)[size:medium]##</t>
+          <t>##GEO:circle[r=2][size:small]##</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 49)।</t>
+          <t>নতুন ভরবেগ $p' = 1.5p$। নতুন গতিশক্তি $K' = \frac{(1.5p)^2}{2m} = 2.25\left(\frac{p^2}{2m}\right) = 2.25K$। গতিশক্তির শতকরা বৃদ্ধি $= (2.25 - 1) \times 100\% = 125\%$।</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 49</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
+          <t>গতিশক্তি বৃদ্ধি পাবে $125\%$</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6165,7 +5884,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>লিফট ও কার্যকর ত্বরণ (সমস্যা 50)</t>
+          <t>উন্নত শক্তি রূপান্তর ও গতিশক্তি-ভরবেগ সম্পর্ক (Advanced Work-Energy &amp; Power)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6178,24 +5897,25 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>$m = 4\text{ kg}$ ভরের একজন ব্যক্তি $a = 4\text{ m/s}^2$ ত্বরণে ওপরে ওঠা একটি লিফটে রাখা ওজন মাপক যন্ত্রে দাঁড়ালেন। ব্যক্তিটির আপাত ওজন কত নিউটন হবে?</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি চেইন যার দৈর্ঘ্য $L$ এবং ভর $M$, একটি মসৃণ গোলার্ধের (Hemisphere of radius $R = L/(\pi/2)$) শীর্ষ হতে পিছলে নামতে শুরু করল। চেইনটি সম্পূর্ণ পিছলে পৃষ্ঠ ত্যাগ করার মুহূর্তে এর গতিশক্তি কত?</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>পদার্থবিজ্ঞানের কাজ-শক্তি সংরক্ষণশীলতা নীতি ও নিউটনীয় বলবিদ্যার সংশ্লিষ্ট সূত্রানুসারে বিশদ সমাধান (সমস্যা 50)।</t>
+          <t>আদি অবস্থায় কোয়াড্র্যান্টে ভরকেন্দ্রের উচ্চতা $\bar{y}_i = \frac{2R}{\pi}$। পৃষ্ঠ ত্যাগের পর আনুভূমিকভাবে ভরকেন্দ্রের উচ্চতা শূন্য বা তলের ভিত্তিতে বিভব শক্তির রূপান্তর বিশ্লেষণ করে: বিভব শক্তি হ্রাস $\Delta U = M g R\left(1 - \frac{2}{\pi}\right)$। সম্পূর্ণ বিভব শক্তি গতিশক্তিতে রূপান্তরিত হওয়ায় $K = M g R\left(1 - \frac{2}{\pi}\right)$।</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>গাণিতিক উত্তর 50</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
+          <t>$K = M g R\left(1 - \frac{2}{\pi}\right)$</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
